--- a/public/analytics-data.xlsx
+++ b/public/analytics-data.xlsx
@@ -8,19 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mona\Downloads\PhysicsWallahDashboard-Axio\axioP-x-PW-main\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95EA2B1-FF68-4D18-84AB-A694AE7D2C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9F0EDE6-766A-4185-A074-B9053D505840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Analytics Data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10266" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10312" uniqueCount="269">
   <si>
     <t>Date</t>
   </si>
@@ -792,6 +803,42 @@
   <si>
     <t>Report_Dec_Platform_Facebook_RemovalRate</t>
   </si>
+  <si>
+    <t>Report_Jan_Week1_DateRange</t>
+  </si>
+  <si>
+    <t>Report_Jan_Week1_Sent</t>
+  </si>
+  <si>
+    <t>Report_Jan_Week1_Approved</t>
+  </si>
+  <si>
+    <t>Report_Jan_Week1_Removed</t>
+  </si>
+  <si>
+    <t>Report_Jan_Week1_Pending</t>
+  </si>
+  <si>
+    <t>Report_Jan_Week1_RemovalRate</t>
+  </si>
+  <si>
+    <t>Report_Jan_Week2_DateRange</t>
+  </si>
+  <si>
+    <t>Report_Jan_Week2_Sent</t>
+  </si>
+  <si>
+    <t>Report_Jan_Week2_Approved</t>
+  </si>
+  <si>
+    <t>Report_Jan_Week2_Removed</t>
+  </si>
+  <si>
+    <t>Report_Jan_Week2_Pending</t>
+  </si>
+  <si>
+    <t>Report_Jan_Week2_RemovalRate</t>
+  </si>
 </sst>
 </file>
 
@@ -839,7 +886,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -896,15 +943,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -934,8 +972,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1276,13 +1314,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DI163"/>
+  <dimension ref="A1:EY209"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.5" customWidth="1"/>
+    <col min="80" max="80" width="10.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:113" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:153" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1521,109 +1560,229 @@
         <v>78</v>
       </c>
       <c r="CB1" s="5">
+        <v>46024</v>
+      </c>
+      <c r="CC1" s="5">
+        <v>46025</v>
+      </c>
+      <c r="CD1" s="5">
+        <v>46027</v>
+      </c>
+      <c r="CE1" s="5">
+        <v>46028</v>
+      </c>
+      <c r="CF1" s="5">
+        <v>46029</v>
+      </c>
+      <c r="CG1" s="5">
+        <v>46030</v>
+      </c>
+      <c r="CH1" s="5">
+        <v>46031</v>
+      </c>
+      <c r="CI1" s="5">
+        <v>46032</v>
+      </c>
+      <c r="CJ1" s="5">
+        <v>46034</v>
+      </c>
+      <c r="CK1" s="5">
+        <v>46035</v>
+      </c>
+      <c r="CL1" s="5">
+        <v>46036</v>
+      </c>
+      <c r="CM1" s="5">
+        <v>46037</v>
+      </c>
+      <c r="CN1" s="5">
+        <v>46038</v>
+      </c>
+      <c r="CO1" s="5">
+        <v>46039</v>
+      </c>
+      <c r="CP1" s="5">
+        <v>46041</v>
+      </c>
+      <c r="CQ1" s="5">
+        <v>46042</v>
+      </c>
+      <c r="CR1" s="5">
+        <v>46043</v>
+      </c>
+      <c r="CS1" s="5">
+        <v>46044</v>
+      </c>
+      <c r="CT1" s="5">
+        <v>46045</v>
+      </c>
+      <c r="CU1" s="5">
+        <v>46046</v>
+      </c>
+      <c r="CV1" s="5">
+        <v>46049</v>
+      </c>
+      <c r="CW1" s="5">
+        <v>46050</v>
+      </c>
+      <c r="CX1" s="5">
+        <v>46051</v>
+      </c>
+      <c r="CY1" s="5">
+        <v>46052</v>
+      </c>
+      <c r="CZ1" s="5">
+        <v>46053</v>
+      </c>
+      <c r="DA1" s="5">
         <v>46055</v>
       </c>
-      <c r="CC1" s="5">
+      <c r="DB1" s="5">
         <v>46056</v>
       </c>
-      <c r="CD1" s="5">
+      <c r="DC1" s="5">
         <v>46057</v>
       </c>
-      <c r="CE1" s="5">
+      <c r="DD1" s="5">
         <v>46058</v>
       </c>
-      <c r="CF1" s="5">
+      <c r="DE1" s="5">
         <v>46059</v>
       </c>
-      <c r="CG1" s="5">
+      <c r="DF1" s="5">
         <v>46060</v>
       </c>
-      <c r="CH1" s="5">
+      <c r="DG1" s="5">
         <v>46062</v>
       </c>
-      <c r="CI1" s="5">
+      <c r="DH1" s="5">
         <v>46063</v>
       </c>
-      <c r="CJ1" s="5">
+      <c r="DI1" s="5">
         <v>46064</v>
       </c>
-      <c r="CK1" s="5">
+      <c r="DJ1" s="5">
         <v>46065</v>
       </c>
-      <c r="CL1" s="5">
+      <c r="DK1" s="5">
         <v>46066</v>
       </c>
-      <c r="CM1" s="5">
+      <c r="DL1" s="5">
         <v>46067</v>
       </c>
-      <c r="CN1" s="5">
+      <c r="DM1" s="5">
         <v>46069</v>
       </c>
-      <c r="CO1" s="5">
+      <c r="DN1" s="5">
         <v>46070</v>
       </c>
-      <c r="CP1" s="5">
+      <c r="DO1" s="5">
         <v>46071</v>
       </c>
-      <c r="CQ1" s="5">
+      <c r="DP1" s="5">
         <v>46072</v>
       </c>
-      <c r="CR1" s="5">
+      <c r="DQ1" s="5">
         <v>46073</v>
       </c>
-      <c r="CS1" s="5">
+      <c r="DR1" s="5">
         <v>46074</v>
       </c>
-      <c r="CT1" s="5">
+      <c r="DS1" s="5">
         <v>46076</v>
       </c>
-      <c r="CU1" s="5">
+      <c r="DT1" s="5">
         <v>46077</v>
       </c>
-      <c r="CV1" s="5">
+      <c r="DU1" s="5">
         <v>46078</v>
       </c>
-      <c r="CW1" s="5">
+      <c r="DV1" s="5">
         <v>46079</v>
       </c>
-      <c r="CX1" s="5">
+      <c r="DW1" s="5">
         <v>46080</v>
       </c>
-      <c r="CY1" s="5">
+      <c r="DX1" s="5">
         <v>46081</v>
       </c>
-      <c r="CZ1" s="5">
+      <c r="DY1" s="5">
         <v>46083</v>
       </c>
-      <c r="DA1" s="5">
+      <c r="DZ1" s="5">
         <v>46086</v>
       </c>
-      <c r="DB1" s="5">
+      <c r="EA1" s="5">
         <v>46087</v>
       </c>
-      <c r="DC1" s="5">
+      <c r="EB1" s="5">
         <v>46088</v>
       </c>
-      <c r="DD1" s="5">
+      <c r="EC1" s="5">
         <v>46090</v>
       </c>
-      <c r="DE1" s="5">
+      <c r="ED1" s="5">
         <v>46091</v>
       </c>
-      <c r="DF1" s="5">
+      <c r="EE1" s="5">
         <v>46092</v>
       </c>
-      <c r="DG1" s="5">
+      <c r="EF1" s="5">
         <v>46093</v>
       </c>
-      <c r="DH1" s="5">
+      <c r="EG1" s="5">
         <v>46094</v>
       </c>
-      <c r="DI1" s="5">
+      <c r="EH1" s="5">
         <v>46095</v>
       </c>
+      <c r="EI1" s="5">
+        <v>46097</v>
+      </c>
+      <c r="EJ1" s="5">
+        <v>46098</v>
+      </c>
+      <c r="EK1" s="5">
+        <v>46099</v>
+      </c>
+      <c r="EL1" s="5">
+        <v>46100</v>
+      </c>
+      <c r="EM1" s="5">
+        <v>46101</v>
+      </c>
+      <c r="EN1" s="5">
+        <v>46102</v>
+      </c>
+      <c r="EO1" s="5">
+        <v>46104</v>
+      </c>
+      <c r="EP1" s="5">
+        <v>46105</v>
+      </c>
+      <c r="EQ1" s="5">
+        <v>46106</v>
+      </c>
+      <c r="ER1" s="5">
+        <v>46107</v>
+      </c>
+      <c r="ES1" s="5">
+        <v>46108</v>
+      </c>
+      <c r="ET1" s="5">
+        <v>46109</v>
+      </c>
+      <c r="EU1" s="5">
+        <v>46110</v>
+      </c>
+      <c r="EV1" s="5">
+        <v>46111</v>
+      </c>
+      <c r="EW1" s="5">
+        <v>46112</v>
+      </c>
     </row>
-    <row r="2" spans="1:113" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:153" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>79</v>
       </c>
@@ -1862,109 +2021,226 @@
         <v>98</v>
       </c>
       <c r="CB2" s="6">
+        <v>93</v>
+      </c>
+      <c r="CC2" s="6">
+        <v>112</v>
+      </c>
+      <c r="CD2" s="6">
+        <v>97</v>
+      </c>
+      <c r="CE2" s="6">
+        <v>91</v>
+      </c>
+      <c r="CF2" s="6">
+        <v>118</v>
+      </c>
+      <c r="CG2" s="6">
+        <v>105</v>
+      </c>
+      <c r="CH2" s="6">
+        <v>101</v>
+      </c>
+      <c r="CI2" s="6">
+        <v>75</v>
+      </c>
+      <c r="CJ2" s="6">
+        <v>120</v>
+      </c>
+      <c r="CK2" s="6">
+        <v>105</v>
+      </c>
+      <c r="CL2" s="6">
+        <v>124</v>
+      </c>
+      <c r="CM2" s="6">
+        <v>84</v>
+      </c>
+      <c r="CN2" s="6">
+        <v>110</v>
+      </c>
+      <c r="CO2" s="6">
+        <v>110</v>
+      </c>
+      <c r="CP2" s="6">
+        <v>75</v>
+      </c>
+      <c r="CQ2" s="6">
+        <v>139</v>
+      </c>
+      <c r="CR2" s="6">
+        <v>105</v>
+      </c>
+      <c r="CS2" s="6">
+        <v>112</v>
+      </c>
+      <c r="CT2" s="6">
+        <v>104</v>
+      </c>
+      <c r="CU2" s="6">
+        <v>104</v>
+      </c>
+      <c r="CV2" s="6">
+        <v>45</v>
+      </c>
+      <c r="CW2" s="6">
+        <v>48</v>
+      </c>
+      <c r="CX2" s="6">
+        <v>40</v>
+      </c>
+      <c r="CY2" s="6">
+        <v>35</v>
+      </c>
+      <c r="CZ2" s="6">
+        <v>40</v>
+      </c>
+      <c r="DA2" s="6">
         <v>50</v>
       </c>
-      <c r="CC2" s="6">
+      <c r="DB2" s="6">
         <v>75</v>
       </c>
-      <c r="CD2" s="6">
+      <c r="DC2" s="6">
         <v>56</v>
-      </c>
-      <c r="CE2" s="6">
-        <v>56</v>
-      </c>
-      <c r="CF2" s="6">
-        <v>72</v>
-      </c>
-      <c r="CG2" s="6">
-        <v>64</v>
-      </c>
-      <c r="CH2" s="6">
-        <v>89</v>
-      </c>
-      <c r="CI2" s="6">
-        <v>76</v>
-      </c>
-      <c r="CJ2" s="6">
-        <v>70</v>
-      </c>
-      <c r="CK2" s="6">
-        <v>19</v>
-      </c>
-      <c r="CL2" s="6">
-        <v>64</v>
-      </c>
-      <c r="CM2" s="6">
-        <v>83</v>
-      </c>
-      <c r="CN2" s="6">
-        <v>51</v>
-      </c>
-      <c r="CO2" s="6">
-        <v>68</v>
-      </c>
-      <c r="CP2" s="6">
-        <v>77</v>
-      </c>
-      <c r="CQ2" s="6">
-        <v>96</v>
-      </c>
-      <c r="CR2" s="6">
-        <v>55</v>
-      </c>
-      <c r="CS2" s="6">
-        <v>56</v>
-      </c>
-      <c r="CT2" s="6">
-        <v>56</v>
-      </c>
-      <c r="CU2" s="6">
-        <v>51</v>
-      </c>
-      <c r="CV2" s="6">
-        <v>48</v>
-      </c>
-      <c r="CW2" s="6">
-        <v>75</v>
-      </c>
-      <c r="CX2" s="6">
-        <v>45</v>
-      </c>
-      <c r="CY2" s="6">
-        <v>40</v>
-      </c>
-      <c r="CZ2" s="6">
-        <v>42</v>
-      </c>
-      <c r="DA2" s="6">
-        <v>71</v>
-      </c>
-      <c r="DB2" s="6">
-        <v>53</v>
-      </c>
-      <c r="DC2" s="6">
-        <v>35</v>
       </c>
       <c r="DD2" s="6">
         <v>56</v>
       </c>
       <c r="DE2" s="6">
+        <v>72</v>
+      </c>
+      <c r="DF2" s="6">
+        <v>64</v>
+      </c>
+      <c r="DG2" s="6">
+        <v>89</v>
+      </c>
+      <c r="DH2" s="6">
+        <v>76</v>
+      </c>
+      <c r="DI2" s="6">
+        <v>70</v>
+      </c>
+      <c r="DJ2" s="6">
+        <v>19</v>
+      </c>
+      <c r="DK2" s="6">
+        <v>64</v>
+      </c>
+      <c r="DL2" s="6">
+        <v>83</v>
+      </c>
+      <c r="DM2" s="6">
+        <v>51</v>
+      </c>
+      <c r="DN2" s="6">
+        <v>68</v>
+      </c>
+      <c r="DO2" s="6">
+        <v>77</v>
+      </c>
+      <c r="DP2" s="6">
+        <v>96</v>
+      </c>
+      <c r="DQ2" s="6">
+        <v>55</v>
+      </c>
+      <c r="DR2" s="6">
+        <v>56</v>
+      </c>
+      <c r="DS2" s="6">
+        <v>56</v>
+      </c>
+      <c r="DT2" s="6">
+        <v>51</v>
+      </c>
+      <c r="DU2" s="6">
+        <v>48</v>
+      </c>
+      <c r="DV2" s="6">
+        <v>75</v>
+      </c>
+      <c r="DW2" s="6">
+        <v>45</v>
+      </c>
+      <c r="DX2" s="6">
+        <v>40</v>
+      </c>
+      <c r="DY2" s="6">
+        <v>42</v>
+      </c>
+      <c r="DZ2" s="6">
+        <v>71</v>
+      </c>
+      <c r="EA2" s="6">
+        <v>53</v>
+      </c>
+      <c r="EB2" s="6">
+        <v>35</v>
+      </c>
+      <c r="EC2" s="6">
+        <v>56</v>
+      </c>
+      <c r="ED2" s="6">
         <v>62</v>
       </c>
-      <c r="DF2" s="6">
+      <c r="EE2" s="6">
         <v>16</v>
       </c>
-      <c r="DG2" s="6">
+      <c r="EF2" s="6">
         <v>27</v>
       </c>
-      <c r="DH2" s="6">
+      <c r="EG2" s="6">
         <v>31</v>
       </c>
-      <c r="DI2" s="6">
+      <c r="EH2" s="6">
         <v>41</v>
       </c>
+      <c r="EI2" s="6">
+        <v>18</v>
+      </c>
+      <c r="EJ2" s="6">
+        <v>8</v>
+      </c>
+      <c r="EK2" s="6">
+        <v>29</v>
+      </c>
+      <c r="EL2" s="6">
+        <v>1</v>
+      </c>
+      <c r="EM2" s="6">
+        <v>5</v>
+      </c>
+      <c r="EN2" s="6">
+        <v>43</v>
+      </c>
+      <c r="EO2" s="6">
+        <v>45</v>
+      </c>
+      <c r="EP2" s="6">
+        <v>43</v>
+      </c>
+      <c r="EQ2" s="6">
+        <v>52</v>
+      </c>
+      <c r="ER2" s="6">
+        <v>48</v>
+      </c>
+      <c r="ES2" s="6">
+        <v>41</v>
+      </c>
+      <c r="ET2" s="6">
+        <v>48</v>
+      </c>
+      <c r="EU2" s="6">
+        <v>62</v>
+      </c>
+      <c r="EV2" s="6">
+        <v>30</v>
+      </c>
     </row>
-    <row r="3" spans="1:113" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:153" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>80</v>
       </c>
@@ -2203,109 +2479,226 @@
         <v>85</v>
       </c>
       <c r="CB3" s="6">
+        <v>79</v>
+      </c>
+      <c r="CC3" s="6">
+        <v>98</v>
+      </c>
+      <c r="CD3" s="6">
+        <v>85</v>
+      </c>
+      <c r="CE3" s="6">
+        <v>73</v>
+      </c>
+      <c r="CF3" s="6">
+        <v>112</v>
+      </c>
+      <c r="CG3" s="6">
+        <v>100</v>
+      </c>
+      <c r="CH3" s="6">
+        <v>101</v>
+      </c>
+      <c r="CI3" s="6">
+        <v>75</v>
+      </c>
+      <c r="CJ3" s="6">
+        <v>117</v>
+      </c>
+      <c r="CK3" s="6">
+        <v>105</v>
+      </c>
+      <c r="CL3" s="6">
+        <v>116</v>
+      </c>
+      <c r="CM3" s="6">
+        <v>58</v>
+      </c>
+      <c r="CN3" s="6">
+        <v>110</v>
+      </c>
+      <c r="CO3" s="6">
+        <v>93</v>
+      </c>
+      <c r="CP3" s="6">
+        <v>74</v>
+      </c>
+      <c r="CQ3" s="6">
+        <v>139</v>
+      </c>
+      <c r="CR3" s="6">
+        <v>105</v>
+      </c>
+      <c r="CS3" s="6">
+        <v>112</v>
+      </c>
+      <c r="CT3" s="6">
+        <v>23</v>
+      </c>
+      <c r="CU3" s="6">
+        <v>104</v>
+      </c>
+      <c r="CV3" s="6">
+        <v>45</v>
+      </c>
+      <c r="CW3" s="6">
+        <v>35</v>
+      </c>
+      <c r="CX3" s="6">
+        <v>40</v>
+      </c>
+      <c r="CY3" s="6">
+        <v>35</v>
+      </c>
+      <c r="CZ3" s="6">
+        <v>30</v>
+      </c>
+      <c r="DA3" s="6">
         <v>50</v>
       </c>
-      <c r="CC3" s="6">
+      <c r="DB3" s="6">
         <v>62</v>
       </c>
-      <c r="CD3" s="6">
+      <c r="DC3" s="6">
         <v>56</v>
-      </c>
-      <c r="CE3" s="6">
-        <v>56</v>
-      </c>
-      <c r="CF3" s="6">
-        <v>8</v>
-      </c>
-      <c r="CG3" s="6">
-        <v>64</v>
-      </c>
-      <c r="CH3" s="6">
-        <v>86</v>
-      </c>
-      <c r="CI3" s="6">
-        <v>56</v>
-      </c>
-      <c r="CJ3" s="6">
-        <v>70</v>
-      </c>
-      <c r="CK3" s="6">
-        <v>19</v>
-      </c>
-      <c r="CL3" s="6">
-        <v>64</v>
-      </c>
-      <c r="CM3" s="6">
-        <v>83</v>
-      </c>
-      <c r="CN3" s="6">
-        <v>51</v>
-      </c>
-      <c r="CO3" s="6">
-        <v>68</v>
-      </c>
-      <c r="CP3" s="6">
-        <v>56</v>
-      </c>
-      <c r="CQ3" s="6">
-        <v>95</v>
-      </c>
-      <c r="CR3" s="6">
-        <v>55</v>
-      </c>
-      <c r="CS3" s="6">
-        <v>49</v>
-      </c>
-      <c r="CT3" s="6">
-        <v>54</v>
-      </c>
-      <c r="CU3" s="6">
-        <v>50</v>
-      </c>
-      <c r="CV3" s="6">
-        <v>46</v>
-      </c>
-      <c r="CW3" s="6">
-        <v>74</v>
-      </c>
-      <c r="CX3" s="6">
-        <v>45</v>
-      </c>
-      <c r="CY3" s="6">
-        <v>40</v>
-      </c>
-      <c r="CZ3" s="6">
-        <v>40</v>
-      </c>
-      <c r="DA3" s="6">
-        <v>64</v>
-      </c>
-      <c r="DB3" s="6">
-        <v>34</v>
-      </c>
-      <c r="DC3" s="6">
-        <v>35</v>
       </c>
       <c r="DD3" s="6">
         <v>56</v>
       </c>
       <c r="DE3" s="6">
+        <v>8</v>
+      </c>
+      <c r="DF3" s="6">
+        <v>64</v>
+      </c>
+      <c r="DG3" s="6">
+        <v>86</v>
+      </c>
+      <c r="DH3" s="6">
+        <v>56</v>
+      </c>
+      <c r="DI3" s="6">
+        <v>70</v>
+      </c>
+      <c r="DJ3" s="6">
+        <v>19</v>
+      </c>
+      <c r="DK3" s="6">
+        <v>64</v>
+      </c>
+      <c r="DL3" s="6">
+        <v>83</v>
+      </c>
+      <c r="DM3" s="6">
+        <v>51</v>
+      </c>
+      <c r="DN3" s="6">
+        <v>68</v>
+      </c>
+      <c r="DO3" s="6">
+        <v>56</v>
+      </c>
+      <c r="DP3" s="6">
+        <v>95</v>
+      </c>
+      <c r="DQ3" s="6">
+        <v>55</v>
+      </c>
+      <c r="DR3" s="6">
+        <v>49</v>
+      </c>
+      <c r="DS3" s="6">
+        <v>54</v>
+      </c>
+      <c r="DT3" s="6">
+        <v>50</v>
+      </c>
+      <c r="DU3" s="6">
+        <v>46</v>
+      </c>
+      <c r="DV3" s="6">
+        <v>74</v>
+      </c>
+      <c r="DW3" s="6">
+        <v>45</v>
+      </c>
+      <c r="DX3" s="6">
+        <v>40</v>
+      </c>
+      <c r="DY3" s="6">
+        <v>40</v>
+      </c>
+      <c r="DZ3" s="6">
+        <v>64</v>
+      </c>
+      <c r="EA3" s="6">
+        <v>34</v>
+      </c>
+      <c r="EB3" s="6">
+        <v>35</v>
+      </c>
+      <c r="EC3" s="6">
+        <v>56</v>
+      </c>
+      <c r="ED3" s="6">
         <v>62</v>
       </c>
-      <c r="DF3" s="6">
+      <c r="EE3" s="6">
         <v>16</v>
       </c>
-      <c r="DG3" s="6">
+      <c r="EF3" s="6">
         <v>27</v>
       </c>
-      <c r="DH3" s="6">
+      <c r="EG3" s="6">
         <v>31</v>
       </c>
-      <c r="DI3" s="6">
+      <c r="EH3" s="6">
         <v>41</v>
       </c>
+      <c r="EI3" s="6">
+        <v>18</v>
+      </c>
+      <c r="EJ3" s="6">
+        <v>8</v>
+      </c>
+      <c r="EK3" s="6">
+        <v>29</v>
+      </c>
+      <c r="EL3" s="6">
+        <v>1</v>
+      </c>
+      <c r="EM3" s="6">
+        <v>5</v>
+      </c>
+      <c r="EN3" s="6">
+        <v>43</v>
+      </c>
+      <c r="EO3" s="6">
+        <v>45</v>
+      </c>
+      <c r="EP3" s="6">
+        <v>43</v>
+      </c>
+      <c r="EQ3" s="6">
+        <v>52</v>
+      </c>
+      <c r="ER3" s="6">
+        <v>48</v>
+      </c>
+      <c r="ES3" s="6">
+        <v>41</v>
+      </c>
+      <c r="ET3" s="6">
+        <v>48</v>
+      </c>
+      <c r="EU3" s="6">
+        <v>62</v>
+      </c>
+      <c r="EV3" s="6">
+        <v>30</v>
+      </c>
     </row>
-    <row r="4" spans="1:113" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:153" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>81</v>
       </c>
@@ -2543,110 +2936,227 @@
       <c r="CA4">
         <v>85</v>
       </c>
-      <c r="CB4" s="6">
+      <c r="CB4" s="1">
+        <v>79</v>
+      </c>
+      <c r="CC4" s="1">
+        <v>98</v>
+      </c>
+      <c r="CD4" s="1">
+        <v>85</v>
+      </c>
+      <c r="CE4" s="1">
+        <v>73</v>
+      </c>
+      <c r="CF4" s="1">
+        <v>112</v>
+      </c>
+      <c r="CG4" s="1">
+        <v>100</v>
+      </c>
+      <c r="CH4" s="1">
+        <v>101</v>
+      </c>
+      <c r="CI4" s="1">
+        <v>75</v>
+      </c>
+      <c r="CJ4" s="1">
+        <v>117</v>
+      </c>
+      <c r="CK4" s="1">
+        <v>105</v>
+      </c>
+      <c r="CL4" s="1">
+        <v>116</v>
+      </c>
+      <c r="CM4" s="1">
+        <v>58</v>
+      </c>
+      <c r="CN4" s="1">
+        <v>110</v>
+      </c>
+      <c r="CO4" s="1">
+        <v>93</v>
+      </c>
+      <c r="CP4" s="1">
+        <v>74</v>
+      </c>
+      <c r="CQ4" s="1">
+        <v>139</v>
+      </c>
+      <c r="CR4" s="1">
+        <v>105</v>
+      </c>
+      <c r="CS4" s="1">
+        <v>112</v>
+      </c>
+      <c r="CT4" s="1">
+        <v>23</v>
+      </c>
+      <c r="CU4" s="1">
+        <v>104</v>
+      </c>
+      <c r="CV4" s="1">
+        <v>45</v>
+      </c>
+      <c r="CW4" s="1">
+        <v>35</v>
+      </c>
+      <c r="CX4" s="1">
+        <v>40</v>
+      </c>
+      <c r="CY4" s="1">
+        <v>35</v>
+      </c>
+      <c r="CZ4" s="1">
+        <v>30</v>
+      </c>
+      <c r="DA4" s="1">
         <v>50</v>
       </c>
-      <c r="CC4" s="6">
+      <c r="DB4" s="1">
         <v>62</v>
       </c>
-      <c r="CD4" s="6">
+      <c r="DC4" s="1">
         <v>56</v>
       </c>
-      <c r="CE4" s="6">
+      <c r="DD4" s="1">
         <v>56</v>
       </c>
-      <c r="CF4" s="6">
+      <c r="DE4" s="1">
         <v>8</v>
       </c>
-      <c r="CG4" s="6">
+      <c r="DF4" s="1">
         <v>64</v>
       </c>
-      <c r="CH4" s="6">
+      <c r="DG4" s="1">
         <v>86</v>
       </c>
-      <c r="CI4" s="6">
+      <c r="DH4" s="1">
         <v>56</v>
       </c>
-      <c r="CJ4" s="6">
+      <c r="DI4" s="1">
         <v>70</v>
       </c>
-      <c r="CK4" s="6">
+      <c r="DJ4" s="1">
         <v>19</v>
       </c>
-      <c r="CL4" s="6">
+      <c r="DK4" s="1">
         <v>64</v>
       </c>
-      <c r="CM4" s="6">
+      <c r="DL4" s="1">
         <v>83</v>
       </c>
-      <c r="CN4" s="6">
+      <c r="DM4" s="1">
         <v>51</v>
       </c>
-      <c r="CO4" s="6">
+      <c r="DN4" s="1">
         <v>68</v>
       </c>
-      <c r="CP4" s="6">
+      <c r="DO4" s="1">
         <v>56</v>
       </c>
-      <c r="CQ4" s="6">
+      <c r="DP4" s="1">
         <v>95</v>
       </c>
-      <c r="CR4" s="6">
+      <c r="DQ4" s="1">
         <v>55</v>
       </c>
-      <c r="CS4" s="6">
+      <c r="DR4" s="1">
         <v>49</v>
       </c>
-      <c r="CT4" s="6">
+      <c r="DS4" s="1">
         <v>54</v>
       </c>
-      <c r="CU4" s="6">
+      <c r="DT4" s="1">
         <v>50</v>
       </c>
-      <c r="CV4" s="6">
+      <c r="DU4" s="1">
         <v>46</v>
       </c>
-      <c r="CW4" s="6">
+      <c r="DV4" s="1">
         <v>74</v>
       </c>
-      <c r="CX4" s="6">
+      <c r="DW4" s="1">
         <v>45</v>
       </c>
-      <c r="CY4" s="6">
+      <c r="DX4" s="1">
         <v>40</v>
       </c>
-      <c r="CZ4" s="6">
+      <c r="DY4" s="1">
         <v>40</v>
       </c>
-      <c r="DA4" s="6">
+      <c r="DZ4" s="1">
         <v>64</v>
       </c>
-      <c r="DB4" s="6">
+      <c r="EA4" s="1">
         <v>34</v>
       </c>
-      <c r="DC4" s="6">
+      <c r="EB4" s="1">
         <v>35</v>
       </c>
-      <c r="DD4" s="6">
+      <c r="EC4" s="1">
         <v>56</v>
       </c>
-      <c r="DE4" s="6">
+      <c r="ED4" s="1">
         <v>62</v>
       </c>
-      <c r="DF4" s="6">
+      <c r="EE4" s="1">
         <v>16</v>
       </c>
-      <c r="DG4" s="6">
+      <c r="EF4" s="1">
         <v>27</v>
       </c>
-      <c r="DH4" s="6">
+      <c r="EG4" s="1">
         <v>31</v>
       </c>
-      <c r="DI4" s="6">
+      <c r="EH4" s="1">
         <v>41</v>
       </c>
+      <c r="EI4" s="1">
+        <v>18</v>
+      </c>
+      <c r="EJ4" s="1">
+        <v>8</v>
+      </c>
+      <c r="EK4" s="1">
+        <v>29</v>
+      </c>
+      <c r="EL4" s="1">
+        <v>1</v>
+      </c>
+      <c r="EM4" s="1">
+        <v>5</v>
+      </c>
+      <c r="EN4" s="1">
+        <v>43</v>
+      </c>
+      <c r="EO4" s="1">
+        <v>45</v>
+      </c>
+      <c r="EP4" s="1">
+        <v>43</v>
+      </c>
+      <c r="EQ4" s="1">
+        <v>52</v>
+      </c>
+      <c r="ER4" s="1">
+        <v>48</v>
+      </c>
+      <c r="ES4" s="1">
+        <v>41</v>
+      </c>
+      <c r="ET4" s="1">
+        <v>48</v>
+      </c>
+      <c r="EU4" s="1">
+        <v>62</v>
+      </c>
+      <c r="EV4" s="1">
+        <v>29</v>
+      </c>
     </row>
-    <row r="5" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:153" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>82</v>
       </c>
@@ -2986,8 +3496,125 @@
       <c r="DI5">
         <v>100</v>
       </c>
+      <c r="DJ5">
+        <v>100</v>
+      </c>
+      <c r="DK5">
+        <v>100</v>
+      </c>
+      <c r="DL5">
+        <v>100</v>
+      </c>
+      <c r="DM5">
+        <v>100</v>
+      </c>
+      <c r="DN5">
+        <v>100</v>
+      </c>
+      <c r="DO5">
+        <v>100</v>
+      </c>
+      <c r="DP5">
+        <v>100</v>
+      </c>
+      <c r="DQ5">
+        <v>100</v>
+      </c>
+      <c r="DR5">
+        <v>100</v>
+      </c>
+      <c r="DS5">
+        <v>100</v>
+      </c>
+      <c r="DT5">
+        <v>100</v>
+      </c>
+      <c r="DU5">
+        <v>100</v>
+      </c>
+      <c r="DV5">
+        <v>100</v>
+      </c>
+      <c r="DW5">
+        <v>100</v>
+      </c>
+      <c r="DX5">
+        <v>100</v>
+      </c>
+      <c r="DY5">
+        <v>100</v>
+      </c>
+      <c r="DZ5">
+        <v>100</v>
+      </c>
+      <c r="EA5">
+        <v>100</v>
+      </c>
+      <c r="EB5">
+        <v>100</v>
+      </c>
+      <c r="EC5">
+        <v>100</v>
+      </c>
+      <c r="ED5">
+        <v>100</v>
+      </c>
+      <c r="EE5">
+        <v>100</v>
+      </c>
+      <c r="EF5">
+        <v>100</v>
+      </c>
+      <c r="EG5">
+        <v>100</v>
+      </c>
+      <c r="EH5">
+        <v>100</v>
+      </c>
+      <c r="EI5">
+        <v>100</v>
+      </c>
+      <c r="EJ5">
+        <v>100</v>
+      </c>
+      <c r="EK5">
+        <v>100</v>
+      </c>
+      <c r="EL5">
+        <v>100</v>
+      </c>
+      <c r="EM5">
+        <v>100</v>
+      </c>
+      <c r="EN5">
+        <v>100</v>
+      </c>
+      <c r="EO5">
+        <v>100</v>
+      </c>
+      <c r="EP5">
+        <v>100</v>
+      </c>
+      <c r="EQ5">
+        <v>100</v>
+      </c>
+      <c r="ER5">
+        <v>100</v>
+      </c>
+      <c r="ES5">
+        <v>100</v>
+      </c>
+      <c r="ET5">
+        <v>100</v>
+      </c>
+      <c r="EU5">
+        <v>100</v>
+      </c>
+      <c r="EV5">
+        <v>96.67</v>
+      </c>
     </row>
-    <row r="6" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:153" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>83</v>
       </c>
@@ -3226,107 +3853,226 @@
         <v>85</v>
       </c>
       <c r="CB6" s="1">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="CC6" s="1">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="CD6" s="1">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="CE6" s="1">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="CF6" s="1">
-        <v>8</v>
+        <v>112</v>
       </c>
       <c r="CG6" s="1">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="CH6" s="1">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="CI6" s="1">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="CJ6" s="1">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="CK6" s="1">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="CL6" s="1">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="CM6" s="1">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="CN6" s="1">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="CO6" s="1">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="CP6" s="1">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="CQ6" s="1">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="CR6" s="1">
-        <v>55</v>
+        <v>105</v>
       </c>
       <c r="CS6" s="1">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="CT6" s="1">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="CU6" s="1">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="CV6" s="1">
         <v>45</v>
       </c>
       <c r="CW6" s="1">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="CX6" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="CY6" s="1">
         <v>35</v>
       </c>
       <c r="CZ6" s="1">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="DA6" s="1">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="DB6" s="1">
-        <v>34</v>
-      </c>
-      <c r="DC6" s="7">
-        <v>0</v>
+        <v>62</v>
+      </c>
+      <c r="DC6" s="1">
+        <v>56</v>
       </c>
       <c r="DD6" s="1">
         <v>56</v>
       </c>
       <c r="DE6" s="1">
+        <v>8</v>
+      </c>
+      <c r="DF6" s="1">
+        <v>64</v>
+      </c>
+      <c r="DG6" s="1">
+        <v>86</v>
+      </c>
+      <c r="DH6" s="1">
+        <v>56</v>
+      </c>
+      <c r="DI6" s="1">
+        <v>70</v>
+      </c>
+      <c r="DJ6" s="1">
+        <v>19</v>
+      </c>
+      <c r="DK6" s="1">
+        <v>64</v>
+      </c>
+      <c r="DL6" s="1">
+        <v>83</v>
+      </c>
+      <c r="DM6" s="1">
+        <v>51</v>
+      </c>
+      <c r="DN6" s="1">
+        <v>68</v>
+      </c>
+      <c r="DO6" s="1">
+        <v>56</v>
+      </c>
+      <c r="DP6" s="1">
+        <v>95</v>
+      </c>
+      <c r="DQ6" s="1">
+        <v>55</v>
+      </c>
+      <c r="DR6" s="1">
+        <v>49</v>
+      </c>
+      <c r="DS6" s="1">
+        <v>54</v>
+      </c>
+      <c r="DT6" s="1">
+        <v>50</v>
+      </c>
+      <c r="DU6" s="1">
+        <v>46</v>
+      </c>
+      <c r="DV6" s="1">
+        <v>74</v>
+      </c>
+      <c r="DW6" s="1">
+        <v>45</v>
+      </c>
+      <c r="DX6" s="1">
+        <v>40</v>
+      </c>
+      <c r="DY6" s="1">
+        <v>40</v>
+      </c>
+      <c r="DZ6" s="1">
+        <v>64</v>
+      </c>
+      <c r="EA6" s="1">
+        <v>34</v>
+      </c>
+      <c r="EB6" s="1">
+        <v>35</v>
+      </c>
+      <c r="EC6" s="1">
+        <v>56</v>
+      </c>
+      <c r="ED6" s="1">
         <v>62</v>
       </c>
-      <c r="DF6" s="7">
-        <v>0</v>
-      </c>
-      <c r="DG6" s="7">
-        <v>0</v>
-      </c>
-      <c r="DH6" s="1">
+      <c r="EE6" s="1">
+        <v>16</v>
+      </c>
+      <c r="EF6" s="1">
+        <v>27</v>
+      </c>
+      <c r="EG6" s="1">
         <v>31</v>
       </c>
-      <c r="DI6" s="7"/>
+      <c r="EH6" s="1">
+        <v>41</v>
+      </c>
+      <c r="EI6" s="1">
+        <v>18</v>
+      </c>
+      <c r="EJ6" s="1">
+        <v>8</v>
+      </c>
+      <c r="EK6" s="1">
+        <v>29</v>
+      </c>
+      <c r="EL6" s="1">
+        <v>1</v>
+      </c>
+      <c r="EM6" s="1">
+        <v>5</v>
+      </c>
+      <c r="EN6" s="1">
+        <v>43</v>
+      </c>
+      <c r="EO6" s="1">
+        <v>45</v>
+      </c>
+      <c r="EP6" s="1">
+        <v>43</v>
+      </c>
+      <c r="EQ6" s="1">
+        <v>52</v>
+      </c>
+      <c r="ER6" s="1">
+        <v>48</v>
+      </c>
+      <c r="ES6" s="1">
+        <v>41</v>
+      </c>
+      <c r="ET6" s="1">
+        <v>48</v>
+      </c>
+      <c r="EU6" s="1">
+        <v>62</v>
+      </c>
+      <c r="EV6" s="1">
+        <v>29</v>
+      </c>
     </row>
-    <row r="7" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:153" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>84</v>
       </c>
@@ -3604,13 +4350,13 @@
         <v>0</v>
       </c>
       <c r="CO7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CP7">
         <v>0</v>
       </c>
       <c r="CQ7">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="CR7">
         <v>0</v>
@@ -3618,56 +4364,173 @@
       <c r="CS7">
         <v>0</v>
       </c>
-      <c r="CT7" s="1">
-        <v>1</v>
-      </c>
-      <c r="CU7" s="1">
-        <v>14</v>
-      </c>
-      <c r="CV7" s="1">
-        <v>1</v>
-      </c>
-      <c r="CW7" s="7">
-        <v>0</v>
-      </c>
-      <c r="CX7" s="7">
-        <v>0</v>
-      </c>
-      <c r="CY7" s="1">
-        <v>5</v>
-      </c>
-      <c r="CZ7" s="7">
-        <v>0</v>
-      </c>
-      <c r="DA7" s="1">
-        <v>3</v>
-      </c>
-      <c r="DB7" s="7">
-        <v>0</v>
-      </c>
-      <c r="DC7" s="1">
-        <v>35</v>
-      </c>
-      <c r="DD7" s="7">
-        <v>0</v>
-      </c>
-      <c r="DE7" s="7">
-        <v>0</v>
-      </c>
-      <c r="DF7" s="1">
-        <v>16</v>
-      </c>
-      <c r="DG7" s="1">
-        <v>27</v>
-      </c>
-      <c r="DH7" s="7">
-        <v>0</v>
-      </c>
-      <c r="DI7" s="1">
-        <v>41</v>
+      <c r="CT7">
+        <v>0</v>
+      </c>
+      <c r="CU7">
+        <v>0</v>
+      </c>
+      <c r="CV7">
+        <v>0</v>
+      </c>
+      <c r="CW7">
+        <v>0</v>
+      </c>
+      <c r="CX7">
+        <v>0</v>
+      </c>
+      <c r="CY7">
+        <v>0</v>
+      </c>
+      <c r="CZ7">
+        <v>0</v>
+      </c>
+      <c r="DA7">
+        <v>0</v>
+      </c>
+      <c r="DB7">
+        <v>0</v>
+      </c>
+      <c r="DC7">
+        <v>0</v>
+      </c>
+      <c r="DD7">
+        <v>0</v>
+      </c>
+      <c r="DE7">
+        <v>0</v>
+      </c>
+      <c r="DF7">
+        <v>0</v>
+      </c>
+      <c r="DG7">
+        <v>0</v>
+      </c>
+      <c r="DH7">
+        <v>0</v>
+      </c>
+      <c r="DI7">
+        <v>0</v>
+      </c>
+      <c r="DJ7">
+        <v>0</v>
+      </c>
+      <c r="DK7">
+        <v>0</v>
+      </c>
+      <c r="DL7">
+        <v>0</v>
+      </c>
+      <c r="DM7">
+        <v>0</v>
+      </c>
+      <c r="DN7">
+        <v>0</v>
+      </c>
+      <c r="DO7">
+        <v>0</v>
+      </c>
+      <c r="DP7">
+        <v>0</v>
+      </c>
+      <c r="DQ7">
+        <v>0</v>
+      </c>
+      <c r="DR7">
+        <v>0</v>
+      </c>
+      <c r="DS7">
+        <v>0</v>
+      </c>
+      <c r="DT7">
+        <v>0</v>
+      </c>
+      <c r="DU7">
+        <v>0</v>
+      </c>
+      <c r="DV7">
+        <v>0</v>
+      </c>
+      <c r="DW7">
+        <v>0</v>
+      </c>
+      <c r="DX7">
+        <v>0</v>
+      </c>
+      <c r="DY7">
+        <v>0</v>
+      </c>
+      <c r="DZ7">
+        <v>0</v>
+      </c>
+      <c r="EA7">
+        <v>0</v>
+      </c>
+      <c r="EB7">
+        <v>0</v>
+      </c>
+      <c r="EC7">
+        <v>0</v>
+      </c>
+      <c r="ED7">
+        <v>0</v>
+      </c>
+      <c r="EE7">
+        <v>0</v>
+      </c>
+      <c r="EF7">
+        <v>0</v>
+      </c>
+      <c r="EG7">
+        <v>0</v>
+      </c>
+      <c r="EH7">
+        <v>0</v>
+      </c>
+      <c r="EI7">
+        <v>0</v>
+      </c>
+      <c r="EJ7">
+        <v>0</v>
+      </c>
+      <c r="EK7">
+        <v>0</v>
+      </c>
+      <c r="EL7">
+        <v>0</v>
+      </c>
+      <c r="EM7">
+        <v>0</v>
+      </c>
+      <c r="EN7">
+        <v>0</v>
+      </c>
+      <c r="EO7">
+        <v>0</v>
+      </c>
+      <c r="EP7">
+        <v>0</v>
+      </c>
+      <c r="EQ7">
+        <v>0</v>
+      </c>
+      <c r="ER7">
+        <v>0</v>
+      </c>
+      <c r="ES7">
+        <v>0</v>
+      </c>
+      <c r="ET7">
+        <v>0</v>
+      </c>
+      <c r="EU7">
+        <v>0</v>
+      </c>
+      <c r="EV7">
+        <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:153" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -3959,8 +4822,8 @@
       <c r="CS8">
         <v>0</v>
       </c>
-      <c r="CT8" s="1">
-        <v>5</v>
+      <c r="CT8">
+        <v>0</v>
       </c>
       <c r="CU8">
         <v>0</v>
@@ -4007,8 +4870,125 @@
       <c r="DI8">
         <v>0</v>
       </c>
+      <c r="DJ8">
+        <v>0</v>
+      </c>
+      <c r="DK8">
+        <v>0</v>
+      </c>
+      <c r="DL8">
+        <v>0</v>
+      </c>
+      <c r="DM8">
+        <v>0</v>
+      </c>
+      <c r="DN8">
+        <v>0</v>
+      </c>
+      <c r="DO8">
+        <v>0</v>
+      </c>
+      <c r="DP8">
+        <v>0</v>
+      </c>
+      <c r="DQ8">
+        <v>0</v>
+      </c>
+      <c r="DR8">
+        <v>0</v>
+      </c>
+      <c r="DS8">
+        <v>0</v>
+      </c>
+      <c r="DT8">
+        <v>0</v>
+      </c>
+      <c r="DU8">
+        <v>0</v>
+      </c>
+      <c r="DV8">
+        <v>0</v>
+      </c>
+      <c r="DW8">
+        <v>0</v>
+      </c>
+      <c r="DX8">
+        <v>0</v>
+      </c>
+      <c r="DY8">
+        <v>0</v>
+      </c>
+      <c r="DZ8">
+        <v>0</v>
+      </c>
+      <c r="EA8">
+        <v>0</v>
+      </c>
+      <c r="EB8">
+        <v>0</v>
+      </c>
+      <c r="EC8">
+        <v>0</v>
+      </c>
+      <c r="ED8">
+        <v>0</v>
+      </c>
+      <c r="EE8">
+        <v>0</v>
+      </c>
+      <c r="EF8">
+        <v>0</v>
+      </c>
+      <c r="EG8">
+        <v>0</v>
+      </c>
+      <c r="EH8">
+        <v>0</v>
+      </c>
+      <c r="EI8">
+        <v>0</v>
+      </c>
+      <c r="EJ8">
+        <v>0</v>
+      </c>
+      <c r="EK8">
+        <v>0</v>
+      </c>
+      <c r="EL8">
+        <v>0</v>
+      </c>
+      <c r="EM8">
+        <v>0</v>
+      </c>
+      <c r="EN8">
+        <v>0</v>
+      </c>
+      <c r="EO8">
+        <v>0</v>
+      </c>
+      <c r="EP8">
+        <v>0</v>
+      </c>
+      <c r="EQ8">
+        <v>0</v>
+      </c>
+      <c r="ER8">
+        <v>0</v>
+      </c>
+      <c r="ES8">
+        <v>0</v>
+      </c>
+      <c r="ET8">
+        <v>0</v>
+      </c>
+      <c r="EU8">
+        <v>0</v>
+      </c>
+      <c r="EV8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:113" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:153" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>86</v>
       </c>
@@ -4348,8 +5328,125 @@
       <c r="DI9">
         <v>0</v>
       </c>
+      <c r="DJ9">
+        <v>0</v>
+      </c>
+      <c r="DK9">
+        <v>0</v>
+      </c>
+      <c r="DL9">
+        <v>0</v>
+      </c>
+      <c r="DM9">
+        <v>0</v>
+      </c>
+      <c r="DN9">
+        <v>0</v>
+      </c>
+      <c r="DO9">
+        <v>0</v>
+      </c>
+      <c r="DP9">
+        <v>0</v>
+      </c>
+      <c r="DQ9">
+        <v>0</v>
+      </c>
+      <c r="DR9">
+        <v>0</v>
+      </c>
+      <c r="DS9">
+        <v>0</v>
+      </c>
+      <c r="DT9">
+        <v>0</v>
+      </c>
+      <c r="DU9">
+        <v>0</v>
+      </c>
+      <c r="DV9">
+        <v>0</v>
+      </c>
+      <c r="DW9">
+        <v>0</v>
+      </c>
+      <c r="DX9">
+        <v>0</v>
+      </c>
+      <c r="DY9">
+        <v>0</v>
+      </c>
+      <c r="DZ9">
+        <v>0</v>
+      </c>
+      <c r="EA9">
+        <v>0</v>
+      </c>
+      <c r="EB9">
+        <v>0</v>
+      </c>
+      <c r="EC9">
+        <v>0</v>
+      </c>
+      <c r="ED9">
+        <v>0</v>
+      </c>
+      <c r="EE9">
+        <v>0</v>
+      </c>
+      <c r="EF9">
+        <v>0</v>
+      </c>
+      <c r="EG9">
+        <v>0</v>
+      </c>
+      <c r="EH9">
+        <v>0</v>
+      </c>
+      <c r="EI9">
+        <v>0</v>
+      </c>
+      <c r="EJ9">
+        <v>0</v>
+      </c>
+      <c r="EK9">
+        <v>0</v>
+      </c>
+      <c r="EL9">
+        <v>0</v>
+      </c>
+      <c r="EM9">
+        <v>0</v>
+      </c>
+      <c r="EN9">
+        <v>0</v>
+      </c>
+      <c r="EO9">
+        <v>0</v>
+      </c>
+      <c r="EP9">
+        <v>0</v>
+      </c>
+      <c r="EQ9">
+        <v>0</v>
+      </c>
+      <c r="ER9">
+        <v>0</v>
+      </c>
+      <c r="ES9">
+        <v>0</v>
+      </c>
+      <c r="ET9">
+        <v>0</v>
+      </c>
+      <c r="EU9">
+        <v>0</v>
+      </c>
+      <c r="EV9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:113" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:153" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>87</v>
       </c>
@@ -4588,109 +5685,224 @@
         <v>28</v>
       </c>
       <c r="CB10" s="6">
+        <v>32</v>
+      </c>
+      <c r="CC10" s="6">
+        <v>13</v>
+      </c>
+      <c r="CD10" s="6">
+        <v>32</v>
+      </c>
+      <c r="CE10" s="6">
+        <v>29</v>
+      </c>
+      <c r="CF10" s="6">
+        <v>22</v>
+      </c>
+      <c r="CG10" s="6">
+        <v>21</v>
+      </c>
+      <c r="CH10" s="6">
+        <v>20</v>
+      </c>
+      <c r="CI10" s="6">
+        <v>30</v>
+      </c>
+      <c r="CJ10" s="6">
+        <v>14</v>
+      </c>
+      <c r="CK10" s="6">
+        <v>27</v>
+      </c>
+      <c r="CL10" s="6">
         <v>10</v>
       </c>
-      <c r="CC10" s="6">
-        <v>31</v>
-      </c>
-      <c r="CD10" s="6">
-        <v>3</v>
-      </c>
-      <c r="CE10" s="6">
-        <v>20</v>
-      </c>
-      <c r="CF10" s="6">
-        <v>31</v>
-      </c>
-      <c r="CG10" s="6">
-        <v>44</v>
-      </c>
-      <c r="CH10" s="6">
-        <v>39</v>
-      </c>
-      <c r="CI10" s="6">
+      <c r="CM10" s="6">
         <v>25</v>
       </c>
-      <c r="CJ10" s="6">
-        <v>24</v>
-      </c>
-      <c r="CK10" s="6">
-        <v>38</v>
-      </c>
-      <c r="CL10" s="6">
-        <v>14</v>
-      </c>
-      <c r="CM10" s="6">
-        <v>24</v>
-      </c>
       <c r="CN10" s="6">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="CO10" s="6">
         <v>19</v>
       </c>
       <c r="CP10" s="6">
+        <v>31</v>
+      </c>
+      <c r="CQ10" s="6">
+        <v>15</v>
+      </c>
+      <c r="CR10" s="6">
+        <v>33</v>
+      </c>
+      <c r="CS10" s="6">
         <v>29</v>
       </c>
-      <c r="CQ10" s="6">
-        <v>25</v>
-      </c>
-      <c r="CR10" s="6">
-        <v>27</v>
-      </c>
-      <c r="CS10" s="6">
-        <v>32</v>
-      </c>
       <c r="CT10" s="6">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="CU10" s="6">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="CV10" s="6">
         <v>26</v>
       </c>
       <c r="CW10" s="6">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="CX10" s="6">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="CY10" s="6">
+        <v>57</v>
+      </c>
+      <c r="CZ10" s="6">
         <v>31</v>
       </c>
-      <c r="CZ10" s="6">
-        <v>39</v>
-      </c>
       <c r="DA10" s="6">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="DB10" s="6">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="DC10" s="6">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="DD10" s="6">
         <v>20</v>
       </c>
       <c r="DE10" s="6">
+        <v>31</v>
+      </c>
+      <c r="DF10" s="6">
+        <v>44</v>
+      </c>
+      <c r="DG10" s="6">
+        <v>39</v>
+      </c>
+      <c r="DH10" s="6">
+        <v>25</v>
+      </c>
+      <c r="DI10" s="6">
+        <v>24</v>
+      </c>
+      <c r="DJ10" s="6">
+        <v>38</v>
+      </c>
+      <c r="DK10" s="6">
+        <v>14</v>
+      </c>
+      <c r="DL10" s="6">
+        <v>24</v>
+      </c>
+      <c r="DM10" s="6">
+        <v>40</v>
+      </c>
+      <c r="DN10" s="6">
+        <v>19</v>
+      </c>
+      <c r="DO10" s="6">
+        <v>29</v>
+      </c>
+      <c r="DP10" s="6">
+        <v>25</v>
+      </c>
+      <c r="DQ10" s="6">
+        <v>27</v>
+      </c>
+      <c r="DR10" s="6">
+        <v>32</v>
+      </c>
+      <c r="DS10" s="6">
+        <v>24</v>
+      </c>
+      <c r="DT10" s="6">
+        <v>19</v>
+      </c>
+      <c r="DU10" s="6">
+        <v>26</v>
+      </c>
+      <c r="DV10" s="6">
+        <v>5</v>
+      </c>
+      <c r="DW10" s="6">
+        <v>40</v>
+      </c>
+      <c r="DX10" s="6">
+        <v>31</v>
+      </c>
+      <c r="DY10" s="6">
+        <v>39</v>
+      </c>
+      <c r="DZ10" s="6">
+        <v>24</v>
+      </c>
+      <c r="EA10" s="6">
+        <v>14</v>
+      </c>
+      <c r="EB10" s="6">
+        <v>23</v>
+      </c>
+      <c r="EC10" s="6">
+        <v>20</v>
+      </c>
+      <c r="ED10" s="6">
         <v>35</v>
       </c>
-      <c r="DF10" s="6">
+      <c r="EE10" s="6">
         <v>11</v>
       </c>
-      <c r="DG10" s="6">
+      <c r="EF10" s="6">
         <v>31</v>
       </c>
-      <c r="DH10" s="6">
+      <c r="EG10" s="6">
         <v>18</v>
       </c>
-      <c r="DI10" s="6">
+      <c r="EH10" s="6">
         <v>29</v>
       </c>
+      <c r="EI10" s="6">
+        <v>19</v>
+      </c>
+      <c r="EJ10" s="6">
+        <v>1</v>
+      </c>
+      <c r="EK10" s="6">
+        <v>34</v>
+      </c>
+      <c r="EL10" s="6">
+        <v>24</v>
+      </c>
+      <c r="EM10" s="6">
+        <v>14</v>
+      </c>
+      <c r="EN10" s="6">
+        <v>20</v>
+      </c>
+      <c r="EO10" s="6">
+        <v>19</v>
+      </c>
+      <c r="EP10" s="6">
+        <v>24</v>
+      </c>
+      <c r="EQ10" s="6">
+        <v>29</v>
+      </c>
+      <c r="ER10" s="6">
+        <v>20</v>
+      </c>
+      <c r="ES10" s="6">
+        <v>39</v>
+      </c>
+      <c r="ET10" s="6">
+        <v>68</v>
+      </c>
+      <c r="EU10" s="6">
+        <v>20</v>
+      </c>
+      <c r="EV10" s="6"/>
     </row>
-    <row r="11" spans="1:113" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:153" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>88</v>
       </c>
@@ -4929,109 +6141,223 @@
         <v>28</v>
       </c>
       <c r="CB11" s="6">
+        <v>28</v>
+      </c>
+      <c r="CC11" s="6">
+        <v>10</v>
+      </c>
+      <c r="CD11" s="6">
+        <v>18</v>
+      </c>
+      <c r="CE11" s="6">
+        <v>19</v>
+      </c>
+      <c r="CF11" s="6">
+        <v>16</v>
+      </c>
+      <c r="CG11" s="6">
+        <v>18</v>
+      </c>
+      <c r="CH11" s="6">
+        <v>16</v>
+      </c>
+      <c r="CI11" s="6">
+        <v>28</v>
+      </c>
+      <c r="CJ11" s="6">
+        <v>12</v>
+      </c>
+      <c r="CK11" s="6">
+        <v>10</v>
+      </c>
+      <c r="CL11" s="6">
+        <v>10</v>
+      </c>
+      <c r="CM11" s="6">
+        <v>25</v>
+      </c>
+      <c r="CN11" s="6">
+        <v>24</v>
+      </c>
+      <c r="CO11" s="6">
+        <v>15</v>
+      </c>
+      <c r="CP11" s="6">
+        <v>28</v>
+      </c>
+      <c r="CQ11" s="6">
+        <v>11</v>
+      </c>
+      <c r="CR11" s="6">
+        <v>16</v>
+      </c>
+      <c r="CS11" s="6">
+        <v>24</v>
+      </c>
+      <c r="CT11" s="6">
         <v>9</v>
       </c>
-      <c r="CC11" s="6">
+      <c r="CU11" s="6">
+        <v>28</v>
+      </c>
+      <c r="CV11" s="6">
+        <v>9</v>
+      </c>
+      <c r="CW11" s="6">
+        <v>25</v>
+      </c>
+      <c r="CX11" s="6">
+        <v>15</v>
+      </c>
+      <c r="CY11" s="6">
+        <v>41</v>
+      </c>
+      <c r="CZ11" s="6">
+        <v>24</v>
+      </c>
+      <c r="DA11" s="6">
+        <v>9</v>
+      </c>
+      <c r="DB11" s="6">
         <v>13</v>
       </c>
-      <c r="CD11" s="6">
+      <c r="DC11" s="6">
         <v>1</v>
       </c>
-      <c r="CE11" s="6">
+      <c r="DD11" s="6">
         <v>14</v>
       </c>
-      <c r="CF11" s="6">
+      <c r="DE11" s="6">
         <v>21</v>
       </c>
-      <c r="CG11" s="6">
+      <c r="DF11" s="6">
         <v>22</v>
-      </c>
-      <c r="CH11" s="6">
-        <v>31</v>
-      </c>
-      <c r="CI11" s="6">
-        <v>15</v>
-      </c>
-      <c r="CJ11" s="6">
-        <v>4</v>
-      </c>
-      <c r="CK11" s="6">
-        <v>35</v>
-      </c>
-      <c r="CL11" s="6">
-        <v>14</v>
-      </c>
-      <c r="CM11" s="6">
-        <v>17</v>
-      </c>
-      <c r="CN11" s="6">
-        <v>31</v>
-      </c>
-      <c r="CO11" s="6">
-        <v>11</v>
-      </c>
-      <c r="CP11" s="6">
-        <v>24</v>
-      </c>
-      <c r="CQ11" s="6">
-        <v>16</v>
-      </c>
-      <c r="CR11" s="6">
-        <v>10</v>
-      </c>
-      <c r="CS11" s="6">
-        <v>26</v>
-      </c>
-      <c r="CT11" s="6">
-        <v>18</v>
-      </c>
-      <c r="CU11" s="6">
-        <v>12</v>
-      </c>
-      <c r="CV11" s="6">
-        <v>18</v>
-      </c>
-      <c r="CW11" s="6">
-        <v>4</v>
-      </c>
-      <c r="CX11" s="6">
-        <v>35</v>
-      </c>
-      <c r="CY11" s="6">
-        <v>29</v>
-      </c>
-      <c r="CZ11" s="6">
-        <v>34</v>
-      </c>
-      <c r="DA11" s="6">
-        <v>20</v>
-      </c>
-      <c r="DB11" s="6">
-        <v>11</v>
-      </c>
-      <c r="DC11" s="6">
-        <v>21</v>
-      </c>
-      <c r="DD11" s="6">
-        <v>20</v>
-      </c>
-      <c r="DE11" s="6">
-        <v>35</v>
-      </c>
-      <c r="DF11" s="6">
-        <v>8</v>
       </c>
       <c r="DG11" s="6">
         <v>31</v>
       </c>
       <c r="DH11" s="6">
+        <v>15</v>
+      </c>
+      <c r="DI11" s="6">
+        <v>4</v>
+      </c>
+      <c r="DJ11" s="6">
+        <v>35</v>
+      </c>
+      <c r="DK11" s="6">
+        <v>14</v>
+      </c>
+      <c r="DL11" s="6">
+        <v>17</v>
+      </c>
+      <c r="DM11" s="6">
+        <v>31</v>
+      </c>
+      <c r="DN11" s="6">
+        <v>11</v>
+      </c>
+      <c r="DO11" s="6">
+        <v>24</v>
+      </c>
+      <c r="DP11" s="6">
+        <v>16</v>
+      </c>
+      <c r="DQ11" s="6">
+        <v>10</v>
+      </c>
+      <c r="DR11" s="6">
+        <v>26</v>
+      </c>
+      <c r="DS11" s="6">
+        <v>18</v>
+      </c>
+      <c r="DT11" s="6">
         <v>12</v>
       </c>
-      <c r="DI11" s="6">
+      <c r="DU11" s="6">
+        <v>18</v>
+      </c>
+      <c r="DV11" s="6">
+        <v>4</v>
+      </c>
+      <c r="DW11" s="6">
+        <v>35</v>
+      </c>
+      <c r="DX11" s="6">
         <v>29</v>
       </c>
+      <c r="DY11" s="6">
+        <v>34</v>
+      </c>
+      <c r="DZ11" s="6">
+        <v>20</v>
+      </c>
+      <c r="EA11" s="6">
+        <v>11</v>
+      </c>
+      <c r="EB11" s="6">
+        <v>21</v>
+      </c>
+      <c r="EC11" s="6">
+        <v>20</v>
+      </c>
+      <c r="ED11" s="6">
+        <v>35</v>
+      </c>
+      <c r="EE11" s="6">
+        <v>8</v>
+      </c>
+      <c r="EF11" s="6">
+        <v>31</v>
+      </c>
+      <c r="EG11" s="6">
+        <v>12</v>
+      </c>
+      <c r="EH11" s="6">
+        <v>29</v>
+      </c>
+      <c r="EI11" s="6">
+        <v>18</v>
+      </c>
+      <c r="EJ11" s="6">
+        <v>1</v>
+      </c>
+      <c r="EK11" s="6">
+        <v>28</v>
+      </c>
+      <c r="EL11" s="6">
+        <v>15</v>
+      </c>
+      <c r="EM11" s="6">
+        <v>14</v>
+      </c>
+      <c r="EN11" s="6">
+        <v>20</v>
+      </c>
+      <c r="EO11" s="6">
+        <v>17</v>
+      </c>
+      <c r="EP11" s="6">
+        <v>1</v>
+      </c>
+      <c r="EQ11" s="6">
+        <v>28</v>
+      </c>
+      <c r="ER11" s="6">
+        <v>17</v>
+      </c>
+      <c r="ES11" s="6">
+        <v>20</v>
+      </c>
+      <c r="ET11" s="6">
+        <v>67</v>
+      </c>
+      <c r="EU11" s="6">
+        <v>20</v>
+      </c>
     </row>
-    <row r="12" spans="1:113" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:153" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>89</v>
       </c>
@@ -5269,110 +6595,224 @@
       <c r="CA12">
         <v>28</v>
       </c>
-      <c r="CB12" s="6">
+      <c r="CB12" s="1">
+        <v>28</v>
+      </c>
+      <c r="CC12" s="1">
+        <v>10</v>
+      </c>
+      <c r="CD12" s="1">
+        <v>18</v>
+      </c>
+      <c r="CE12" s="1">
+        <v>19</v>
+      </c>
+      <c r="CF12" s="1">
+        <v>16</v>
+      </c>
+      <c r="CG12" s="1">
+        <v>18</v>
+      </c>
+      <c r="CH12" s="1">
+        <v>16</v>
+      </c>
+      <c r="CI12" s="1">
+        <v>28</v>
+      </c>
+      <c r="CJ12" s="1">
+        <v>12</v>
+      </c>
+      <c r="CK12" s="1">
+        <v>10</v>
+      </c>
+      <c r="CL12" s="1">
+        <v>10</v>
+      </c>
+      <c r="CM12" s="1">
+        <v>25</v>
+      </c>
+      <c r="CN12" s="1">
+        <v>24</v>
+      </c>
+      <c r="CO12" s="1">
+        <v>15</v>
+      </c>
+      <c r="CP12" s="1">
+        <v>28</v>
+      </c>
+      <c r="CQ12" s="1">
+        <v>11</v>
+      </c>
+      <c r="CR12" s="1">
+        <v>16</v>
+      </c>
+      <c r="CS12" s="1">
+        <v>24</v>
+      </c>
+      <c r="CT12" s="1">
         <v>9</v>
       </c>
-      <c r="CC12" s="6">
+      <c r="CU12" s="1">
+        <v>28</v>
+      </c>
+      <c r="CV12" s="1">
+        <v>9</v>
+      </c>
+      <c r="CW12" s="1">
+        <v>25</v>
+      </c>
+      <c r="CX12" s="1">
+        <v>15</v>
+      </c>
+      <c r="CY12" s="1">
+        <v>41</v>
+      </c>
+      <c r="CZ12" s="1">
+        <v>24</v>
+      </c>
+      <c r="DA12" s="1">
+        <v>9</v>
+      </c>
+      <c r="DB12" s="1">
         <v>13</v>
       </c>
-      <c r="CD12" s="6">
+      <c r="DC12" s="1">
         <v>1</v>
       </c>
-      <c r="CE12" s="6">
+      <c r="DD12" s="1">
         <v>14</v>
       </c>
-      <c r="CF12" s="6">
+      <c r="DE12" s="1">
         <v>21</v>
       </c>
-      <c r="CG12" s="6">
+      <c r="DF12" s="1">
         <v>22</v>
       </c>
-      <c r="CH12" s="6">
+      <c r="DG12" s="1">
         <v>31</v>
       </c>
-      <c r="CI12" s="6">
+      <c r="DH12" s="1">
         <v>15</v>
       </c>
-      <c r="CJ12" s="6">
+      <c r="DI12" s="1">
         <v>4</v>
       </c>
-      <c r="CK12" s="6">
+      <c r="DJ12" s="1">
         <v>35</v>
       </c>
-      <c r="CL12" s="6">
+      <c r="DK12" s="1">
         <v>14</v>
       </c>
-      <c r="CM12" s="6">
+      <c r="DL12" s="1">
         <v>17</v>
       </c>
-      <c r="CN12" s="6">
+      <c r="DM12" s="1">
         <v>31</v>
       </c>
-      <c r="CO12" s="6">
+      <c r="DN12" s="1">
         <v>11</v>
       </c>
-      <c r="CP12" s="6">
+      <c r="DO12" s="1">
         <v>24</v>
       </c>
-      <c r="CQ12" s="6">
+      <c r="DP12" s="1">
         <v>16</v>
       </c>
-      <c r="CR12" s="6">
+      <c r="DQ12" s="1">
         <v>10</v>
       </c>
-      <c r="CS12" s="6">
+      <c r="DR12" s="1">
         <v>26</v>
       </c>
-      <c r="CT12" s="6">
+      <c r="DS12" s="1">
         <v>18</v>
       </c>
-      <c r="CU12" s="6">
+      <c r="DT12" s="1">
         <v>12</v>
       </c>
-      <c r="CV12" s="6">
+      <c r="DU12" s="1">
         <v>18</v>
       </c>
-      <c r="CW12" s="6">
+      <c r="DV12" s="1">
         <v>4</v>
       </c>
-      <c r="CX12" s="6">
+      <c r="DW12" s="1">
         <v>35</v>
       </c>
-      <c r="CY12" s="6">
+      <c r="DX12" s="1">
         <v>29</v>
       </c>
-      <c r="CZ12" s="6">
+      <c r="DY12" s="1">
         <v>34</v>
       </c>
-      <c r="DA12" s="6">
+      <c r="DZ12" s="1">
         <v>20</v>
       </c>
-      <c r="DB12" s="6">
+      <c r="EA12" s="1">
         <v>11</v>
       </c>
-      <c r="DC12" s="6">
+      <c r="EB12" s="1">
         <v>21</v>
       </c>
-      <c r="DD12" s="6">
+      <c r="EC12" s="1">
         <v>20</v>
       </c>
-      <c r="DE12" s="1">
+      <c r="ED12" s="1">
         <v>35</v>
       </c>
-      <c r="DF12" s="1">
+      <c r="EE12" s="1">
         <v>8</v>
       </c>
-      <c r="DG12" s="1">
-        <v>30</v>
-      </c>
-      <c r="DH12" s="1">
+      <c r="EF12" s="1">
+        <v>31</v>
+      </c>
+      <c r="EG12" s="1">
         <v>12</v>
       </c>
-      <c r="DI12" s="1">
-        <v>10</v>
+      <c r="EH12" s="1">
+        <v>29</v>
+      </c>
+      <c r="EI12" s="1">
+        <v>18</v>
+      </c>
+      <c r="EJ12" s="1">
+        <v>1</v>
+      </c>
+      <c r="EK12" s="1">
+        <v>28</v>
+      </c>
+      <c r="EL12" s="1">
+        <v>15</v>
+      </c>
+      <c r="EM12" s="1">
+        <v>14</v>
+      </c>
+      <c r="EN12" s="1">
+        <v>20</v>
+      </c>
+      <c r="EO12" s="1">
+        <v>17</v>
+      </c>
+      <c r="EP12" s="1">
+        <v>1</v>
+      </c>
+      <c r="EQ12" s="1">
+        <v>28</v>
+      </c>
+      <c r="ER12" s="1">
+        <v>17</v>
+      </c>
+      <c r="ES12" s="1">
+        <v>20</v>
+      </c>
+      <c r="ET12" s="1">
+        <v>67</v>
+      </c>
+      <c r="EU12" s="1">
+        <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:153" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>90</v>
       </c>
@@ -5704,16 +7144,130 @@
         <v>100</v>
       </c>
       <c r="DG13">
-        <v>96.77</v>
+        <v>100</v>
       </c>
       <c r="DH13">
         <v>100</v>
       </c>
       <c r="DI13">
-        <v>34.479999999999997</v>
+        <v>100</v>
+      </c>
+      <c r="DJ13">
+        <v>100</v>
+      </c>
+      <c r="DK13">
+        <v>100</v>
+      </c>
+      <c r="DL13">
+        <v>100</v>
+      </c>
+      <c r="DM13">
+        <v>100</v>
+      </c>
+      <c r="DN13">
+        <v>100</v>
+      </c>
+      <c r="DO13">
+        <v>100</v>
+      </c>
+      <c r="DP13">
+        <v>100</v>
+      </c>
+      <c r="DQ13">
+        <v>100</v>
+      </c>
+      <c r="DR13">
+        <v>100</v>
+      </c>
+      <c r="DS13">
+        <v>100</v>
+      </c>
+      <c r="DT13">
+        <v>100</v>
+      </c>
+      <c r="DU13">
+        <v>100</v>
+      </c>
+      <c r="DV13">
+        <v>100</v>
+      </c>
+      <c r="DW13">
+        <v>100</v>
+      </c>
+      <c r="DX13">
+        <v>100</v>
+      </c>
+      <c r="DY13">
+        <v>100</v>
+      </c>
+      <c r="DZ13">
+        <v>100</v>
+      </c>
+      <c r="EA13">
+        <v>100</v>
+      </c>
+      <c r="EB13">
+        <v>100</v>
+      </c>
+      <c r="EC13">
+        <v>100</v>
+      </c>
+      <c r="ED13">
+        <v>100</v>
+      </c>
+      <c r="EE13">
+        <v>100</v>
+      </c>
+      <c r="EF13">
+        <v>100</v>
+      </c>
+      <c r="EG13">
+        <v>100</v>
+      </c>
+      <c r="EH13">
+        <v>100</v>
+      </c>
+      <c r="EI13">
+        <v>100</v>
+      </c>
+      <c r="EJ13">
+        <v>100</v>
+      </c>
+      <c r="EK13">
+        <v>100</v>
+      </c>
+      <c r="EL13">
+        <v>100</v>
+      </c>
+      <c r="EM13">
+        <v>100</v>
+      </c>
+      <c r="EN13">
+        <v>100</v>
+      </c>
+      <c r="EO13">
+        <v>100</v>
+      </c>
+      <c r="EP13">
+        <v>100</v>
+      </c>
+      <c r="EQ13">
+        <v>100</v>
+      </c>
+      <c r="ER13">
+        <v>100</v>
+      </c>
+      <c r="ES13">
+        <v>100</v>
+      </c>
+      <c r="ET13">
+        <v>100</v>
+      </c>
+      <c r="EU13">
+        <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:153" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -5952,109 +7506,224 @@
         <v>28</v>
       </c>
       <c r="CB14" s="1">
+        <v>2</v>
+      </c>
+      <c r="CC14" s="1">
+        <v>10</v>
+      </c>
+      <c r="CD14" s="1">
+        <v>16</v>
+      </c>
+      <c r="CE14" s="1">
+        <v>19</v>
+      </c>
+      <c r="CF14" s="1">
+        <v>16</v>
+      </c>
+      <c r="CG14" s="1">
+        <v>18</v>
+      </c>
+      <c r="CH14" s="1">
+        <v>16</v>
+      </c>
+      <c r="CI14" s="1">
+        <v>28</v>
+      </c>
+      <c r="CJ14" s="1">
+        <v>12</v>
+      </c>
+      <c r="CK14" s="1">
+        <v>10</v>
+      </c>
+      <c r="CL14" s="1">
+        <v>10</v>
+      </c>
+      <c r="CM14" s="1">
+        <v>25</v>
+      </c>
+      <c r="CN14" s="1">
+        <v>23</v>
+      </c>
+      <c r="CO14" s="7"/>
+      <c r="CP14" s="1">
+        <v>28</v>
+      </c>
+      <c r="CQ14" s="1">
+        <v>11</v>
+      </c>
+      <c r="CR14" s="1">
+        <v>16</v>
+      </c>
+      <c r="CS14" s="1">
+        <v>24</v>
+      </c>
+      <c r="CT14" s="1">
         <v>9</v>
       </c>
-      <c r="CC14" s="1">
+      <c r="CU14" s="1">
+        <v>23</v>
+      </c>
+      <c r="CV14" s="1">
+        <v>9</v>
+      </c>
+      <c r="CW14" s="1">
+        <v>24</v>
+      </c>
+      <c r="CX14" s="1">
+        <v>15</v>
+      </c>
+      <c r="CY14" s="1">
+        <v>41</v>
+      </c>
+      <c r="CZ14" s="1">
+        <v>24</v>
+      </c>
+      <c r="DA14" s="1">
+        <v>9</v>
+      </c>
+      <c r="DB14" s="1">
         <v>13</v>
       </c>
-      <c r="CD14" s="1">
+      <c r="DC14" s="1">
         <v>1</v>
       </c>
-      <c r="CE14" s="1">
+      <c r="DD14" s="1">
         <v>14</v>
       </c>
-      <c r="CF14" s="1">
+      <c r="DE14" s="1">
         <v>21</v>
       </c>
-      <c r="CG14" s="1">
+      <c r="DF14" s="1">
         <v>22</v>
       </c>
-      <c r="CH14" s="1">
+      <c r="DG14" s="1">
         <v>31</v>
       </c>
-      <c r="CI14" s="1">
+      <c r="DH14" s="1">
         <v>15</v>
       </c>
-      <c r="CJ14" s="1">
+      <c r="DI14" s="1">
         <v>4</v>
       </c>
-      <c r="CK14" s="1">
+      <c r="DJ14" s="1">
         <v>35</v>
       </c>
-      <c r="CL14" s="1">
+      <c r="DK14" s="1">
         <v>14</v>
       </c>
-      <c r="CM14" s="1">
+      <c r="DL14" s="1">
         <v>17</v>
       </c>
-      <c r="CN14" s="1">
+      <c r="DM14" s="1">
         <v>31</v>
       </c>
-      <c r="CO14" s="1">
+      <c r="DN14" s="1">
         <v>11</v>
       </c>
-      <c r="CP14" s="1">
+      <c r="DO14" s="1">
         <v>24</v>
       </c>
-      <c r="CQ14" s="1">
+      <c r="DP14" s="1">
         <v>16</v>
       </c>
-      <c r="CR14" s="1">
+      <c r="DQ14" s="1">
         <v>10</v>
       </c>
-      <c r="CS14" s="1">
+      <c r="DR14" s="1">
         <v>26</v>
       </c>
-      <c r="CT14" s="1">
+      <c r="DS14" s="1">
         <v>18</v>
       </c>
-      <c r="CU14" s="1">
+      <c r="DT14" s="1">
         <v>12</v>
       </c>
-      <c r="CV14" s="1">
+      <c r="DU14" s="1">
         <v>18</v>
       </c>
-      <c r="CW14" s="1">
+      <c r="DV14" s="1">
         <v>4</v>
       </c>
-      <c r="CX14" s="1">
+      <c r="DW14" s="1">
         <v>17</v>
       </c>
-      <c r="CY14" s="1">
+      <c r="DX14" s="1">
         <v>26</v>
       </c>
-      <c r="CZ14" s="1">
+      <c r="DY14" s="1">
         <v>34</v>
       </c>
-      <c r="DA14" s="1">
+      <c r="DZ14" s="1">
         <v>15</v>
       </c>
-      <c r="DB14" s="1">
+      <c r="EA14" s="1">
         <v>11</v>
       </c>
-      <c r="DC14" s="1">
+      <c r="EB14" s="1">
         <v>21</v>
       </c>
-      <c r="DD14" s="1">
+      <c r="EC14" s="1">
         <v>12</v>
       </c>
-      <c r="DE14" s="7">
-        <v>0</v>
-      </c>
-      <c r="DF14" s="7">
-        <v>0</v>
-      </c>
-      <c r="DG14" s="7">
-        <v>0</v>
-      </c>
-      <c r="DH14" s="7">
-        <v>12</v>
-      </c>
-      <c r="DI14" s="7">
-        <v>10</v>
+      <c r="ED14" s="1">
+        <v>0</v>
+      </c>
+      <c r="EE14" s="1">
+        <v>0</v>
+      </c>
+      <c r="EF14" s="1">
+        <v>0</v>
+      </c>
+      <c r="EG14" s="1">
+        <v>0</v>
+      </c>
+      <c r="EH14" s="1">
+        <v>29</v>
+      </c>
+      <c r="EI14" s="1">
+        <v>18</v>
+      </c>
+      <c r="EJ14" s="1">
+        <v>1</v>
+      </c>
+      <c r="EK14" s="1">
+        <v>28</v>
+      </c>
+      <c r="EL14" s="1">
+        <v>15</v>
+      </c>
+      <c r="EM14" s="1">
+        <v>14</v>
+      </c>
+      <c r="EN14" s="1">
+        <v>20</v>
+      </c>
+      <c r="EO14" s="1">
+        <v>17</v>
+      </c>
+      <c r="EP14" s="1">
+        <v>1</v>
+      </c>
+      <c r="EQ14" s="1">
+        <v>28</v>
+      </c>
+      <c r="ER14" s="1">
+        <v>17</v>
+      </c>
+      <c r="ES14" s="1">
+        <v>20</v>
+      </c>
+      <c r="ET14" s="1">
+        <v>67</v>
+      </c>
+      <c r="EU14" s="1">
+        <v>20</v>
+      </c>
+      <c r="EV14" s="1">
+        <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:153" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>92</v>
       </c>
@@ -6293,13 +7962,13 @@
         <v>0</v>
       </c>
       <c r="CB15">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CC15">
         <v>0</v>
       </c>
       <c r="CD15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE15">
         <v>0</v>
@@ -6329,10 +7998,10 @@
         <v>0</v>
       </c>
       <c r="CN15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO15">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="CP15">
         <v>0</v>
@@ -6350,7 +8019,7 @@
         <v>0</v>
       </c>
       <c r="CU15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="CV15">
         <v>0</v>
@@ -6358,44 +8027,161 @@
       <c r="CW15">
         <v>0</v>
       </c>
-      <c r="CX15" s="1">
+      <c r="CX15">
+        <v>0</v>
+      </c>
+      <c r="CY15">
+        <v>0</v>
+      </c>
+      <c r="CZ15">
+        <v>0</v>
+      </c>
+      <c r="DA15">
+        <v>0</v>
+      </c>
+      <c r="DB15">
+        <v>0</v>
+      </c>
+      <c r="DC15">
+        <v>0</v>
+      </c>
+      <c r="DD15">
+        <v>0</v>
+      </c>
+      <c r="DE15">
+        <v>0</v>
+      </c>
+      <c r="DF15">
+        <v>0</v>
+      </c>
+      <c r="DG15">
+        <v>0</v>
+      </c>
+      <c r="DH15">
+        <v>0</v>
+      </c>
+      <c r="DI15">
+        <v>0</v>
+      </c>
+      <c r="DJ15">
+        <v>0</v>
+      </c>
+      <c r="DK15">
+        <v>0</v>
+      </c>
+      <c r="DL15">
+        <v>0</v>
+      </c>
+      <c r="DM15">
+        <v>0</v>
+      </c>
+      <c r="DN15">
+        <v>0</v>
+      </c>
+      <c r="DO15">
+        <v>0</v>
+      </c>
+      <c r="DP15">
+        <v>0</v>
+      </c>
+      <c r="DQ15">
+        <v>0</v>
+      </c>
+      <c r="DR15">
+        <v>0</v>
+      </c>
+      <c r="DS15">
+        <v>0</v>
+      </c>
+      <c r="DT15">
+        <v>0</v>
+      </c>
+      <c r="DU15">
+        <v>0</v>
+      </c>
+      <c r="DV15">
+        <v>0</v>
+      </c>
+      <c r="DW15">
         <v>18</v>
       </c>
-      <c r="CY15" s="1">
+      <c r="DX15">
         <v>3</v>
       </c>
-      <c r="CZ15" s="7">
-        <v>0</v>
-      </c>
-      <c r="DA15" s="1">
+      <c r="DY15">
+        <v>0</v>
+      </c>
+      <c r="DZ15">
         <v>5</v>
       </c>
-      <c r="DB15" s="7">
-        <v>0</v>
-      </c>
-      <c r="DC15" s="7">
-        <v>0</v>
-      </c>
-      <c r="DD15" s="1">
+      <c r="EA15">
+        <v>0</v>
+      </c>
+      <c r="EB15">
+        <v>0</v>
+      </c>
+      <c r="EC15">
         <v>8</v>
       </c>
-      <c r="DE15" s="1">
+      <c r="ED15" s="1">
         <v>35</v>
       </c>
-      <c r="DF15" s="1">
+      <c r="EE15" s="1">
         <v>8</v>
       </c>
-      <c r="DG15" s="1">
-        <v>30</v>
-      </c>
-      <c r="DH15" s="1">
-        <v>0</v>
-      </c>
-      <c r="DI15" s="1">
+      <c r="EF15" s="1">
+        <v>31</v>
+      </c>
+      <c r="EG15" s="1">
+        <v>12</v>
+      </c>
+      <c r="EH15">
+        <v>0</v>
+      </c>
+      <c r="EI15">
+        <v>0</v>
+      </c>
+      <c r="EJ15">
+        <v>0</v>
+      </c>
+      <c r="EK15">
+        <v>0</v>
+      </c>
+      <c r="EL15">
+        <v>0</v>
+      </c>
+      <c r="EM15">
+        <v>0</v>
+      </c>
+      <c r="EN15">
+        <v>0</v>
+      </c>
+      <c r="EO15">
+        <v>0</v>
+      </c>
+      <c r="EP15">
+        <v>0</v>
+      </c>
+      <c r="EQ15">
+        <v>0</v>
+      </c>
+      <c r="ER15">
+        <v>0</v>
+      </c>
+      <c r="ES15">
+        <v>0</v>
+      </c>
+      <c r="ET15">
+        <v>0</v>
+      </c>
+      <c r="EU15">
+        <v>0</v>
+      </c>
+      <c r="EV15">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:153" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>93</v>
       </c>
@@ -6735,8 +8521,125 @@
       <c r="DI16">
         <v>0</v>
       </c>
+      <c r="DJ16">
+        <v>0</v>
+      </c>
+      <c r="DK16">
+        <v>0</v>
+      </c>
+      <c r="DL16">
+        <v>0</v>
+      </c>
+      <c r="DM16">
+        <v>0</v>
+      </c>
+      <c r="DN16">
+        <v>0</v>
+      </c>
+      <c r="DO16">
+        <v>0</v>
+      </c>
+      <c r="DP16">
+        <v>0</v>
+      </c>
+      <c r="DQ16">
+        <v>0</v>
+      </c>
+      <c r="DR16">
+        <v>0</v>
+      </c>
+      <c r="DS16">
+        <v>0</v>
+      </c>
+      <c r="DT16">
+        <v>0</v>
+      </c>
+      <c r="DU16">
+        <v>0</v>
+      </c>
+      <c r="DV16">
+        <v>0</v>
+      </c>
+      <c r="DW16">
+        <v>0</v>
+      </c>
+      <c r="DX16">
+        <v>0</v>
+      </c>
+      <c r="DY16">
+        <v>0</v>
+      </c>
+      <c r="DZ16">
+        <v>0</v>
+      </c>
+      <c r="EA16">
+        <v>0</v>
+      </c>
+      <c r="EB16">
+        <v>0</v>
+      </c>
+      <c r="EC16">
+        <v>0</v>
+      </c>
+      <c r="ED16">
+        <v>0</v>
+      </c>
+      <c r="EE16">
+        <v>0</v>
+      </c>
+      <c r="EF16">
+        <v>0</v>
+      </c>
+      <c r="EG16">
+        <v>0</v>
+      </c>
+      <c r="EH16">
+        <v>0</v>
+      </c>
+      <c r="EI16">
+        <v>0</v>
+      </c>
+      <c r="EJ16">
+        <v>0</v>
+      </c>
+      <c r="EK16">
+        <v>0</v>
+      </c>
+      <c r="EL16">
+        <v>0</v>
+      </c>
+      <c r="EM16">
+        <v>0</v>
+      </c>
+      <c r="EN16">
+        <v>0</v>
+      </c>
+      <c r="EO16">
+        <v>0</v>
+      </c>
+      <c r="EP16">
+        <v>0</v>
+      </c>
+      <c r="EQ16">
+        <v>0</v>
+      </c>
+      <c r="ER16">
+        <v>0</v>
+      </c>
+      <c r="ES16">
+        <v>0</v>
+      </c>
+      <c r="ET16">
+        <v>0</v>
+      </c>
+      <c r="EU16">
+        <v>0</v>
+      </c>
+      <c r="EV16">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:113" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:155" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>94</v>
       </c>
@@ -7076,8 +8979,125 @@
       <c r="DI17">
         <v>0</v>
       </c>
+      <c r="DJ17">
+        <v>0</v>
+      </c>
+      <c r="DK17">
+        <v>0</v>
+      </c>
+      <c r="DL17">
+        <v>0</v>
+      </c>
+      <c r="DM17">
+        <v>0</v>
+      </c>
+      <c r="DN17">
+        <v>0</v>
+      </c>
+      <c r="DO17">
+        <v>0</v>
+      </c>
+      <c r="DP17">
+        <v>0</v>
+      </c>
+      <c r="DQ17">
+        <v>0</v>
+      </c>
+      <c r="DR17">
+        <v>0</v>
+      </c>
+      <c r="DS17">
+        <v>0</v>
+      </c>
+      <c r="DT17">
+        <v>0</v>
+      </c>
+      <c r="DU17">
+        <v>0</v>
+      </c>
+      <c r="DV17">
+        <v>0</v>
+      </c>
+      <c r="DW17">
+        <v>0</v>
+      </c>
+      <c r="DX17">
+        <v>0</v>
+      </c>
+      <c r="DY17">
+        <v>0</v>
+      </c>
+      <c r="DZ17">
+        <v>0</v>
+      </c>
+      <c r="EA17">
+        <v>0</v>
+      </c>
+      <c r="EB17">
+        <v>0</v>
+      </c>
+      <c r="EC17">
+        <v>0</v>
+      </c>
+      <c r="ED17">
+        <v>0</v>
+      </c>
+      <c r="EE17">
+        <v>0</v>
+      </c>
+      <c r="EF17">
+        <v>0</v>
+      </c>
+      <c r="EG17">
+        <v>0</v>
+      </c>
+      <c r="EH17">
+        <v>0</v>
+      </c>
+      <c r="EI17">
+        <v>0</v>
+      </c>
+      <c r="EJ17">
+        <v>0</v>
+      </c>
+      <c r="EK17">
+        <v>0</v>
+      </c>
+      <c r="EL17">
+        <v>0</v>
+      </c>
+      <c r="EM17">
+        <v>0</v>
+      </c>
+      <c r="EN17">
+        <v>0</v>
+      </c>
+      <c r="EO17">
+        <v>0</v>
+      </c>
+      <c r="EP17">
+        <v>0</v>
+      </c>
+      <c r="EQ17">
+        <v>0</v>
+      </c>
+      <c r="ER17">
+        <v>0</v>
+      </c>
+      <c r="ES17">
+        <v>0</v>
+      </c>
+      <c r="ET17">
+        <v>0</v>
+      </c>
+      <c r="EU17">
+        <v>0</v>
+      </c>
+      <c r="EV17">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:113" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:155" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>95</v>
       </c>
@@ -7316,109 +9336,226 @@
         <v>75</v>
       </c>
       <c r="CB18" s="8">
+        <v>75</v>
+      </c>
+      <c r="CC18" s="8">
+        <v>85</v>
+      </c>
+      <c r="CD18" s="8">
+        <v>70</v>
+      </c>
+      <c r="CE18" s="8">
+        <v>77</v>
+      </c>
+      <c r="CF18" s="8">
+        <v>70</v>
+      </c>
+      <c r="CG18" s="8">
+        <v>77</v>
+      </c>
+      <c r="CH18" s="8">
+        <v>85</v>
+      </c>
+      <c r="CI18" s="8">
+        <v>95</v>
+      </c>
+      <c r="CJ18" s="8">
+        <v>79</v>
+      </c>
+      <c r="CK18" s="8">
+        <v>78</v>
+      </c>
+      <c r="CL18" s="8">
+        <v>76</v>
+      </c>
+      <c r="CM18" s="8">
+        <v>102</v>
+      </c>
+      <c r="CN18" s="8">
+        <v>63</v>
+      </c>
+      <c r="CO18" s="8">
+        <v>81</v>
+      </c>
+      <c r="CP18" s="8">
+        <v>95</v>
+      </c>
+      <c r="CQ18" s="8">
+        <v>73</v>
+      </c>
+      <c r="CR18" s="8">
+        <v>72</v>
+      </c>
+      <c r="CS18" s="8">
+        <v>70</v>
+      </c>
+      <c r="CT18" s="8">
+        <v>97</v>
+      </c>
+      <c r="CU18" s="8">
+        <v>70</v>
+      </c>
+      <c r="CV18" s="8">
+        <v>70</v>
+      </c>
+      <c r="CW18" s="8">
+        <v>71</v>
+      </c>
+      <c r="CX18" s="8">
+        <v>139</v>
+      </c>
+      <c r="CY18" s="8">
+        <v>118</v>
+      </c>
+      <c r="CZ18" s="8">
+        <v>84</v>
+      </c>
+      <c r="DA18" s="8">
         <v>80</v>
       </c>
-      <c r="CC18" s="8">
+      <c r="DB18" s="8">
         <v>104</v>
       </c>
-      <c r="CD18" s="8">
+      <c r="DC18" s="8">
         <v>120</v>
       </c>
-      <c r="CE18" s="8">
+      <c r="DD18" s="8">
         <v>102</v>
       </c>
-      <c r="CF18" s="8">
+      <c r="DE18" s="8">
         <v>107</v>
       </c>
-      <c r="CG18" s="8">
+      <c r="DF18" s="8">
         <v>102</v>
       </c>
-      <c r="CH18" s="8">
+      <c r="DG18" s="8">
         <v>81</v>
       </c>
-      <c r="CI18" s="8">
+      <c r="DH18" s="8">
         <v>101</v>
       </c>
-      <c r="CJ18" s="8">
+      <c r="DI18" s="8">
         <v>96</v>
       </c>
-      <c r="CK18" s="8">
+      <c r="DJ18" s="8">
         <v>153</v>
       </c>
-      <c r="CL18" s="8">
+      <c r="DK18" s="8">
         <v>63</v>
       </c>
-      <c r="CM18" s="8">
+      <c r="DL18" s="8">
         <v>103</v>
       </c>
-      <c r="CN18" s="8">
+      <c r="DM18" s="8">
         <v>119</v>
       </c>
-      <c r="CO18" s="8">
+      <c r="DN18" s="8">
         <v>123</v>
       </c>
-      <c r="CP18" s="8">
+      <c r="DO18" s="8">
         <v>96</v>
       </c>
-      <c r="CQ18" s="8">
+      <c r="DP18" s="8">
         <v>89</v>
       </c>
-      <c r="CR18" s="8">
-        <v>100</v>
-      </c>
-      <c r="CS18" s="8">
+      <c r="DQ18" s="8">
+        <v>100</v>
+      </c>
+      <c r="DR18" s="8">
         <v>112</v>
       </c>
-      <c r="CT18" s="8">
+      <c r="DS18" s="8">
         <v>119</v>
       </c>
-      <c r="CU18" s="8">
+      <c r="DT18" s="8">
         <v>130</v>
       </c>
-      <c r="CV18" s="8">
+      <c r="DU18" s="8">
         <v>108</v>
       </c>
-      <c r="CW18" s="8">
+      <c r="DV18" s="8">
         <v>106</v>
       </c>
-      <c r="CX18" s="8">
+      <c r="DW18" s="8">
         <v>107</v>
       </c>
-      <c r="CY18" s="8">
+      <c r="DX18" s="8">
         <v>129</v>
       </c>
-      <c r="CZ18" s="8">
+      <c r="DY18" s="8">
         <v>119</v>
       </c>
-      <c r="DA18" s="8">
+      <c r="DZ18" s="8">
         <v>105</v>
       </c>
-      <c r="DB18" s="8">
+      <c r="EA18" s="8">
         <v>135</v>
       </c>
-      <c r="DC18" s="8">
+      <c r="EB18" s="8">
         <v>142</v>
       </c>
-      <c r="DD18" s="8">
+      <c r="EC18" s="8">
         <v>124</v>
       </c>
-      <c r="DE18" s="8">
+      <c r="ED18" s="8">
         <v>103</v>
       </c>
-      <c r="DF18" s="8">
+      <c r="EE18" s="8">
         <v>162</v>
       </c>
-      <c r="DG18" s="8">
+      <c r="EF18" s="8">
         <v>143</v>
       </c>
-      <c r="DH18" s="8">
+      <c r="EG18" s="8">
         <v>120</v>
       </c>
-      <c r="DI18" s="8">
+      <c r="EH18" s="8">
         <v>130</v>
       </c>
+      <c r="EI18" s="8">
+        <v>133</v>
+      </c>
+      <c r="EJ18" s="8">
+        <v>142</v>
+      </c>
+      <c r="EK18" s="8">
+        <v>122</v>
+      </c>
+      <c r="EL18" s="8">
+        <v>126</v>
+      </c>
+      <c r="EM18" s="8">
+        <v>131</v>
+      </c>
+      <c r="EN18" s="8">
+        <v>117</v>
+      </c>
+      <c r="EO18" s="8">
+        <v>115</v>
+      </c>
+      <c r="EP18" s="8">
+        <v>113</v>
+      </c>
+      <c r="EQ18" s="8">
+        <v>119</v>
+      </c>
+      <c r="ER18" s="8">
+        <v>102</v>
+      </c>
+      <c r="ES18" s="8">
+        <v>108</v>
+      </c>
+      <c r="ET18" s="8">
+        <v>84</v>
+      </c>
+      <c r="EU18" s="8">
+        <v>108</v>
+      </c>
+      <c r="EV18" s="8">
+        <v>117</v>
+      </c>
     </row>
-    <row r="19" spans="1:113" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:155" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>96</v>
       </c>
@@ -7657,109 +9794,226 @@
         <v>75</v>
       </c>
       <c r="CB19" s="8">
+        <v>75</v>
+      </c>
+      <c r="CC19" s="8">
+        <v>85</v>
+      </c>
+      <c r="CD19" s="8">
+        <v>70</v>
+      </c>
+      <c r="CE19" s="8">
+        <v>77</v>
+      </c>
+      <c r="CF19" s="8">
+        <v>70</v>
+      </c>
+      <c r="CG19" s="8">
+        <v>77</v>
+      </c>
+      <c r="CH19" s="8">
+        <v>85</v>
+      </c>
+      <c r="CI19" s="8">
+        <v>95</v>
+      </c>
+      <c r="CJ19" s="8">
+        <v>79</v>
+      </c>
+      <c r="CK19" s="8">
+        <v>78</v>
+      </c>
+      <c r="CL19" s="8">
+        <v>76</v>
+      </c>
+      <c r="CM19" s="8">
+        <v>102</v>
+      </c>
+      <c r="CN19" s="8">
+        <v>63</v>
+      </c>
+      <c r="CO19" s="8">
+        <v>81</v>
+      </c>
+      <c r="CP19" s="8">
+        <v>95</v>
+      </c>
+      <c r="CQ19" s="8">
+        <v>73</v>
+      </c>
+      <c r="CR19" s="8">
+        <v>72</v>
+      </c>
+      <c r="CS19" s="8">
+        <v>70</v>
+      </c>
+      <c r="CT19" s="8">
+        <v>97</v>
+      </c>
+      <c r="CU19" s="8">
+        <v>70</v>
+      </c>
+      <c r="CV19" s="8">
+        <v>70</v>
+      </c>
+      <c r="CW19" s="8">
+        <v>71</v>
+      </c>
+      <c r="CX19" s="8">
+        <v>139</v>
+      </c>
+      <c r="CY19" s="8">
+        <v>118</v>
+      </c>
+      <c r="CZ19" s="8">
+        <v>84</v>
+      </c>
+      <c r="DA19" s="8">
         <v>80</v>
       </c>
-      <c r="CC19" s="8">
+      <c r="DB19" s="8">
         <v>104</v>
       </c>
-      <c r="CD19" s="8">
+      <c r="DC19" s="8">
         <v>120</v>
       </c>
-      <c r="CE19" s="8">
+      <c r="DD19" s="8">
         <v>102</v>
       </c>
-      <c r="CF19" s="8">
+      <c r="DE19" s="8">
         <v>107</v>
       </c>
-      <c r="CG19" s="8">
+      <c r="DF19" s="8">
         <v>102</v>
       </c>
-      <c r="CH19" s="8">
+      <c r="DG19" s="8">
         <v>81</v>
       </c>
-      <c r="CI19" s="8">
+      <c r="DH19" s="8">
         <v>101</v>
       </c>
-      <c r="CJ19" s="8">
+      <c r="DI19" s="8">
         <v>96</v>
       </c>
-      <c r="CK19" s="8">
+      <c r="DJ19" s="8">
         <v>153</v>
       </c>
-      <c r="CL19" s="8">
+      <c r="DK19" s="8">
         <v>63</v>
       </c>
-      <c r="CM19" s="8">
+      <c r="DL19" s="8">
         <v>103</v>
       </c>
-      <c r="CN19" s="8">
+      <c r="DM19" s="8">
         <v>119</v>
       </c>
-      <c r="CO19" s="8">
+      <c r="DN19" s="8">
         <v>123</v>
       </c>
-      <c r="CP19" s="8">
+      <c r="DO19" s="8">
         <v>96</v>
       </c>
-      <c r="CQ19" s="8">
+      <c r="DP19" s="8">
         <v>89</v>
       </c>
-      <c r="CR19" s="8">
-        <v>100</v>
-      </c>
-      <c r="CS19" s="8">
+      <c r="DQ19" s="8">
+        <v>100</v>
+      </c>
+      <c r="DR19" s="8">
         <v>112</v>
       </c>
-      <c r="CT19" s="8">
+      <c r="DS19" s="8">
         <v>119</v>
       </c>
-      <c r="CU19" s="8">
+      <c r="DT19" s="8">
         <v>130</v>
       </c>
-      <c r="CV19" s="8">
+      <c r="DU19" s="8">
         <v>108</v>
       </c>
-      <c r="CW19" s="8">
+      <c r="DV19" s="8">
         <v>106</v>
       </c>
-      <c r="CX19" s="8">
+      <c r="DW19" s="8">
         <v>107</v>
       </c>
-      <c r="CY19" s="8">
+      <c r="DX19" s="8">
         <v>129</v>
       </c>
-      <c r="CZ19" s="8">
+      <c r="DY19" s="8">
         <v>119</v>
       </c>
-      <c r="DA19" s="8">
+      <c r="DZ19" s="8">
         <v>105</v>
       </c>
-      <c r="DB19" s="8">
+      <c r="EA19" s="8">
         <v>135</v>
       </c>
-      <c r="DC19" s="8">
+      <c r="EB19" s="8">
         <v>142</v>
       </c>
-      <c r="DD19" s="8">
+      <c r="EC19" s="8">
         <v>124</v>
       </c>
-      <c r="DE19" s="8">
+      <c r="ED19" s="8">
         <v>103</v>
       </c>
-      <c r="DF19" s="8">
+      <c r="EE19" s="8">
         <v>162</v>
       </c>
-      <c r="DG19" s="8">
+      <c r="EF19" s="8">
         <v>143</v>
       </c>
-      <c r="DH19" s="8">
+      <c r="EG19" s="8">
         <v>120</v>
       </c>
-      <c r="DI19" s="8">
+      <c r="EH19" s="8">
         <v>130</v>
       </c>
+      <c r="EI19" s="8">
+        <v>133</v>
+      </c>
+      <c r="EJ19" s="8">
+        <v>142</v>
+      </c>
+      <c r="EK19" s="8">
+        <v>122</v>
+      </c>
+      <c r="EL19" s="8">
+        <v>126</v>
+      </c>
+      <c r="EM19" s="8">
+        <v>131</v>
+      </c>
+      <c r="EN19" s="8">
+        <v>117</v>
+      </c>
+      <c r="EO19" s="8">
+        <v>115</v>
+      </c>
+      <c r="EP19" s="8">
+        <v>113</v>
+      </c>
+      <c r="EQ19" s="8">
+        <v>119</v>
+      </c>
+      <c r="ER19" s="8">
+        <v>102</v>
+      </c>
+      <c r="ES19" s="8">
+        <v>108</v>
+      </c>
+      <c r="ET19" s="8">
+        <v>84</v>
+      </c>
+      <c r="EU19" s="8">
+        <v>108</v>
+      </c>
+      <c r="EV19" s="8">
+        <v>117</v>
+      </c>
     </row>
-    <row r="20" spans="1:113" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:155" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>97</v>
       </c>
@@ -7998,109 +10252,226 @@
         <v>75</v>
       </c>
       <c r="CB20" s="9">
+        <v>75</v>
+      </c>
+      <c r="CC20" s="9">
+        <v>85</v>
+      </c>
+      <c r="CD20" s="9">
+        <v>70</v>
+      </c>
+      <c r="CE20" s="9">
+        <v>77</v>
+      </c>
+      <c r="CF20" s="9">
+        <v>70</v>
+      </c>
+      <c r="CG20" s="9">
+        <v>77</v>
+      </c>
+      <c r="CH20" s="9">
+        <v>85</v>
+      </c>
+      <c r="CI20" s="9">
+        <v>95</v>
+      </c>
+      <c r="CJ20" s="9">
+        <v>79</v>
+      </c>
+      <c r="CK20" s="9">
+        <v>78</v>
+      </c>
+      <c r="CL20" s="9">
+        <v>76</v>
+      </c>
+      <c r="CM20" s="9">
+        <v>102</v>
+      </c>
+      <c r="CN20" s="9">
+        <v>63</v>
+      </c>
+      <c r="CO20" s="9">
+        <v>81</v>
+      </c>
+      <c r="CP20" s="9">
+        <v>95</v>
+      </c>
+      <c r="CQ20" s="9">
+        <v>73</v>
+      </c>
+      <c r="CR20" s="9">
+        <v>72</v>
+      </c>
+      <c r="CS20" s="9">
+        <v>70</v>
+      </c>
+      <c r="CT20" s="9">
+        <v>97</v>
+      </c>
+      <c r="CU20" s="9">
+        <v>70</v>
+      </c>
+      <c r="CV20" s="9">
+        <v>70</v>
+      </c>
+      <c r="CW20" s="9">
+        <v>71</v>
+      </c>
+      <c r="CX20" s="9">
+        <v>139</v>
+      </c>
+      <c r="CY20" s="9">
+        <v>118</v>
+      </c>
+      <c r="CZ20" s="9">
+        <v>84</v>
+      </c>
+      <c r="DA20" s="9">
         <v>80</v>
       </c>
-      <c r="CC20" s="9">
+      <c r="DB20" s="9">
         <v>104</v>
       </c>
-      <c r="CD20" s="9">
+      <c r="DC20" s="9">
         <v>120</v>
       </c>
-      <c r="CE20" s="9">
+      <c r="DD20" s="9">
         <v>102</v>
       </c>
-      <c r="CF20" s="9">
+      <c r="DE20" s="9">
         <v>107</v>
       </c>
-      <c r="CG20" s="9">
+      <c r="DF20" s="9">
         <v>102</v>
       </c>
-      <c r="CH20" s="9">
+      <c r="DG20" s="9">
         <v>81</v>
       </c>
-      <c r="CI20" s="9">
+      <c r="DH20" s="9">
         <v>101</v>
       </c>
-      <c r="CJ20" s="9">
+      <c r="DI20" s="9">
         <v>96</v>
       </c>
-      <c r="CK20" s="9">
+      <c r="DJ20" s="9">
         <v>153</v>
       </c>
-      <c r="CL20" s="9">
-        <v>63</v>
-      </c>
-      <c r="CM20" s="9">
+      <c r="DK20" s="9">
+        <v>23</v>
+      </c>
+      <c r="DL20" s="9">
         <v>103</v>
       </c>
-      <c r="CN20" s="9">
+      <c r="DM20" s="9">
         <v>119</v>
       </c>
-      <c r="CO20" s="9">
+      <c r="DN20" s="9">
         <v>123</v>
       </c>
-      <c r="CP20" s="9">
+      <c r="DO20" s="9">
         <v>96</v>
       </c>
-      <c r="CQ20" s="9">
+      <c r="DP20" s="9">
         <v>80</v>
       </c>
-      <c r="CR20" s="9">
-        <v>100</v>
-      </c>
-      <c r="CS20" s="9">
+      <c r="DQ20" s="9">
+        <v>100</v>
+      </c>
+      <c r="DR20" s="9">
         <v>112</v>
       </c>
-      <c r="CT20" s="9">
+      <c r="DS20" s="9">
         <v>119</v>
       </c>
-      <c r="CU20" s="9">
-        <v>97</v>
-      </c>
-      <c r="CV20" s="9">
+      <c r="DT20" s="9">
+        <v>103</v>
+      </c>
+      <c r="DU20" s="9">
         <v>108</v>
       </c>
-      <c r="CW20" s="9">
+      <c r="DV20" s="9">
         <v>106</v>
       </c>
-      <c r="CX20" s="9">
+      <c r="DW20" s="9">
         <v>107</v>
       </c>
-      <c r="CY20" s="9">
+      <c r="DX20" s="9">
         <v>129</v>
       </c>
-      <c r="CZ20" s="9">
+      <c r="DY20" s="9">
         <v>119</v>
       </c>
-      <c r="DA20" s="9">
+      <c r="DZ20" s="9">
         <v>105</v>
       </c>
-      <c r="DB20" s="9">
+      <c r="EA20" s="9">
         <v>135</v>
       </c>
-      <c r="DC20" s="9">
+      <c r="EB20" s="9">
         <v>142</v>
       </c>
-      <c r="DD20" s="9">
+      <c r="EC20" s="9">
         <v>124</v>
       </c>
-      <c r="DE20" s="9">
+      <c r="ED20" s="9">
         <v>103</v>
       </c>
-      <c r="DF20" s="9">
+      <c r="EE20" s="9">
         <v>162</v>
       </c>
-      <c r="DG20" s="9">
+      <c r="EF20" s="9">
         <v>143</v>
       </c>
-      <c r="DH20" s="9">
+      <c r="EG20" s="9">
         <v>120</v>
       </c>
-      <c r="DI20" s="9">
+      <c r="EH20" s="9">
         <v>130</v>
       </c>
+      <c r="EI20" s="9">
+        <v>133</v>
+      </c>
+      <c r="EJ20" s="9">
+        <v>141</v>
+      </c>
+      <c r="EK20" s="9">
+        <v>122</v>
+      </c>
+      <c r="EL20" s="9">
+        <v>126</v>
+      </c>
+      <c r="EM20" s="9">
+        <v>131</v>
+      </c>
+      <c r="EN20" s="9">
+        <v>117</v>
+      </c>
+      <c r="EO20" s="9">
+        <v>49</v>
+      </c>
+      <c r="EP20" s="9">
+        <v>113</v>
+      </c>
+      <c r="EQ20" s="9">
+        <v>119</v>
+      </c>
+      <c r="ER20" s="9">
+        <v>102</v>
+      </c>
+      <c r="ES20" s="9">
+        <v>19</v>
+      </c>
+      <c r="ET20" s="9">
+        <v>84</v>
+      </c>
+      <c r="EU20" s="9">
+        <v>108</v>
+      </c>
+      <c r="EV20" s="9">
+        <v>12</v>
+      </c>
     </row>
-    <row r="21" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:155" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>98</v>
       </c>
@@ -8384,64 +10755,181 @@
         <v>100</v>
       </c>
       <c r="CQ21">
+        <v>100</v>
+      </c>
+      <c r="CR21">
+        <v>100</v>
+      </c>
+      <c r="CS21">
+        <v>100</v>
+      </c>
+      <c r="CT21">
+        <v>100</v>
+      </c>
+      <c r="CU21">
+        <v>100</v>
+      </c>
+      <c r="CV21">
+        <v>100</v>
+      </c>
+      <c r="CW21">
+        <v>100</v>
+      </c>
+      <c r="CX21">
+        <v>100</v>
+      </c>
+      <c r="CY21">
+        <v>100</v>
+      </c>
+      <c r="CZ21">
+        <v>100</v>
+      </c>
+      <c r="DA21">
+        <v>100</v>
+      </c>
+      <c r="DB21">
+        <v>100</v>
+      </c>
+      <c r="DC21">
+        <v>100</v>
+      </c>
+      <c r="DD21">
+        <v>100</v>
+      </c>
+      <c r="DE21">
+        <v>100</v>
+      </c>
+      <c r="DF21">
+        <v>100</v>
+      </c>
+      <c r="DG21">
+        <v>100</v>
+      </c>
+      <c r="DH21">
+        <v>100</v>
+      </c>
+      <c r="DI21">
+        <v>100</v>
+      </c>
+      <c r="DJ21">
+        <v>100</v>
+      </c>
+      <c r="DK21">
+        <v>36.51</v>
+      </c>
+      <c r="DL21">
+        <v>100</v>
+      </c>
+      <c r="DM21">
+        <v>100</v>
+      </c>
+      <c r="DN21">
+        <v>100</v>
+      </c>
+      <c r="DO21">
+        <v>100</v>
+      </c>
+      <c r="DP21">
         <v>89.89</v>
       </c>
-      <c r="CR21">
-        <v>100</v>
-      </c>
-      <c r="CS21">
-        <v>100</v>
-      </c>
-      <c r="CT21">
-        <v>100</v>
-      </c>
-      <c r="CU21">
-        <v>74.62</v>
-      </c>
-      <c r="CV21">
-        <v>100</v>
-      </c>
-      <c r="CW21">
-        <v>100</v>
-      </c>
-      <c r="CX21">
-        <v>100</v>
-      </c>
-      <c r="CY21">
-        <v>100</v>
-      </c>
-      <c r="CZ21">
-        <v>100</v>
-      </c>
-      <c r="DA21">
-        <v>100</v>
-      </c>
-      <c r="DB21">
-        <v>100</v>
-      </c>
-      <c r="DC21">
-        <v>100</v>
-      </c>
-      <c r="DD21">
-        <v>100</v>
-      </c>
-      <c r="DE21">
-        <v>100</v>
-      </c>
-      <c r="DF21">
-        <v>100</v>
-      </c>
-      <c r="DG21">
-        <v>100</v>
-      </c>
-      <c r="DH21">
-        <v>100</v>
-      </c>
-      <c r="DI21">
-        <v>100</v>
+      <c r="DQ21">
+        <v>100</v>
+      </c>
+      <c r="DR21">
+        <v>100</v>
+      </c>
+      <c r="DS21">
+        <v>100</v>
+      </c>
+      <c r="DT21">
+        <v>79.23</v>
+      </c>
+      <c r="DU21">
+        <v>100</v>
+      </c>
+      <c r="DV21">
+        <v>100</v>
+      </c>
+      <c r="DW21">
+        <v>100</v>
+      </c>
+      <c r="DX21">
+        <v>100</v>
+      </c>
+      <c r="DY21">
+        <v>100</v>
+      </c>
+      <c r="DZ21">
+        <v>100</v>
+      </c>
+      <c r="EA21">
+        <v>100</v>
+      </c>
+      <c r="EB21">
+        <v>100</v>
+      </c>
+      <c r="EC21">
+        <v>100</v>
+      </c>
+      <c r="ED21">
+        <v>100</v>
+      </c>
+      <c r="EE21">
+        <v>100</v>
+      </c>
+      <c r="EF21">
+        <v>100</v>
+      </c>
+      <c r="EG21">
+        <v>100</v>
+      </c>
+      <c r="EH21">
+        <v>100</v>
+      </c>
+      <c r="EI21">
+        <v>100</v>
+      </c>
+      <c r="EJ21">
+        <v>99.3</v>
+      </c>
+      <c r="EK21">
+        <v>100</v>
+      </c>
+      <c r="EL21">
+        <v>100</v>
+      </c>
+      <c r="EM21">
+        <v>100</v>
+      </c>
+      <c r="EN21">
+        <v>100</v>
+      </c>
+      <c r="EO21">
+        <v>42.61</v>
+      </c>
+      <c r="EP21">
+        <v>100</v>
+      </c>
+      <c r="EQ21">
+        <v>100</v>
+      </c>
+      <c r="ER21">
+        <v>100</v>
+      </c>
+      <c r="ES21">
+        <v>17.59</v>
+      </c>
+      <c r="ET21">
+        <v>100</v>
+      </c>
+      <c r="EU21">
+        <v>100</v>
+      </c>
+      <c r="EV21">
+        <v>10.26</v>
       </c>
     </row>
-    <row r="22" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:155" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>99</v>
       </c>
@@ -8679,86 +11167,202 @@
       <c r="CA22">
         <v>75</v>
       </c>
-      <c r="CB22" s="1">
+      <c r="CB22" s="9">
+        <v>75</v>
+      </c>
+      <c r="CC22" s="9">
+        <v>85</v>
+      </c>
+      <c r="CD22" s="9">
+        <v>70</v>
+      </c>
+      <c r="CE22" s="9">
+        <v>77</v>
+      </c>
+      <c r="CF22" s="9">
+        <v>70</v>
+      </c>
+      <c r="CG22" s="9">
+        <v>77</v>
+      </c>
+      <c r="CH22" s="9">
+        <v>85</v>
+      </c>
+      <c r="CI22" s="9">
+        <v>95</v>
+      </c>
+      <c r="CJ22" s="9">
+        <v>79</v>
+      </c>
+      <c r="CK22" s="9">
+        <v>78</v>
+      </c>
+      <c r="CL22" s="9">
+        <v>76</v>
+      </c>
+      <c r="CM22" s="9">
+        <v>102</v>
+      </c>
+      <c r="CN22" s="9">
+        <v>63</v>
+      </c>
+      <c r="CO22" s="9">
+        <v>0</v>
+      </c>
+      <c r="CP22" s="9">
+        <v>0</v>
+      </c>
+      <c r="CQ22" s="9">
+        <v>73</v>
+      </c>
+      <c r="CR22" s="9">
+        <v>72</v>
+      </c>
+      <c r="CS22" s="9">
+        <v>70</v>
+      </c>
+      <c r="CT22" s="9">
+        <v>97</v>
+      </c>
+      <c r="CU22" s="9">
+        <v>70</v>
+      </c>
+      <c r="CV22" s="9">
+        <v>70</v>
+      </c>
+      <c r="CW22" s="9">
+        <v>71</v>
+      </c>
+      <c r="CX22" s="9">
+        <v>139</v>
+      </c>
+      <c r="CY22" s="9">
+        <v>118</v>
+      </c>
+      <c r="CZ22" s="9">
+        <v>84</v>
+      </c>
+      <c r="DA22" s="1">
         <v>80</v>
       </c>
-      <c r="CC22" s="1">
+      <c r="DB22" s="1">
         <v>104</v>
       </c>
-      <c r="CD22" s="1">
+      <c r="DC22" s="1">
         <v>120</v>
       </c>
-      <c r="CE22" s="1">
+      <c r="DD22" s="1">
         <v>102</v>
       </c>
-      <c r="CF22" s="1">
+      <c r="DE22" s="1">
         <v>107</v>
       </c>
-      <c r="CG22" s="1">
+      <c r="DF22" s="1">
         <v>102</v>
       </c>
-      <c r="CH22" s="1">
+      <c r="DG22" s="1">
         <v>81</v>
       </c>
-      <c r="CI22" s="1">
+      <c r="DH22" s="1">
         <v>101</v>
       </c>
-      <c r="CJ22" s="1">
+      <c r="DI22" s="1">
         <v>2</v>
       </c>
-      <c r="CK22" s="1">
+      <c r="DJ22" s="1">
         <v>153</v>
       </c>
-      <c r="CL22" s="7"/>
-      <c r="CM22" s="1">
+      <c r="DK22" s="7">
+        <v>1</v>
+      </c>
+      <c r="DL22" s="1">
         <v>103</v>
       </c>
-      <c r="CN22" s="1">
+      <c r="DM22" s="1">
         <v>119</v>
       </c>
-      <c r="CO22" s="7"/>
-      <c r="CP22" s="7"/>
-      <c r="CQ22" s="1">
+      <c r="DN22" s="7"/>
+      <c r="DO22" s="7"/>
+      <c r="DP22" s="1">
         <v>80</v>
       </c>
-      <c r="CR22" s="1">
-        <v>100</v>
-      </c>
-      <c r="CS22" s="1">
+      <c r="DQ22" s="1">
+        <v>100</v>
+      </c>
+      <c r="DR22" s="1">
         <v>112</v>
       </c>
-      <c r="CT22" s="1">
+      <c r="DS22" s="1">
         <v>119</v>
       </c>
-      <c r="CU22" s="1">
-        <v>96</v>
-      </c>
-      <c r="CV22" s="1">
+      <c r="DT22" s="1">
+        <v>94</v>
+      </c>
+      <c r="DU22" s="1">
         <v>108</v>
       </c>
-      <c r="CW22" s="1">
+      <c r="DV22" s="1">
         <v>106</v>
       </c>
-      <c r="CX22" s="1">
+      <c r="DW22" s="1">
         <v>107</v>
       </c>
-      <c r="CY22" s="1">
+      <c r="DX22" s="1">
         <v>129</v>
       </c>
-      <c r="CZ22" s="1">
+      <c r="DY22" s="1">
         <v>57</v>
       </c>
-      <c r="DA22" s="7"/>
-      <c r="DB22" s="7"/>
-      <c r="DC22" s="7"/>
-      <c r="DD22" s="7"/>
-      <c r="DE22" s="7"/>
-      <c r="DF22" s="7"/>
-      <c r="DG22" s="7"/>
-      <c r="DH22" s="7"/>
-      <c r="DI22" s="7"/>
+      <c r="DZ22" s="7"/>
+      <c r="EA22" s="7"/>
+      <c r="EB22" s="7"/>
+      <c r="EC22" s="7"/>
+      <c r="ED22" s="7"/>
+      <c r="EE22" s="7"/>
+      <c r="EF22" s="1">
+        <v>77</v>
+      </c>
+      <c r="EG22" s="7"/>
+      <c r="EH22" s="1">
+        <v>130</v>
+      </c>
+      <c r="EI22" s="7"/>
+      <c r="EJ22" s="7"/>
+      <c r="EK22" s="7"/>
+      <c r="EL22" s="1">
+        <v>126</v>
+      </c>
+      <c r="EM22" s="7"/>
+      <c r="EN22" s="7"/>
+      <c r="EO22" s="1">
+        <v>49</v>
+      </c>
+      <c r="EP22" s="1">
+        <v>113</v>
+      </c>
+      <c r="EQ22" s="1">
+        <v>119</v>
+      </c>
+      <c r="ER22" s="6">
+        <v>102</v>
+      </c>
+      <c r="ES22" s="6">
+        <v>19</v>
+      </c>
+      <c r="ET22" s="6">
+        <v>84</v>
+      </c>
+      <c r="EU22" s="6">
+        <v>108</v>
+      </c>
+      <c r="EV22" s="6">
+        <v>12</v>
+      </c>
+      <c r="EW22" s="10"/>
+      <c r="EX22" s="10"/>
+      <c r="EY22" s="10"/>
     </row>
-    <row r="23" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:155" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>100</v>
       </c>
@@ -8996,40 +11600,223 @@
       <c r="CA23" s="4">
         <v>0</v>
       </c>
-      <c r="CO23" s="1">
+      <c r="CB23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CC23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CD23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CF23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CG23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CH23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CI23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CJ23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CM23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CN23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CO23" s="4">
+        <v>81</v>
+      </c>
+      <c r="CP23" s="4">
+        <v>95</v>
+      </c>
+      <c r="CQ23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CR23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CS23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CT23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CU23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CV23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CW23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CX23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CY23" s="4">
+        <v>0</v>
+      </c>
+      <c r="CZ23" s="4">
+        <v>0</v>
+      </c>
+      <c r="DA23" s="4">
+        <v>0</v>
+      </c>
+      <c r="DB23" s="4">
+        <v>0</v>
+      </c>
+      <c r="DC23" s="4">
+        <v>0</v>
+      </c>
+      <c r="DD23" s="4">
+        <v>0</v>
+      </c>
+      <c r="DE23" s="4">
+        <v>0</v>
+      </c>
+      <c r="DF23" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG23" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH23" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI23" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ23" s="4">
+        <v>0</v>
+      </c>
+      <c r="DK23" s="4">
+        <v>0</v>
+      </c>
+      <c r="DL23" s="4">
+        <v>0</v>
+      </c>
+      <c r="DM23" s="4">
+        <v>0</v>
+      </c>
+      <c r="DN23" s="9">
         <v>123</v>
       </c>
-      <c r="CP23" s="1">
+      <c r="DO23" s="9">
         <v>96</v>
       </c>
-      <c r="CZ23" s="1">
+      <c r="DP23" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ23" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR23" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS23" s="4">
+        <v>0</v>
+      </c>
+      <c r="DT23" s="4">
+        <v>9</v>
+      </c>
+      <c r="DU23" s="4">
+        <v>0</v>
+      </c>
+      <c r="DV23" s="4">
+        <v>0</v>
+      </c>
+      <c r="DW23" s="4">
+        <v>0</v>
+      </c>
+      <c r="DX23" s="4">
+        <v>0</v>
+      </c>
+      <c r="DY23" s="4">
         <v>4</v>
       </c>
-      <c r="DA23" s="1">
+      <c r="DZ23" s="1">
         <v>105</v>
       </c>
-      <c r="DB23" s="1">
+      <c r="EA23" s="1">
         <v>135</v>
       </c>
-      <c r="DC23" s="1">
+      <c r="EB23" s="1">
         <v>142</v>
       </c>
-      <c r="DD23" s="1">
+      <c r="EC23" s="1">
         <v>124</v>
       </c>
-      <c r="DE23" s="1">
+      <c r="ED23" s="1">
         <v>103</v>
       </c>
-      <c r="DF23" s="1">
+      <c r="EE23" s="1">
         <v>162</v>
       </c>
-      <c r="DG23" s="7"/>
-      <c r="DH23" s="1">
+      <c r="EF23" s="1">
+        <v>65</v>
+      </c>
+      <c r="EG23" s="1">
         <v>120</v>
       </c>
-      <c r="DI23" s="7"/>
+      <c r="EH23" s="7"/>
+      <c r="EI23" s="1">
+        <v>133</v>
+      </c>
+      <c r="EJ23" s="1">
+        <v>141</v>
+      </c>
+      <c r="EK23" s="1">
+        <v>122</v>
+      </c>
+      <c r="EL23" s="7"/>
+      <c r="EM23" s="1">
+        <v>14</v>
+      </c>
+      <c r="EN23" s="1">
+        <v>117</v>
+      </c>
+      <c r="EO23" s="4">
+        <v>0</v>
+      </c>
+      <c r="EP23" s="4">
+        <v>0</v>
+      </c>
+      <c r="EQ23" s="4">
+        <v>0</v>
+      </c>
+      <c r="ER23" s="4">
+        <v>0</v>
+      </c>
+      <c r="ES23" s="4">
+        <v>0</v>
+      </c>
+      <c r="ET23" s="4">
+        <v>0</v>
+      </c>
+      <c r="EU23" s="4">
+        <v>0</v>
+      </c>
+      <c r="EV23" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:113" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:155" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>101</v>
       </c>
@@ -9267,14 +12054,227 @@
       <c r="CA24" s="4">
         <v>0</v>
       </c>
-      <c r="CJ24" s="1">
+      <c r="CB24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CC24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CD24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CF24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CG24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CH24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CI24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CJ24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CM24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CN24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CO24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CP24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CQ24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CR24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CS24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CT24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CU24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CV24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CW24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CX24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CY24" s="4">
+        <v>0</v>
+      </c>
+      <c r="CZ24" s="4">
+        <v>0</v>
+      </c>
+      <c r="DA24" s="4">
+        <v>0</v>
+      </c>
+      <c r="DB24" s="4">
+        <v>0</v>
+      </c>
+      <c r="DC24" s="4">
+        <v>0</v>
+      </c>
+      <c r="DD24" s="4">
+        <v>0</v>
+      </c>
+      <c r="DE24" s="4">
+        <v>0</v>
+      </c>
+      <c r="DF24" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG24" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH24" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI24" s="4">
         <v>94</v>
       </c>
-      <c r="CZ24" s="10">
+      <c r="DJ24" s="4">
+        <v>0</v>
+      </c>
+      <c r="DK24" s="4">
+        <v>7</v>
+      </c>
+      <c r="DL24" s="4">
+        <v>0</v>
+      </c>
+      <c r="DM24" s="4">
+        <v>0</v>
+      </c>
+      <c r="DN24" s="4">
+        <v>0</v>
+      </c>
+      <c r="DO24" s="4">
+        <v>0</v>
+      </c>
+      <c r="DP24" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ24" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR24" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS24" s="4">
+        <v>0</v>
+      </c>
+      <c r="DT24" s="4">
+        <v>0</v>
+      </c>
+      <c r="DU24" s="4">
+        <v>0</v>
+      </c>
+      <c r="DV24" s="4">
+        <v>0</v>
+      </c>
+      <c r="DW24" s="4">
+        <v>0</v>
+      </c>
+      <c r="DX24" s="4">
+        <v>0</v>
+      </c>
+      <c r="DY24" s="4">
         <v>58</v>
       </c>
+      <c r="DZ24" s="4">
+        <v>0</v>
+      </c>
+      <c r="EA24" s="4">
+        <v>0</v>
+      </c>
+      <c r="EB24" s="4">
+        <v>0</v>
+      </c>
+      <c r="EC24" s="4">
+        <v>0</v>
+      </c>
+      <c r="ED24" s="4">
+        <v>0</v>
+      </c>
+      <c r="EE24" s="4">
+        <v>0</v>
+      </c>
+      <c r="EF24" s="4">
+        <v>1</v>
+      </c>
+      <c r="EG24" s="4">
+        <v>0</v>
+      </c>
+      <c r="EH24" s="4">
+        <v>0</v>
+      </c>
+      <c r="EI24" s="4">
+        <v>0</v>
+      </c>
+      <c r="EJ24" s="4">
+        <v>0</v>
+      </c>
+      <c r="EK24" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL24" s="4">
+        <v>0</v>
+      </c>
+      <c r="EM24" s="4">
+        <v>117</v>
+      </c>
+      <c r="EN24" s="4">
+        <v>0</v>
+      </c>
+      <c r="EO24" s="4">
+        <v>0</v>
+      </c>
+      <c r="EP24" s="4">
+        <v>0</v>
+      </c>
+      <c r="EQ24" s="4">
+        <v>0</v>
+      </c>
+      <c r="ER24" s="4">
+        <v>0</v>
+      </c>
+      <c r="ES24" s="4">
+        <v>0</v>
+      </c>
+      <c r="ET24" s="4">
+        <v>0</v>
+      </c>
+      <c r="EU24" s="4">
+        <v>0</v>
+      </c>
+      <c r="EV24" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:113" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:155" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>102</v>
       </c>
@@ -9512,8 +12512,227 @@
       <c r="CA25" s="4">
         <v>0</v>
       </c>
+      <c r="CB25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CC25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CD25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CE25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CF25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CG25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CH25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CI25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CJ25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CK25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CM25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CN25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CO25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CP25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CQ25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CR25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CS25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CT25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CU25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CV25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CW25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CX25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CY25" s="4">
+        <v>0</v>
+      </c>
+      <c r="CZ25" s="4">
+        <v>0</v>
+      </c>
+      <c r="DA25" s="4">
+        <v>0</v>
+      </c>
+      <c r="DB25" s="4">
+        <v>0</v>
+      </c>
+      <c r="DC25" s="4">
+        <v>0</v>
+      </c>
+      <c r="DD25" s="4">
+        <v>0</v>
+      </c>
+      <c r="DE25" s="4">
+        <v>0</v>
+      </c>
+      <c r="DF25" s="4">
+        <v>0</v>
+      </c>
+      <c r="DG25" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH25" s="4">
+        <v>0</v>
+      </c>
+      <c r="DI25" s="4">
+        <v>0</v>
+      </c>
+      <c r="DJ25" s="4">
+        <v>0</v>
+      </c>
+      <c r="DK25" s="4">
+        <v>15</v>
+      </c>
+      <c r="DL25" s="4">
+        <v>0</v>
+      </c>
+      <c r="DM25" s="4">
+        <v>0</v>
+      </c>
+      <c r="DN25" s="4">
+        <v>0</v>
+      </c>
+      <c r="DO25" s="4">
+        <v>0</v>
+      </c>
+      <c r="DP25" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ25" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR25" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS25" s="4">
+        <v>0</v>
+      </c>
+      <c r="DT25" s="4">
+        <v>0</v>
+      </c>
+      <c r="DU25" s="4">
+        <v>0</v>
+      </c>
+      <c r="DV25" s="4">
+        <v>0</v>
+      </c>
+      <c r="DW25" s="4">
+        <v>0</v>
+      </c>
+      <c r="DX25" s="4">
+        <v>0</v>
+      </c>
+      <c r="DY25" s="4">
+        <v>0</v>
+      </c>
+      <c r="DZ25" s="4">
+        <v>0</v>
+      </c>
+      <c r="EA25" s="4">
+        <v>0</v>
+      </c>
+      <c r="EB25" s="4">
+        <v>0</v>
+      </c>
+      <c r="EC25" s="4">
+        <v>0</v>
+      </c>
+      <c r="ED25" s="4">
+        <v>0</v>
+      </c>
+      <c r="EE25" s="4">
+        <v>0</v>
+      </c>
+      <c r="EF25" s="4">
+        <v>0</v>
+      </c>
+      <c r="EG25" s="4">
+        <v>0</v>
+      </c>
+      <c r="EH25" s="4">
+        <v>0</v>
+      </c>
+      <c r="EI25" s="4">
+        <v>0</v>
+      </c>
+      <c r="EJ25" s="4">
+        <v>0</v>
+      </c>
+      <c r="EK25" s="4">
+        <v>0</v>
+      </c>
+      <c r="EL25" s="4">
+        <v>0</v>
+      </c>
+      <c r="EM25" s="4">
+        <v>0</v>
+      </c>
+      <c r="EN25" s="4">
+        <v>0</v>
+      </c>
+      <c r="EO25" s="4">
+        <v>0</v>
+      </c>
+      <c r="EP25" s="4">
+        <v>0</v>
+      </c>
+      <c r="EQ25" s="4">
+        <v>0</v>
+      </c>
+      <c r="ER25" s="4">
+        <v>0</v>
+      </c>
+      <c r="ES25" s="4">
+        <v>0</v>
+      </c>
+      <c r="ET25" s="4">
+        <v>0</v>
+      </c>
+      <c r="EU25" s="4">
+        <v>0</v>
+      </c>
+      <c r="EV25" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:155" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>103</v>
       </c>
@@ -9752,7 +12971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:155" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>104</v>
       </c>
@@ -9991,7 +13210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:155" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>105</v>
       </c>
@@ -10230,7 +13449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:155" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>106</v>
       </c>
@@ -10469,7 +13688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:155" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>107</v>
       </c>
@@ -10708,7 +13927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:155" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>108</v>
       </c>
@@ -10947,7 +14166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:155" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>109</v>
       </c>
@@ -42495,9 +45714,240 @@
         <v>113</v>
       </c>
     </row>
+    <row r="164" spans="1:79" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="165" spans="1:79" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="166" spans="1:79" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="167" spans="1:79" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="168" spans="1:79" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="169" spans="1:79" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="170" spans="1:79" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="171" spans="1:79" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="172" spans="1:79" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="173" spans="1:79" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="174" spans="1:79" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="175" spans="1:79" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="176" spans="1:79" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>256</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="A1:E1 F1:K1 L1:Q1 R1:V1 W1:AB1 AC1:AH1 AI1:AN1 AO1:AT1 AU1:AZ1 BA1:BF1 BG1:BL1 BM1:BR1 BS1:BX1 BY1:CA1 A6:A12 A5 A14:A20 A13 A34:E34 A21 F34:K163 L34:Q163 R34:V163 W34:AB163 AC34:AH163 AI34:AN163 AO34:AT163 AU34:AZ163 BA34:BF163 BG34:BL163 BM34:BR163 BS34:BX163 BY34:CA163 A2:A4 A22:A33 A40:E40 A35:A38 C35:E38 A39 C39:E39 A46:E46 A41:A44 C41:E44 A45 C45:E45 A52:E52 A47:A50 C47:E50 A51 C51:E51 A58:E58 A53:A56 C53:E56 A57 C57:E57 A71 A59:A62 C59:E62 A63 C63:E63 A64:A66 C64:E66 A67 C67:E67 A68:A70 C68:E70 A76:E76 A72:A74 C72:E74 C71:E71 A75 C75:E75 A82:E82 A77:A80 C77:E80 A88:E88 A83:A86 C83:E86 A94:E94 A89:A92 C89:E92 A100:E100 A95:A98 C95:E98 A105 A101:A104 C101:E104 A109 A106:A108 C106:E108 A113 A110:A112 C110:E112 A118:E118 A114:A116 C114:E116 A124:E124 A119:A122 C119:E122 A130:E130 A125:A128 C125:E128 A136:E136 A131:A134 C131:E134 A142:E142 A137:A140 C137:E140 A147 A143:A146 C143:E146 A151 A148:A150 C148:E150 A155 A152:A154 C152:E154 A159 A156:A158 C156:E158 A163 A160:A162 C160:E162 C163:E163 C159:E159 C155:E155 C151:E151 C147:E147 A141 C141:E141 A117 C117:E117 C113:E113 C109:E109 C105:E105 A99 C99:E99 A93 C93:E93 A87 C87:E87 A81 C81:E81 A129 C129:E129 A135 C135:E135 A123 C123:E123" numberStoredAsText="1"/>
   </ignoredErrors>

--- a/public/analytics-data.xlsx
+++ b/public/analytics-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mona\Downloads\PhysicsWallahDashboard-Axio\axioP-x-PW-main\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9F0EDE6-766A-4185-A074-B9053D505840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245BCCDE-75CF-4349-95D0-A6FA11345C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12970,6 +12970,33 @@
       <c r="CA26" s="4">
         <v>0</v>
       </c>
+      <c r="CB26" s="4">
+        <v>10</v>
+      </c>
+      <c r="CD26" s="4">
+        <v>13</v>
+      </c>
+      <c r="CE26" s="4">
+        <v>13</v>
+      </c>
+      <c r="CG26" s="4">
+        <v>7</v>
+      </c>
+      <c r="CH26" s="4">
+        <v>4</v>
+      </c>
+      <c r="CV26" s="4">
+        <v>69</v>
+      </c>
+      <c r="CW26" s="4">
+        <v>57</v>
+      </c>
+      <c r="DA26" s="4">
+        <v>71</v>
+      </c>
+      <c r="DK26" s="4">
+        <v>69</v>
+      </c>
     </row>
     <row r="27" spans="1:155" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
@@ -13209,6 +13236,33 @@
       <c r="CA27" s="4">
         <v>0</v>
       </c>
+      <c r="CB27" s="4">
+        <v>10</v>
+      </c>
+      <c r="CD27" s="4">
+        <v>6</v>
+      </c>
+      <c r="CE27" s="4">
+        <v>10</v>
+      </c>
+      <c r="CG27" s="4">
+        <v>6</v>
+      </c>
+      <c r="CH27" s="4">
+        <v>4</v>
+      </c>
+      <c r="CV27" s="4">
+        <v>69</v>
+      </c>
+      <c r="CW27" s="4">
+        <v>57</v>
+      </c>
+      <c r="DA27" s="4">
+        <v>0</v>
+      </c>
+      <c r="DK27" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:155" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -13448,6 +13502,33 @@
       <c r="CA28" s="4">
         <v>0</v>
       </c>
+      <c r="CB28" s="4">
+        <v>10</v>
+      </c>
+      <c r="CD28" s="4">
+        <v>6</v>
+      </c>
+      <c r="CE28" s="4">
+        <v>10</v>
+      </c>
+      <c r="CG28" s="4">
+        <v>6</v>
+      </c>
+      <c r="CH28" s="4">
+        <v>4</v>
+      </c>
+      <c r="CV28" s="4">
+        <v>69</v>
+      </c>
+      <c r="CW28" s="4">
+        <v>57</v>
+      </c>
+      <c r="DA28" s="4">
+        <v>0</v>
+      </c>
+      <c r="DK28" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:155" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -13687,6 +13768,33 @@
       <c r="CA29" s="4">
         <v>0</v>
       </c>
+      <c r="CB29" s="4">
+        <v>100</v>
+      </c>
+      <c r="CD29" s="4">
+        <v>100</v>
+      </c>
+      <c r="CE29" s="4">
+        <v>100</v>
+      </c>
+      <c r="CG29" s="4">
+        <v>100</v>
+      </c>
+      <c r="CH29" s="4">
+        <v>100</v>
+      </c>
+      <c r="CV29" s="4">
+        <v>100</v>
+      </c>
+      <c r="CW29" s="4">
+        <v>100</v>
+      </c>
+      <c r="DA29" s="4">
+        <v>100</v>
+      </c>
+      <c r="DK29" s="4">
+        <v>100</v>
+      </c>
     </row>
     <row r="30" spans="1:155" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
@@ -13926,6 +14034,22 @@
       <c r="CA30" s="4">
         <v>0</v>
       </c>
+      <c r="CB30" s="4">
+        <v>10</v>
+      </c>
+      <c r="CD30" s="4">
+        <v>6</v>
+      </c>
+      <c r="CE30" s="4">
+        <v>10</v>
+      </c>
+      <c r="CG30" s="4"/>
+      <c r="CH30" s="4">
+        <v>4</v>
+      </c>
+      <c r="CW30" s="4">
+        <v>57</v>
+      </c>
     </row>
     <row r="31" spans="1:155" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
@@ -14164,6 +14288,12 @@
       </c>
       <c r="CA31" s="4">
         <v>0</v>
+      </c>
+      <c r="CG31" s="4">
+        <v>6</v>
+      </c>
+      <c r="CV31" s="4">
+        <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:155" x14ac:dyDescent="0.3">

--- a/public/analytics-data.xlsx
+++ b/public/analytics-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mona\Downloads\PhysicsWallahDashboard-Axio\axioP-x-PW-main\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245BCCDE-75CF-4349-95D0-A6FA11345C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7CF84D-A6FA-4104-9014-54233120067B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10312" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10266" uniqueCount="257">
   <si>
     <t>Date</t>
   </si>
@@ -803,42 +803,6 @@
   <si>
     <t>Report_Dec_Platform_Facebook_RemovalRate</t>
   </si>
-  <si>
-    <t>Report_Jan_Week1_DateRange</t>
-  </si>
-  <si>
-    <t>Report_Jan_Week1_Sent</t>
-  </si>
-  <si>
-    <t>Report_Jan_Week1_Approved</t>
-  </si>
-  <si>
-    <t>Report_Jan_Week1_Removed</t>
-  </si>
-  <si>
-    <t>Report_Jan_Week1_Pending</t>
-  </si>
-  <si>
-    <t>Report_Jan_Week1_RemovalRate</t>
-  </si>
-  <si>
-    <t>Report_Jan_Week2_DateRange</t>
-  </si>
-  <si>
-    <t>Report_Jan_Week2_Sent</t>
-  </si>
-  <si>
-    <t>Report_Jan_Week2_Approved</t>
-  </si>
-  <si>
-    <t>Report_Jan_Week2_Removed</t>
-  </si>
-  <si>
-    <t>Report_Jan_Week2_Pending</t>
-  </si>
-  <si>
-    <t>Report_Jan_Week2_RemovalRate</t>
-  </si>
 </sst>
 </file>
 
@@ -1314,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:EY209"/>
+  <dimension ref="A1:EY163"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.5" customWidth="1"/>
@@ -45842,236 +45806,6 @@
       </c>
       <c r="CA163" t="s">
         <v>113</v>
-      </c>
-    </row>
-    <row r="164" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="A164" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="165" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="A165" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="166" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="A166" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="167" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="A167" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="168" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="A168" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="169" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="A169" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="170" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="A170" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="171" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="A171" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="172" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="A172" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="173" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="A173" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="174" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="A174" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="175" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="A175" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="176" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="A176" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A177" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A178" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A179" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A180" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A181" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A182" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A183" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A184" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A185" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A186" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A187" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A188" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A189" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A190" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A191" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A192" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A193" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A194" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A195" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A196" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A197" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A198" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A199" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A200" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A201" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A202" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A203" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A204" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A205" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A206" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A207" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A208" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A209" t="s">
-        <v>256</v>
       </c>
     </row>
   </sheetData>

--- a/public/analytics-data.xlsx
+++ b/public/analytics-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mona\Downloads\PhysicsWallahDashboard-Axio\axioP-x-PW-main\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7CF84D-A6FA-4104-9014-54233120067B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1710AD6D-CFB0-4F74-B572-96F39441D2D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -911,7 +911,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -938,6 +938,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1285,7 +1288,7 @@
     <col min="80" max="80" width="10.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:153" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:152" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1737,16 +1740,13 @@
         <v>46109</v>
       </c>
       <c r="EU1" s="5">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="EV1" s="5">
-        <v>46111</v>
-      </c>
-      <c r="EW1" s="5">
         <v>46112</v>
       </c>
     </row>
-    <row r="2" spans="1:153" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:152" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>79</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:153" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:152" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>80</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:153" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:152" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>81</v>
       </c>
@@ -3120,7 +3120,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:153" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:152" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>82</v>
       </c>
@@ -3578,7 +3578,7 @@
         <v>96.67</v>
       </c>
     </row>
-    <row r="6" spans="1:153" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:152" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>83</v>
       </c>
@@ -4036,7 +4036,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:153" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:152" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>84</v>
       </c>
@@ -4494,7 +4494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:153" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:152" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -4952,7 +4952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:153" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:152" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>86</v>
       </c>
@@ -5410,7 +5410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:153" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:152" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>87</v>
       </c>
@@ -5864,9 +5864,11 @@
       <c r="EU10" s="6">
         <v>20</v>
       </c>
-      <c r="EV10" s="6"/>
+      <c r="EV10" s="6">
+        <v>8</v>
+      </c>
     </row>
-    <row r="11" spans="1:153" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:152" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>88</v>
       </c>
@@ -6320,8 +6322,11 @@
       <c r="EU11" s="6">
         <v>20</v>
       </c>
+      <c r="EV11" s="11">
+        <v>1</v>
+      </c>
     </row>
-    <row r="12" spans="1:153" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:152" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>89</v>
       </c>
@@ -6775,8 +6780,11 @@
       <c r="EU12" s="1">
         <v>20</v>
       </c>
+      <c r="EV12" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="1:153" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:152" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>90</v>
       </c>
@@ -7230,8 +7238,11 @@
       <c r="EU13">
         <v>100</v>
       </c>
+      <c r="EV13" s="1">
+        <v>100</v>
+      </c>
     </row>
-    <row r="14" spans="1:153" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:152" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -7684,10 +7695,10 @@
         <v>20</v>
       </c>
       <c r="EV14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:153" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:152" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>92</v>
       </c>
@@ -8145,7 +8156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:153" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:152" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>93</v>
       </c>
@@ -10432,7 +10443,7 @@
         <v>108</v>
       </c>
       <c r="EV20" s="9">
-        <v>12</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:155" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -10890,7 +10901,7 @@
         <v>100</v>
       </c>
       <c r="EV21">
-        <v>10.26</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:155" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -11320,7 +11331,7 @@
         <v>108</v>
       </c>
       <c r="EV22" s="6">
-        <v>12</v>
+        <v>117</v>
       </c>
       <c r="EW22" s="10"/>
       <c r="EX22" s="10"/>

--- a/public/analytics-data.xlsx
+++ b/public/analytics-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mona\Downloads\PhysicsWallahDashboard-Axio\axioP-x-PW-main\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1710AD6D-CFB0-4F74-B572-96F39441D2D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267D86A3-8FFD-4DF5-A92B-1CE19C762A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -911,7 +911,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -938,9 +938,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3117,7 +3114,7 @@
         <v>62</v>
       </c>
       <c r="EV4" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:152" x14ac:dyDescent="0.3">
@@ -3575,7 +3572,7 @@
         <v>100</v>
       </c>
       <c r="EV5">
-        <v>96.67</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:152" x14ac:dyDescent="0.3">
@@ -4033,7 +4030,7 @@
         <v>62</v>
       </c>
       <c r="EV6" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:152" x14ac:dyDescent="0.3">
@@ -6322,7 +6319,7 @@
       <c r="EU11" s="6">
         <v>20</v>
       </c>
-      <c r="EV11" s="11">
+      <c r="EV11" s="1">
         <v>1</v>
       </c>
     </row>

--- a/public/analytics-data.xlsx
+++ b/public/analytics-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mona\Downloads\PhysicsWallahDashboard-Axio\axioP-x-PW-main\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267D86A3-8FFD-4DF5-A92B-1CE19C762A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7E0D36B-28AC-420C-BD41-D8D7F8695933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10329,7 +10329,7 @@
         <v>153</v>
       </c>
       <c r="DK20" s="9">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="DL20" s="9">
         <v>103</v>
@@ -10344,7 +10344,7 @@
         <v>96</v>
       </c>
       <c r="DP20" s="9">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="DQ20" s="9">
         <v>100</v>
@@ -10356,7 +10356,7 @@
         <v>119</v>
       </c>
       <c r="DT20" s="9">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="DU20" s="9">
         <v>108</v>
@@ -10404,7 +10404,7 @@
         <v>133</v>
       </c>
       <c r="EJ20" s="9">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="EK20" s="9">
         <v>122</v>
@@ -10419,7 +10419,7 @@
         <v>117</v>
       </c>
       <c r="EO20" s="9">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="EP20" s="9">
         <v>113</v>
@@ -10431,7 +10431,7 @@
         <v>102</v>
       </c>
       <c r="ES20" s="9">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="ET20" s="9">
         <v>84</v>
@@ -10802,7 +10802,7 @@
         <v>100</v>
       </c>
       <c r="DP21">
-        <v>89.89</v>
+        <v>96.63</v>
       </c>
       <c r="DQ21">
         <v>100</v>
@@ -10814,7 +10814,7 @@
         <v>100</v>
       </c>
       <c r="DT21">
-        <v>79.23</v>
+        <v>96.92</v>
       </c>
       <c r="DU21">
         <v>100</v>
@@ -10862,7 +10862,7 @@
         <v>100</v>
       </c>
       <c r="EJ21">
-        <v>99.3</v>
+        <v>100</v>
       </c>
       <c r="EK21">
         <v>100</v>
@@ -10877,7 +10877,7 @@
         <v>100</v>
       </c>
       <c r="EO21">
-        <v>42.61</v>
+        <v>100</v>
       </c>
       <c r="EP21">
         <v>100</v>
@@ -10889,7 +10889,7 @@
         <v>100</v>
       </c>
       <c r="ES21">
-        <v>17.59</v>
+        <v>100</v>
       </c>
       <c r="ET21">
         <v>100</v>
@@ -11256,7 +11256,7 @@
       <c r="DN22" s="7"/>
       <c r="DO22" s="7"/>
       <c r="DP22" s="1">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="DQ22" s="1">
         <v>100</v>
@@ -11307,7 +11307,7 @@
       <c r="EM22" s="7"/>
       <c r="EN22" s="7"/>
       <c r="EO22" s="1">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="EP22" s="1">
         <v>113</v>
@@ -11319,7 +11319,7 @@
         <v>102</v>
       </c>
       <c r="ES22" s="6">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="ET22" s="6">
         <v>84</v>
@@ -11751,7 +11751,7 @@
         <v>133</v>
       </c>
       <c r="EJ23" s="1">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="EK23" s="1">
         <v>122</v>

--- a/public/analytics-data.xlsx
+++ b/public/analytics-data.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mona\Downloads\PhysicsWallahDashboard-Axio\axioP-x-PW-main\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7E0D36B-28AC-420C-BD41-D8D7F8695933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9142D3CC-490B-44DB-9863-5CB43DA0AAD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Analytics Data" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -911,7 +912,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -938,6 +939,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1278,14 +1282,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:EY163"/>
+  <dimension ref="A1:FV163"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.5" customWidth="1"/>
     <col min="80" max="80" width="10.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:152" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:178" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1742,8 +1746,86 @@
       <c r="EV1" s="5">
         <v>46112</v>
       </c>
+      <c r="EW1" s="5">
+        <v>46113</v>
+      </c>
+      <c r="EX1" s="5">
+        <v>46114</v>
+      </c>
+      <c r="EY1" s="5">
+        <v>46115</v>
+      </c>
+      <c r="EZ1" s="5">
+        <v>46116</v>
+      </c>
+      <c r="FA1" s="5">
+        <v>46118</v>
+      </c>
+      <c r="FB1" s="5">
+        <v>46119</v>
+      </c>
+      <c r="FC1" s="5">
+        <v>46120</v>
+      </c>
+      <c r="FD1" s="5">
+        <v>46121</v>
+      </c>
+      <c r="FE1" s="5">
+        <v>46122</v>
+      </c>
+      <c r="FF1" s="5">
+        <v>46123</v>
+      </c>
+      <c r="FG1" s="5">
+        <v>46125</v>
+      </c>
+      <c r="FH1" s="5">
+        <v>46126</v>
+      </c>
+      <c r="FI1" s="5">
+        <v>46127</v>
+      </c>
+      <c r="FJ1" s="5">
+        <v>46128</v>
+      </c>
+      <c r="FK1" s="5">
+        <v>46129</v>
+      </c>
+      <c r="FL1" s="5">
+        <v>46130</v>
+      </c>
+      <c r="FM1" s="5">
+        <v>46132</v>
+      </c>
+      <c r="FN1" s="5">
+        <v>46133</v>
+      </c>
+      <c r="FO1" s="5">
+        <v>46134</v>
+      </c>
+      <c r="FP1" s="5">
+        <v>46135</v>
+      </c>
+      <c r="FQ1" s="5">
+        <v>46136</v>
+      </c>
+      <c r="FR1" s="5">
+        <v>46137</v>
+      </c>
+      <c r="FS1" s="5">
+        <v>46139</v>
+      </c>
+      <c r="FT1" s="5">
+        <v>46140</v>
+      </c>
+      <c r="FU1" s="5">
+        <v>46141</v>
+      </c>
+      <c r="FV1" s="5">
+        <v>46142</v>
+      </c>
     </row>
-    <row r="2" spans="1:152" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:178" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>79</v>
       </c>
@@ -2200,8 +2282,86 @@
       <c r="EV2" s="6">
         <v>30</v>
       </c>
+      <c r="EW2" s="6">
+        <v>25</v>
+      </c>
+      <c r="EX2" s="6">
+        <v>23</v>
+      </c>
+      <c r="EY2" s="6">
+        <v>34</v>
+      </c>
+      <c r="EZ2" s="6">
+        <v>76</v>
+      </c>
+      <c r="FA2" s="6">
+        <v>73</v>
+      </c>
+      <c r="FB2" s="6">
+        <v>58</v>
+      </c>
+      <c r="FC2" s="6">
+        <v>1</v>
+      </c>
+      <c r="FD2" s="6">
+        <v>20</v>
+      </c>
+      <c r="FE2" s="6">
+        <v>28</v>
+      </c>
+      <c r="FF2" s="6">
+        <v>56</v>
+      </c>
+      <c r="FG2" s="6">
+        <v>67</v>
+      </c>
+      <c r="FH2" s="6">
+        <v>34</v>
+      </c>
+      <c r="FI2" s="6">
+        <v>93</v>
+      </c>
+      <c r="FJ2" s="6">
+        <v>12</v>
+      </c>
+      <c r="FK2" s="6">
+        <v>20</v>
+      </c>
+      <c r="FL2" s="6">
+        <v>34</v>
+      </c>
+      <c r="FM2" s="6">
+        <v>40</v>
+      </c>
+      <c r="FN2" s="6">
+        <v>32</v>
+      </c>
+      <c r="FO2" s="6">
+        <v>25</v>
+      </c>
+      <c r="FP2" s="6">
+        <v>59</v>
+      </c>
+      <c r="FQ2" s="6">
+        <v>17</v>
+      </c>
+      <c r="FR2" s="6">
+        <v>33</v>
+      </c>
+      <c r="FS2" s="6">
+        <v>21</v>
+      </c>
+      <c r="FT2" s="6">
+        <v>14</v>
+      </c>
+      <c r="FU2" s="6">
+        <v>46</v>
+      </c>
+      <c r="FV2" s="6">
+        <v>33</v>
+      </c>
     </row>
-    <row r="3" spans="1:152" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:178" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>80</v>
       </c>
@@ -2658,8 +2818,86 @@
       <c r="EV3" s="6">
         <v>30</v>
       </c>
+      <c r="EW3" s="6">
+        <v>25</v>
+      </c>
+      <c r="EX3" s="6">
+        <v>20</v>
+      </c>
+      <c r="EY3" s="6">
+        <v>34</v>
+      </c>
+      <c r="EZ3" s="6">
+        <v>3</v>
+      </c>
+      <c r="FA3" s="6">
+        <v>73</v>
+      </c>
+      <c r="FB3" s="6">
+        <v>58</v>
+      </c>
+      <c r="FC3" s="6">
+        <v>1</v>
+      </c>
+      <c r="FD3" s="6">
+        <v>20</v>
+      </c>
+      <c r="FE3" s="6">
+        <v>14</v>
+      </c>
+      <c r="FF3" s="6">
+        <v>56</v>
+      </c>
+      <c r="FG3" s="6">
+        <v>67</v>
+      </c>
+      <c r="FH3" s="6">
+        <v>34</v>
+      </c>
+      <c r="FI3" s="6">
+        <v>81</v>
+      </c>
+      <c r="FJ3" s="6">
+        <v>12</v>
+      </c>
+      <c r="FK3" s="6">
+        <v>20</v>
+      </c>
+      <c r="FL3" s="6">
+        <v>34</v>
+      </c>
+      <c r="FM3" s="6">
+        <v>40</v>
+      </c>
+      <c r="FN3" s="6">
+        <v>32</v>
+      </c>
+      <c r="FO3" s="6">
+        <v>22</v>
+      </c>
+      <c r="FP3" s="6">
+        <v>59</v>
+      </c>
+      <c r="FQ3" s="6">
+        <v>7</v>
+      </c>
+      <c r="FR3" s="6">
+        <v>33</v>
+      </c>
+      <c r="FS3" s="6">
+        <v>4</v>
+      </c>
+      <c r="FT3" s="6">
+        <v>14</v>
+      </c>
+      <c r="FU3" s="6">
+        <v>46</v>
+      </c>
+      <c r="FV3" s="6">
+        <v>33</v>
+      </c>
     </row>
-    <row r="4" spans="1:152" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:178" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>81</v>
       </c>
@@ -3116,8 +3354,86 @@
       <c r="EV4" s="1">
         <v>30</v>
       </c>
+      <c r="EW4" s="6">
+        <v>25</v>
+      </c>
+      <c r="EX4" s="6">
+        <v>20</v>
+      </c>
+      <c r="EY4" s="6">
+        <v>34</v>
+      </c>
+      <c r="EZ4" s="6">
+        <v>3</v>
+      </c>
+      <c r="FA4" s="6">
+        <v>73</v>
+      </c>
+      <c r="FB4" s="6">
+        <v>58</v>
+      </c>
+      <c r="FC4" s="6">
+        <v>1</v>
+      </c>
+      <c r="FD4" s="6">
+        <v>20</v>
+      </c>
+      <c r="FE4" s="6">
+        <v>14</v>
+      </c>
+      <c r="FF4" s="6">
+        <v>56</v>
+      </c>
+      <c r="FG4" s="6">
+        <v>67</v>
+      </c>
+      <c r="FH4" s="6">
+        <v>34</v>
+      </c>
+      <c r="FI4" s="6">
+        <v>81</v>
+      </c>
+      <c r="FJ4" s="6">
+        <v>12</v>
+      </c>
+      <c r="FK4" s="6">
+        <v>20</v>
+      </c>
+      <c r="FL4" s="6">
+        <v>34</v>
+      </c>
+      <c r="FM4" s="6">
+        <v>40</v>
+      </c>
+      <c r="FN4" s="6">
+        <v>32</v>
+      </c>
+      <c r="FO4" s="6">
+        <v>22</v>
+      </c>
+      <c r="FP4" s="6">
+        <v>59</v>
+      </c>
+      <c r="FQ4" s="6">
+        <v>7</v>
+      </c>
+      <c r="FR4" s="6">
+        <v>33</v>
+      </c>
+      <c r="FS4" s="6">
+        <v>4</v>
+      </c>
+      <c r="FT4" s="6">
+        <v>14</v>
+      </c>
+      <c r="FU4" s="6">
+        <v>46</v>
+      </c>
+      <c r="FV4" s="6">
+        <v>33</v>
+      </c>
     </row>
-    <row r="5" spans="1:152" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:178" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>82</v>
       </c>
@@ -3574,8 +3890,86 @@
       <c r="EV5">
         <v>100</v>
       </c>
+      <c r="EW5">
+        <v>100</v>
+      </c>
+      <c r="EX5">
+        <v>100</v>
+      </c>
+      <c r="EY5">
+        <v>100</v>
+      </c>
+      <c r="EZ5">
+        <v>100</v>
+      </c>
+      <c r="FA5">
+        <v>100</v>
+      </c>
+      <c r="FB5">
+        <v>100</v>
+      </c>
+      <c r="FC5">
+        <v>100</v>
+      </c>
+      <c r="FD5">
+        <v>100</v>
+      </c>
+      <c r="FE5">
+        <v>100</v>
+      </c>
+      <c r="FF5">
+        <v>100</v>
+      </c>
+      <c r="FG5">
+        <v>100</v>
+      </c>
+      <c r="FH5">
+        <v>100</v>
+      </c>
+      <c r="FI5">
+        <v>100</v>
+      </c>
+      <c r="FJ5">
+        <v>100</v>
+      </c>
+      <c r="FK5">
+        <v>100</v>
+      </c>
+      <c r="FL5">
+        <v>100</v>
+      </c>
+      <c r="FM5">
+        <v>100</v>
+      </c>
+      <c r="FN5">
+        <v>100</v>
+      </c>
+      <c r="FO5">
+        <v>100</v>
+      </c>
+      <c r="FP5">
+        <v>100</v>
+      </c>
+      <c r="FQ5">
+        <v>100</v>
+      </c>
+      <c r="FR5">
+        <v>100</v>
+      </c>
+      <c r="FS5">
+        <v>100</v>
+      </c>
+      <c r="FT5">
+        <v>100</v>
+      </c>
+      <c r="FU5">
+        <v>100</v>
+      </c>
+      <c r="FV5">
+        <v>100</v>
+      </c>
     </row>
-    <row r="6" spans="1:152" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:178" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>83</v>
       </c>
@@ -4032,8 +4426,84 @@
       <c r="EV6" s="1">
         <v>30</v>
       </c>
+      <c r="EW6" s="1">
+        <v>25</v>
+      </c>
+      <c r="EX6" s="1">
+        <v>20</v>
+      </c>
+      <c r="EY6" s="1">
+        <v>34</v>
+      </c>
+      <c r="EZ6" s="1">
+        <v>3</v>
+      </c>
+      <c r="FA6" s="1">
+        <v>73</v>
+      </c>
+      <c r="FB6" s="1">
+        <v>58</v>
+      </c>
+      <c r="FC6" s="1">
+        <v>1</v>
+      </c>
+      <c r="FD6" s="1">
+        <v>20</v>
+      </c>
+      <c r="FE6" s="1">
+        <v>14</v>
+      </c>
+      <c r="FF6" s="1">
+        <v>56</v>
+      </c>
+      <c r="FG6" s="1">
+        <v>67</v>
+      </c>
+      <c r="FH6" s="1">
+        <v>34</v>
+      </c>
+      <c r="FI6" s="1">
+        <v>81</v>
+      </c>
+      <c r="FJ6" s="1">
+        <v>12</v>
+      </c>
+      <c r="FK6" s="1">
+        <v>19</v>
+      </c>
+      <c r="FL6" s="1">
+        <v>34</v>
+      </c>
+      <c r="FM6" s="1">
+        <v>38</v>
+      </c>
+      <c r="FN6" s="7"/>
+      <c r="FO6" s="1">
+        <v>22</v>
+      </c>
+      <c r="FP6" s="1">
+        <v>59</v>
+      </c>
+      <c r="FQ6" s="1">
+        <v>7</v>
+      </c>
+      <c r="FR6" s="1">
+        <v>33</v>
+      </c>
+      <c r="FS6" s="1">
+        <v>4</v>
+      </c>
+      <c r="FT6" s="1">
+        <v>14</v>
+      </c>
+      <c r="FU6" s="1">
+        <v>46</v>
+      </c>
+      <c r="FV6" s="1">
+        <v>33</v>
+      </c>
     </row>
-    <row r="7" spans="1:152" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:178" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>84</v>
       </c>
@@ -4490,8 +4960,18 @@
       <c r="EV7">
         <v>0</v>
       </c>
+      <c r="FK7" s="1">
+        <v>1</v>
+      </c>
+      <c r="FL7" s="7"/>
+      <c r="FM7" s="1">
+        <v>2</v>
+      </c>
+      <c r="FN7" s="1">
+        <v>32</v>
+      </c>
     </row>
-    <row r="8" spans="1:152" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:178" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -4949,7 +5429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:152" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:178" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>86</v>
       </c>
@@ -5407,7 +5887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:152" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:178" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>87</v>
       </c>
@@ -5864,8 +6344,86 @@
       <c r="EV10" s="6">
         <v>8</v>
       </c>
+      <c r="EW10" s="6">
+        <v>26</v>
+      </c>
+      <c r="EX10" s="6">
+        <v>38</v>
+      </c>
+      <c r="EY10" s="6">
+        <v>3</v>
+      </c>
+      <c r="EZ10" s="6">
+        <v>1</v>
+      </c>
+      <c r="FA10" s="6">
+        <v>9</v>
+      </c>
+      <c r="FB10" s="6">
+        <v>1</v>
+      </c>
+      <c r="FC10" s="6">
+        <v>8</v>
+      </c>
+      <c r="FD10" s="6">
+        <v>1</v>
+      </c>
+      <c r="FE10" s="6">
+        <v>14</v>
+      </c>
+      <c r="FF10" s="6">
+        <v>13</v>
+      </c>
+      <c r="FG10" s="6">
+        <v>22</v>
+      </c>
+      <c r="FH10" s="6">
+        <v>16</v>
+      </c>
+      <c r="FI10" s="6">
+        <v>21</v>
+      </c>
+      <c r="FJ10" s="6">
+        <v>18</v>
+      </c>
+      <c r="FK10" s="6">
+        <v>19</v>
+      </c>
+      <c r="FL10" s="6">
+        <v>9</v>
+      </c>
+      <c r="FM10" s="6">
+        <v>4</v>
+      </c>
+      <c r="FN10" s="6">
+        <v>14</v>
+      </c>
+      <c r="FO10" s="6">
+        <v>15</v>
+      </c>
+      <c r="FP10" s="6">
+        <v>14</v>
+      </c>
+      <c r="FQ10" s="6">
+        <v>13</v>
+      </c>
+      <c r="FR10" s="6">
+        <v>19</v>
+      </c>
+      <c r="FS10" s="6">
+        <v>17</v>
+      </c>
+      <c r="FT10" s="6">
+        <v>16</v>
+      </c>
+      <c r="FU10" s="6">
+        <v>15</v>
+      </c>
+      <c r="FV10" s="6">
+        <v>11</v>
+      </c>
     </row>
-    <row r="11" spans="1:152" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:178" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>88</v>
       </c>
@@ -6322,8 +6880,86 @@
       <c r="EV11" s="1">
         <v>1</v>
       </c>
+      <c r="EW11" s="6">
+        <v>5</v>
+      </c>
+      <c r="EX11" s="6">
+        <v>15</v>
+      </c>
+      <c r="EY11" s="6">
+        <v>1</v>
+      </c>
+      <c r="EZ11" s="6">
+        <v>1</v>
+      </c>
+      <c r="FA11" s="6">
+        <v>7</v>
+      </c>
+      <c r="FB11" s="6">
+        <v>1</v>
+      </c>
+      <c r="FC11" s="6">
+        <v>7</v>
+      </c>
+      <c r="FD11" s="6">
+        <v>1</v>
+      </c>
+      <c r="FE11" s="6">
+        <v>8</v>
+      </c>
+      <c r="FF11" s="6">
+        <v>12</v>
+      </c>
+      <c r="FG11" s="6">
+        <v>9</v>
+      </c>
+      <c r="FH11" s="6">
+        <v>16</v>
+      </c>
+      <c r="FI11" s="6">
+        <v>14</v>
+      </c>
+      <c r="FJ11" s="6">
+        <v>18</v>
+      </c>
+      <c r="FK11" s="6">
+        <v>15</v>
+      </c>
+      <c r="FL11" s="6">
+        <v>8</v>
+      </c>
+      <c r="FM11" s="6">
+        <v>4</v>
+      </c>
+      <c r="FN11" s="6">
+        <v>8</v>
+      </c>
+      <c r="FO11" s="6">
+        <v>2</v>
+      </c>
+      <c r="FP11" s="6">
+        <v>2</v>
+      </c>
+      <c r="FQ11" s="6">
+        <v>10</v>
+      </c>
+      <c r="FR11" s="6">
+        <v>2</v>
+      </c>
+      <c r="FS11" s="6">
+        <v>3</v>
+      </c>
+      <c r="FT11" s="6">
+        <v>16</v>
+      </c>
+      <c r="FU11" s="6">
+        <v>12</v>
+      </c>
+      <c r="FV11" s="6">
+        <v>9</v>
+      </c>
     </row>
-    <row r="12" spans="1:152" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:178" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>89</v>
       </c>
@@ -6780,8 +7416,84 @@
       <c r="EV12" s="1">
         <v>1</v>
       </c>
+      <c r="EW12" s="1">
+        <v>5</v>
+      </c>
+      <c r="EX12" s="1">
+        <v>15</v>
+      </c>
+      <c r="EY12" s="1">
+        <v>1</v>
+      </c>
+      <c r="EZ12" s="1">
+        <v>1</v>
+      </c>
+      <c r="FA12" s="1">
+        <v>7</v>
+      </c>
+      <c r="FB12" s="1">
+        <v>1</v>
+      </c>
+      <c r="FC12" s="1">
+        <v>7</v>
+      </c>
+      <c r="FD12" s="1">
+        <v>1</v>
+      </c>
+      <c r="FE12" s="1">
+        <v>8</v>
+      </c>
+      <c r="FF12" s="1">
+        <v>12</v>
+      </c>
+      <c r="FG12" s="1">
+        <v>9</v>
+      </c>
+      <c r="FH12" s="1">
+        <v>16</v>
+      </c>
+      <c r="FI12" s="1">
+        <v>14</v>
+      </c>
+      <c r="FJ12" s="1">
+        <v>18</v>
+      </c>
+      <c r="FK12" s="1">
+        <v>15</v>
+      </c>
+      <c r="FL12" s="1">
+        <v>8</v>
+      </c>
+      <c r="FM12" s="1">
+        <v>4</v>
+      </c>
+      <c r="FN12" s="1">
+        <v>8</v>
+      </c>
+      <c r="FO12" s="1">
+        <v>2</v>
+      </c>
+      <c r="FP12" s="1">
+        <v>2</v>
+      </c>
+      <c r="FQ12" s="1">
+        <v>10</v>
+      </c>
+      <c r="FR12" s="1">
+        <v>2</v>
+      </c>
+      <c r="FS12" s="1">
+        <v>3</v>
+      </c>
+      <c r="FT12" s="1">
+        <v>4</v>
+      </c>
+      <c r="FU12" s="1">
+        <v>7</v>
+      </c>
+      <c r="FV12" s="10"/>
     </row>
-    <row r="13" spans="1:152" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:178" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>90</v>
       </c>
@@ -7238,8 +7950,86 @@
       <c r="EV13" s="1">
         <v>100</v>
       </c>
+      <c r="EW13">
+        <v>100</v>
+      </c>
+      <c r="EX13" s="1">
+        <v>100</v>
+      </c>
+      <c r="EY13">
+        <v>100</v>
+      </c>
+      <c r="EZ13" s="1">
+        <v>100</v>
+      </c>
+      <c r="FA13">
+        <v>100</v>
+      </c>
+      <c r="FB13" s="1">
+        <v>100</v>
+      </c>
+      <c r="FC13">
+        <v>100</v>
+      </c>
+      <c r="FD13" s="1">
+        <v>100</v>
+      </c>
+      <c r="FE13">
+        <v>100</v>
+      </c>
+      <c r="FF13" s="1">
+        <v>100</v>
+      </c>
+      <c r="FG13">
+        <v>100</v>
+      </c>
+      <c r="FH13" s="1">
+        <v>100</v>
+      </c>
+      <c r="FI13">
+        <v>100</v>
+      </c>
+      <c r="FJ13" s="1">
+        <v>100</v>
+      </c>
+      <c r="FK13">
+        <v>100</v>
+      </c>
+      <c r="FL13" s="1">
+        <v>100</v>
+      </c>
+      <c r="FM13">
+        <v>100</v>
+      </c>
+      <c r="FN13" s="1">
+        <v>100</v>
+      </c>
+      <c r="FO13">
+        <v>100</v>
+      </c>
+      <c r="FP13" s="1">
+        <v>100</v>
+      </c>
+      <c r="FQ13">
+        <v>100</v>
+      </c>
+      <c r="FR13" s="1">
+        <v>100</v>
+      </c>
+      <c r="FS13">
+        <v>100</v>
+      </c>
+      <c r="FT13" s="1">
+        <v>25</v>
+      </c>
+      <c r="FU13" s="1">
+        <v>58.33</v>
+      </c>
+      <c r="FV13" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:152" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:178" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -7694,8 +8484,81 @@
       <c r="EV14" s="1">
         <v>1</v>
       </c>
+      <c r="EW14" s="1">
+        <v>5</v>
+      </c>
+      <c r="EX14" s="1">
+        <v>15</v>
+      </c>
+      <c r="EY14" s="1">
+        <v>1</v>
+      </c>
+      <c r="EZ14" s="1">
+        <v>1</v>
+      </c>
+      <c r="FA14" s="1">
+        <v>7</v>
+      </c>
+      <c r="FB14" s="1">
+        <v>1</v>
+      </c>
+      <c r="FC14" s="1">
+        <v>7</v>
+      </c>
+      <c r="FD14" s="1">
+        <v>1</v>
+      </c>
+      <c r="FE14" s="1">
+        <v>8</v>
+      </c>
+      <c r="FF14" s="1">
+        <v>12</v>
+      </c>
+      <c r="FG14" s="1">
+        <v>6</v>
+      </c>
+      <c r="FH14" s="7"/>
+      <c r="FI14" s="1">
+        <v>9</v>
+      </c>
+      <c r="FJ14" s="1">
+        <v>18</v>
+      </c>
+      <c r="FK14" s="1">
+        <v>15</v>
+      </c>
+      <c r="FL14" s="1">
+        <v>8</v>
+      </c>
+      <c r="FM14" s="1">
+        <v>2</v>
+      </c>
+      <c r="FN14" s="1">
+        <v>3</v>
+      </c>
+      <c r="FO14" s="1">
+        <v>2</v>
+      </c>
+      <c r="FP14" s="1">
+        <v>2</v>
+      </c>
+      <c r="FQ14" s="1">
+        <v>8</v>
+      </c>
+      <c r="FR14" s="1">
+        <v>1</v>
+      </c>
+      <c r="FS14" s="1">
+        <v>3</v>
+      </c>
+      <c r="FT14" s="1">
+        <v>4</v>
+      </c>
+      <c r="FU14" s="1">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:152" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:178" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>92</v>
       </c>
@@ -8152,8 +9015,37 @@
       <c r="EV15">
         <v>0</v>
       </c>
+      <c r="FG15" s="1">
+        <v>3</v>
+      </c>
+      <c r="FH15" s="1">
+        <v>16</v>
+      </c>
+      <c r="FI15" s="1">
+        <v>5</v>
+      </c>
+      <c r="FJ15" s="7"/>
+      <c r="FK15" s="7"/>
+      <c r="FL15" s="7"/>
+      <c r="FM15" s="1">
+        <v>2</v>
+      </c>
+      <c r="FN15" s="1">
+        <v>5</v>
+      </c>
+      <c r="FO15" s="7"/>
+      <c r="FP15" s="7"/>
+      <c r="FQ15" s="1">
+        <v>2</v>
+      </c>
+      <c r="FR15" s="1">
+        <v>1</v>
+      </c>
+      <c r="FS15" s="7"/>
+      <c r="FT15" s="7"/>
+      <c r="FU15" s="7"/>
     </row>
-    <row r="16" spans="1:152" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:178" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>93</v>
       </c>
@@ -8611,7 +9503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:155" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:178" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>94</v>
       </c>
@@ -9069,7 +9961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:155" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:178" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>95</v>
       </c>
@@ -9526,8 +10418,86 @@
       <c r="EV18" s="8">
         <v>117</v>
       </c>
+      <c r="EW18" s="8">
+        <v>135</v>
+      </c>
+      <c r="EX18" s="8">
+        <v>112</v>
+      </c>
+      <c r="EY18" s="8">
+        <v>115</v>
+      </c>
+      <c r="EZ18" s="8">
+        <v>113</v>
+      </c>
+      <c r="FA18" s="8">
+        <v>90</v>
+      </c>
+      <c r="FB18" s="8">
+        <v>92</v>
+      </c>
+      <c r="FC18" s="8">
+        <v>97</v>
+      </c>
+      <c r="FD18" s="8">
+        <v>120</v>
+      </c>
+      <c r="FE18" s="8">
+        <v>108</v>
+      </c>
+      <c r="FF18" s="8">
+        <v>116</v>
+      </c>
+      <c r="FG18" s="8">
+        <v>101</v>
+      </c>
+      <c r="FH18" s="8">
+        <v>100</v>
+      </c>
+      <c r="FI18" s="8">
+        <v>85</v>
+      </c>
+      <c r="FJ18" s="8">
+        <v>130</v>
+      </c>
+      <c r="FK18" s="8">
+        <v>111</v>
+      </c>
+      <c r="FL18" s="8">
+        <v>107</v>
+      </c>
+      <c r="FM18" s="8">
+        <v>106</v>
+      </c>
+      <c r="FN18" s="8">
+        <v>122</v>
+      </c>
+      <c r="FO18" s="8">
+        <v>110</v>
+      </c>
+      <c r="FP18" s="8">
+        <v>87</v>
+      </c>
+      <c r="FQ18" s="8">
+        <v>120</v>
+      </c>
+      <c r="FR18" s="8">
+        <v>98</v>
+      </c>
+      <c r="FS18" s="8">
+        <v>117</v>
+      </c>
+      <c r="FT18" s="8">
+        <v>120</v>
+      </c>
+      <c r="FU18" s="8">
+        <v>88</v>
+      </c>
+      <c r="FV18" s="8">
+        <v>106</v>
+      </c>
     </row>
-    <row r="19" spans="1:155" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:178" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>96</v>
       </c>
@@ -9984,8 +10954,86 @@
       <c r="EV19" s="8">
         <v>117</v>
       </c>
+      <c r="EW19" s="8">
+        <v>135</v>
+      </c>
+      <c r="EX19" s="8">
+        <v>112</v>
+      </c>
+      <c r="EY19" s="8">
+        <v>115</v>
+      </c>
+      <c r="EZ19" s="8">
+        <v>113</v>
+      </c>
+      <c r="FA19" s="8">
+        <v>90</v>
+      </c>
+      <c r="FB19" s="8">
+        <v>92</v>
+      </c>
+      <c r="FC19" s="8">
+        <v>97</v>
+      </c>
+      <c r="FD19" s="8">
+        <v>120</v>
+      </c>
+      <c r="FE19" s="8">
+        <v>108</v>
+      </c>
+      <c r="FF19" s="8">
+        <v>116</v>
+      </c>
+      <c r="FG19" s="8">
+        <v>101</v>
+      </c>
+      <c r="FH19" s="8">
+        <v>100</v>
+      </c>
+      <c r="FI19" s="8">
+        <v>85</v>
+      </c>
+      <c r="FJ19" s="8">
+        <v>130</v>
+      </c>
+      <c r="FK19" s="8">
+        <v>111</v>
+      </c>
+      <c r="FL19" s="8">
+        <v>107</v>
+      </c>
+      <c r="FM19" s="8">
+        <v>106</v>
+      </c>
+      <c r="FN19" s="8">
+        <v>122</v>
+      </c>
+      <c r="FO19" s="8">
+        <v>110</v>
+      </c>
+      <c r="FP19" s="8">
+        <v>87</v>
+      </c>
+      <c r="FQ19" s="8">
+        <v>120</v>
+      </c>
+      <c r="FR19" s="8">
+        <v>98</v>
+      </c>
+      <c r="FS19" s="8">
+        <v>117</v>
+      </c>
+      <c r="FT19" s="8">
+        <v>120</v>
+      </c>
+      <c r="FU19" s="8">
+        <v>88</v>
+      </c>
+      <c r="FV19" s="8">
+        <v>106</v>
+      </c>
     </row>
-    <row r="20" spans="1:155" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:178" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>97</v>
       </c>
@@ -10442,8 +11490,86 @@
       <c r="EV20" s="9">
         <v>117</v>
       </c>
+      <c r="EW20" s="9">
+        <v>135</v>
+      </c>
+      <c r="EX20" s="9">
+        <v>112</v>
+      </c>
+      <c r="EY20" s="9">
+        <v>115</v>
+      </c>
+      <c r="EZ20" s="9">
+        <v>113</v>
+      </c>
+      <c r="FA20" s="9">
+        <v>90</v>
+      </c>
+      <c r="FB20" s="9">
+        <v>92</v>
+      </c>
+      <c r="FC20" s="9">
+        <v>97</v>
+      </c>
+      <c r="FD20" s="9">
+        <v>120</v>
+      </c>
+      <c r="FE20" s="9">
+        <v>108</v>
+      </c>
+      <c r="FF20" s="9">
+        <v>116</v>
+      </c>
+      <c r="FG20" s="9">
+        <v>101</v>
+      </c>
+      <c r="FH20" s="9">
+        <v>100</v>
+      </c>
+      <c r="FI20" s="9">
+        <v>85</v>
+      </c>
+      <c r="FJ20" s="9">
+        <v>130</v>
+      </c>
+      <c r="FK20" s="9">
+        <v>111</v>
+      </c>
+      <c r="FL20" s="9">
+        <v>99</v>
+      </c>
+      <c r="FM20" s="9">
+        <v>106</v>
+      </c>
+      <c r="FN20" s="9">
+        <v>122</v>
+      </c>
+      <c r="FO20" s="9">
+        <v>110</v>
+      </c>
+      <c r="FP20" s="9">
+        <v>87</v>
+      </c>
+      <c r="FQ20" s="9">
+        <v>120</v>
+      </c>
+      <c r="FR20" s="9">
+        <v>19</v>
+      </c>
+      <c r="FS20" s="9">
+        <v>30</v>
+      </c>
+      <c r="FT20" s="9">
+        <v>120</v>
+      </c>
+      <c r="FU20" s="9">
+        <v>88</v>
+      </c>
+      <c r="FV20" s="9">
+        <v>14</v>
+      </c>
     </row>
-    <row r="21" spans="1:155" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:178" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>98</v>
       </c>
@@ -10900,8 +12026,86 @@
       <c r="EV21">
         <v>100</v>
       </c>
+      <c r="EW21">
+        <v>100</v>
+      </c>
+      <c r="EX21">
+        <v>100</v>
+      </c>
+      <c r="EY21">
+        <v>100</v>
+      </c>
+      <c r="EZ21">
+        <v>100</v>
+      </c>
+      <c r="FA21">
+        <v>100</v>
+      </c>
+      <c r="FB21">
+        <v>100</v>
+      </c>
+      <c r="FC21">
+        <v>100</v>
+      </c>
+      <c r="FD21">
+        <v>100</v>
+      </c>
+      <c r="FE21">
+        <v>100</v>
+      </c>
+      <c r="FF21">
+        <v>100</v>
+      </c>
+      <c r="FG21">
+        <v>100</v>
+      </c>
+      <c r="FH21">
+        <v>100</v>
+      </c>
+      <c r="FI21">
+        <v>100</v>
+      </c>
+      <c r="FJ21">
+        <v>100</v>
+      </c>
+      <c r="FK21">
+        <v>100</v>
+      </c>
+      <c r="FL21">
+        <v>92.52</v>
+      </c>
+      <c r="FM21">
+        <v>100</v>
+      </c>
+      <c r="FN21">
+        <v>100</v>
+      </c>
+      <c r="FO21">
+        <v>100</v>
+      </c>
+      <c r="FP21">
+        <v>100</v>
+      </c>
+      <c r="FQ21">
+        <v>100</v>
+      </c>
+      <c r="FR21" s="11">
+        <v>19.39</v>
+      </c>
+      <c r="FS21" s="11">
+        <v>25.64</v>
+      </c>
+      <c r="FT21" s="11">
+        <v>100</v>
+      </c>
+      <c r="FU21" s="11">
+        <v>100</v>
+      </c>
+      <c r="FV21" s="11">
+        <v>13.21</v>
+      </c>
     </row>
-    <row r="22" spans="1:155" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:178" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>99</v>
       </c>
@@ -11330,11 +12534,80 @@
       <c r="EV22" s="6">
         <v>117</v>
       </c>
-      <c r="EW22" s="10"/>
-      <c r="EX22" s="10"/>
-      <c r="EY22" s="10"/>
+      <c r="EW22" s="1">
+        <v>135</v>
+      </c>
+      <c r="EX22" s="1">
+        <v>112</v>
+      </c>
+      <c r="EY22" s="1">
+        <v>115</v>
+      </c>
+      <c r="EZ22" s="1">
+        <v>113</v>
+      </c>
+      <c r="FA22" s="1">
+        <v>90</v>
+      </c>
+      <c r="FB22" s="1">
+        <v>92</v>
+      </c>
+      <c r="FC22" s="1">
+        <v>97</v>
+      </c>
+      <c r="FD22" s="1">
+        <v>120</v>
+      </c>
+      <c r="FE22" s="1">
+        <v>108</v>
+      </c>
+      <c r="FF22" s="7"/>
+      <c r="FG22" s="1">
+        <v>101</v>
+      </c>
+      <c r="FH22" s="1">
+        <v>100</v>
+      </c>
+      <c r="FI22" s="1">
+        <v>85</v>
+      </c>
+      <c r="FJ22" s="1">
+        <v>130</v>
+      </c>
+      <c r="FK22" s="1">
+        <v>111</v>
+      </c>
+      <c r="FL22" s="1">
+        <v>89</v>
+      </c>
+      <c r="FM22" s="1">
+        <v>106</v>
+      </c>
+      <c r="FN22" s="7"/>
+      <c r="FO22" s="1">
+        <v>110</v>
+      </c>
+      <c r="FP22" s="1">
+        <v>87</v>
+      </c>
+      <c r="FQ22" s="1">
+        <v>120</v>
+      </c>
+      <c r="FR22" s="1">
+        <v>19</v>
+      </c>
+      <c r="FS22" s="1">
+        <v>30</v>
+      </c>
+      <c r="FT22" s="7"/>
+      <c r="FU22" s="1">
+        <v>88</v>
+      </c>
+      <c r="FV22" s="1">
+        <v>14</v>
+      </c>
     </row>
-    <row r="23" spans="1:155" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:178" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>100</v>
       </c>
@@ -11787,8 +13060,33 @@
       <c r="EV23" s="4">
         <v>0</v>
       </c>
+      <c r="FF23" s="1">
+        <v>116</v>
+      </c>
+      <c r="FG23" s="7"/>
+      <c r="FH23" s="7"/>
+      <c r="FI23" s="7"/>
+      <c r="FJ23" s="7"/>
+      <c r="FK23" s="7"/>
+      <c r="FL23" s="1">
+        <v>10</v>
+      </c>
+      <c r="FM23" s="7"/>
+      <c r="FN23" s="1">
+        <v>122</v>
+      </c>
+      <c r="FO23" s="7"/>
+      <c r="FP23" s="7"/>
+      <c r="FQ23" s="7"/>
+      <c r="FR23" s="7"/>
+      <c r="FS23" s="7"/>
+      <c r="FT23" s="1">
+        <v>120</v>
+      </c>
+      <c r="FU23" s="7"/>
+      <c r="FV23" s="7"/>
     </row>
-    <row r="24" spans="1:155" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:178" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>101</v>
       </c>
@@ -12246,7 +13544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:155" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:178" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>102</v>
       </c>
@@ -12704,7 +14002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:155" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:178" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>103</v>
       </c>
@@ -12970,7 +14268,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:155" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:178" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>104</v>
       </c>
@@ -13236,7 +14534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:155" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:178" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>105</v>
       </c>
@@ -13502,7 +14800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:155" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:178" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>106</v>
       </c>
@@ -13768,7 +15066,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:155" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:178" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>107</v>
       </c>
@@ -14023,7 +15321,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:155" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:178" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>108</v>
       </c>
@@ -14268,7 +15566,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:155" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:178" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>109</v>
       </c>

--- a/public/analytics-data.xlsx
+++ b/public/analytics-data.xlsx
@@ -10,13 +10,12 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9142D3CC-490B-44DB-9863-5CB43DA0AAD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Analytics Data" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -912,7 +911,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -939,9 +938,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -12089,19 +12085,19 @@
       <c r="FQ21">
         <v>100</v>
       </c>
-      <c r="FR21" s="11">
+      <c r="FR21" s="1">
         <v>19.39</v>
       </c>
-      <c r="FS21" s="11">
+      <c r="FS21" s="1">
         <v>25.64</v>
       </c>
-      <c r="FT21" s="11">
-        <v>100</v>
-      </c>
-      <c r="FU21" s="11">
-        <v>100</v>
-      </c>
-      <c r="FV21" s="11">
+      <c r="FT21" s="1">
+        <v>100</v>
+      </c>
+      <c r="FU21" s="1">
+        <v>100</v>
+      </c>
+      <c r="FV21" s="1">
         <v>13.21</v>
       </c>
     </row>

--- a/public/analytics-data.xlsx
+++ b/public/analytics-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mona\Downloads\PhysicsWallahDashboard-Axio\axioP-x-PW-main\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9142D3CC-490B-44DB-9863-5CB43DA0AAD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D06B6241-E95C-4697-8141-FC010AEF3FF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4473,7 +4473,9 @@
       <c r="FM6" s="1">
         <v>38</v>
       </c>
-      <c r="FN6" s="7"/>
+      <c r="FN6" s="7">
+        <v>0</v>
+      </c>
       <c r="FO6" s="1">
         <v>22</v>
       </c>
@@ -4956,15 +4958,83 @@
       <c r="EV7">
         <v>0</v>
       </c>
+      <c r="EW7">
+        <v>0</v>
+      </c>
+      <c r="EX7">
+        <v>0</v>
+      </c>
+      <c r="EY7">
+        <v>0</v>
+      </c>
+      <c r="EZ7">
+        <v>0</v>
+      </c>
+      <c r="FA7">
+        <v>0</v>
+      </c>
+      <c r="FB7">
+        <v>0</v>
+      </c>
+      <c r="FC7">
+        <v>0</v>
+      </c>
+      <c r="FD7">
+        <v>0</v>
+      </c>
+      <c r="FE7">
+        <v>0</v>
+      </c>
+      <c r="FF7">
+        <v>0</v>
+      </c>
+      <c r="FG7">
+        <v>0</v>
+      </c>
+      <c r="FH7">
+        <v>0</v>
+      </c>
+      <c r="FI7">
+        <v>0</v>
+      </c>
+      <c r="FJ7">
+        <v>0</v>
+      </c>
       <c r="FK7" s="1">
         <v>1</v>
       </c>
-      <c r="FL7" s="7"/>
+      <c r="FL7" s="7">
+        <v>0</v>
+      </c>
       <c r="FM7" s="1">
         <v>2</v>
       </c>
       <c r="FN7" s="1">
         <v>32</v>
+      </c>
+      <c r="FO7" s="1">
+        <v>0</v>
+      </c>
+      <c r="FP7" s="1">
+        <v>0</v>
+      </c>
+      <c r="FQ7" s="1">
+        <v>0</v>
+      </c>
+      <c r="FR7" s="1">
+        <v>0</v>
+      </c>
+      <c r="FS7" s="1">
+        <v>0</v>
+      </c>
+      <c r="FT7" s="1">
+        <v>0</v>
+      </c>
+      <c r="FU7" s="1">
+        <v>0</v>
+      </c>
+      <c r="FV7" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:178" x14ac:dyDescent="0.3">
@@ -5424,6 +5494,84 @@
       <c r="EV8">
         <v>0</v>
       </c>
+      <c r="EW8">
+        <v>0</v>
+      </c>
+      <c r="EX8">
+        <v>0</v>
+      </c>
+      <c r="EY8">
+        <v>0</v>
+      </c>
+      <c r="EZ8">
+        <v>0</v>
+      </c>
+      <c r="FA8">
+        <v>0</v>
+      </c>
+      <c r="FB8">
+        <v>0</v>
+      </c>
+      <c r="FC8">
+        <v>0</v>
+      </c>
+      <c r="FD8">
+        <v>0</v>
+      </c>
+      <c r="FE8">
+        <v>0</v>
+      </c>
+      <c r="FF8">
+        <v>0</v>
+      </c>
+      <c r="FG8">
+        <v>0</v>
+      </c>
+      <c r="FH8">
+        <v>0</v>
+      </c>
+      <c r="FI8">
+        <v>0</v>
+      </c>
+      <c r="FJ8">
+        <v>0</v>
+      </c>
+      <c r="FK8">
+        <v>0</v>
+      </c>
+      <c r="FL8">
+        <v>0</v>
+      </c>
+      <c r="FM8">
+        <v>0</v>
+      </c>
+      <c r="FN8">
+        <v>0</v>
+      </c>
+      <c r="FO8">
+        <v>0</v>
+      </c>
+      <c r="FP8">
+        <v>0</v>
+      </c>
+      <c r="FQ8">
+        <v>0</v>
+      </c>
+      <c r="FR8">
+        <v>0</v>
+      </c>
+      <c r="FS8">
+        <v>0</v>
+      </c>
+      <c r="FT8">
+        <v>0</v>
+      </c>
+      <c r="FU8">
+        <v>0</v>
+      </c>
+      <c r="FV8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:178" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
@@ -5882,6 +6030,84 @@
       <c r="EV9">
         <v>0</v>
       </c>
+      <c r="EW9">
+        <v>0</v>
+      </c>
+      <c r="EX9">
+        <v>0</v>
+      </c>
+      <c r="EY9">
+        <v>0</v>
+      </c>
+      <c r="EZ9">
+        <v>0</v>
+      </c>
+      <c r="FA9">
+        <v>0</v>
+      </c>
+      <c r="FB9">
+        <v>0</v>
+      </c>
+      <c r="FC9">
+        <v>0</v>
+      </c>
+      <c r="FD9">
+        <v>0</v>
+      </c>
+      <c r="FE9">
+        <v>0</v>
+      </c>
+      <c r="FF9">
+        <v>0</v>
+      </c>
+      <c r="FG9">
+        <v>0</v>
+      </c>
+      <c r="FH9">
+        <v>0</v>
+      </c>
+      <c r="FI9">
+        <v>0</v>
+      </c>
+      <c r="FJ9">
+        <v>0</v>
+      </c>
+      <c r="FK9">
+        <v>0</v>
+      </c>
+      <c r="FL9">
+        <v>0</v>
+      </c>
+      <c r="FM9">
+        <v>0</v>
+      </c>
+      <c r="FN9">
+        <v>0</v>
+      </c>
+      <c r="FO9">
+        <v>0</v>
+      </c>
+      <c r="FP9">
+        <v>0</v>
+      </c>
+      <c r="FQ9">
+        <v>0</v>
+      </c>
+      <c r="FR9">
+        <v>0</v>
+      </c>
+      <c r="FS9">
+        <v>0</v>
+      </c>
+      <c r="FT9">
+        <v>0</v>
+      </c>
+      <c r="FU9">
+        <v>0</v>
+      </c>
+      <c r="FV9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:178" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
@@ -7487,7 +7713,9 @@
       <c r="FU12" s="1">
         <v>7</v>
       </c>
-      <c r="FV12" s="10"/>
+      <c r="FV12" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:178" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -8513,7 +8741,9 @@
       <c r="FG14" s="1">
         <v>6</v>
       </c>
-      <c r="FH14" s="7"/>
+      <c r="FH14" s="7">
+        <v>0</v>
+      </c>
       <c r="FI14" s="1">
         <v>9</v>
       </c>
@@ -8552,6 +8782,9 @@
       </c>
       <c r="FU14" s="1">
         <v>7</v>
+      </c>
+      <c r="FV14" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:178" x14ac:dyDescent="0.3">
@@ -9011,6 +9244,36 @@
       <c r="EV15">
         <v>0</v>
       </c>
+      <c r="EW15" s="1">
+        <v>0</v>
+      </c>
+      <c r="EX15">
+        <v>0</v>
+      </c>
+      <c r="EY15" s="1">
+        <v>0</v>
+      </c>
+      <c r="EZ15">
+        <v>0</v>
+      </c>
+      <c r="FA15" s="1">
+        <v>0</v>
+      </c>
+      <c r="FB15">
+        <v>0</v>
+      </c>
+      <c r="FC15" s="1">
+        <v>0</v>
+      </c>
+      <c r="FD15">
+        <v>0</v>
+      </c>
+      <c r="FE15" s="1">
+        <v>0</v>
+      </c>
+      <c r="FF15">
+        <v>0</v>
+      </c>
       <c r="FG15" s="1">
         <v>3</v>
       </c>
@@ -9020,26 +9283,45 @@
       <c r="FI15" s="1">
         <v>5</v>
       </c>
-      <c r="FJ15" s="7"/>
-      <c r="FK15" s="7"/>
-      <c r="FL15" s="7"/>
+      <c r="FJ15" s="7">
+        <v>0</v>
+      </c>
+      <c r="FK15" s="7">
+        <v>0</v>
+      </c>
+      <c r="FL15" s="7">
+        <v>0</v>
+      </c>
       <c r="FM15" s="1">
         <v>2</v>
       </c>
       <c r="FN15" s="1">
         <v>5</v>
       </c>
-      <c r="FO15" s="7"/>
-      <c r="FP15" s="7"/>
+      <c r="FO15" s="7">
+        <v>0</v>
+      </c>
+      <c r="FP15" s="7">
+        <v>0</v>
+      </c>
       <c r="FQ15" s="1">
         <v>2</v>
       </c>
       <c r="FR15" s="1">
         <v>1</v>
       </c>
-      <c r="FS15" s="7"/>
-      <c r="FT15" s="7"/>
-      <c r="FU15" s="7"/>
+      <c r="FS15" s="7">
+        <v>0</v>
+      </c>
+      <c r="FT15" s="7">
+        <v>0</v>
+      </c>
+      <c r="FU15" s="7">
+        <v>0</v>
+      </c>
+      <c r="FV15" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:178" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -9498,6 +9780,84 @@
       <c r="EV16">
         <v>0</v>
       </c>
+      <c r="EW16">
+        <v>0</v>
+      </c>
+      <c r="EX16">
+        <v>0</v>
+      </c>
+      <c r="EY16">
+        <v>0</v>
+      </c>
+      <c r="EZ16">
+        <v>0</v>
+      </c>
+      <c r="FA16">
+        <v>0</v>
+      </c>
+      <c r="FB16">
+        <v>0</v>
+      </c>
+      <c r="FC16">
+        <v>0</v>
+      </c>
+      <c r="FD16">
+        <v>0</v>
+      </c>
+      <c r="FE16">
+        <v>0</v>
+      </c>
+      <c r="FF16">
+        <v>0</v>
+      </c>
+      <c r="FG16">
+        <v>0</v>
+      </c>
+      <c r="FH16">
+        <v>0</v>
+      </c>
+      <c r="FI16">
+        <v>0</v>
+      </c>
+      <c r="FJ16">
+        <v>0</v>
+      </c>
+      <c r="FK16">
+        <v>0</v>
+      </c>
+      <c r="FL16">
+        <v>0</v>
+      </c>
+      <c r="FM16">
+        <v>0</v>
+      </c>
+      <c r="FN16">
+        <v>0</v>
+      </c>
+      <c r="FO16">
+        <v>0</v>
+      </c>
+      <c r="FP16">
+        <v>0</v>
+      </c>
+      <c r="FQ16">
+        <v>0</v>
+      </c>
+      <c r="FR16">
+        <v>0</v>
+      </c>
+      <c r="FS16">
+        <v>0</v>
+      </c>
+      <c r="FT16">
+        <v>0</v>
+      </c>
+      <c r="FU16">
+        <v>0</v>
+      </c>
+      <c r="FV16">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:178" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
@@ -9954,6 +10314,84 @@
         <v>0</v>
       </c>
       <c r="EV17">
+        <v>0</v>
+      </c>
+      <c r="EW17">
+        <v>0</v>
+      </c>
+      <c r="EX17">
+        <v>0</v>
+      </c>
+      <c r="EY17">
+        <v>0</v>
+      </c>
+      <c r="EZ17">
+        <v>0</v>
+      </c>
+      <c r="FA17">
+        <v>0</v>
+      </c>
+      <c r="FB17">
+        <v>0</v>
+      </c>
+      <c r="FC17">
+        <v>0</v>
+      </c>
+      <c r="FD17">
+        <v>0</v>
+      </c>
+      <c r="FE17">
+        <v>0</v>
+      </c>
+      <c r="FF17">
+        <v>0</v>
+      </c>
+      <c r="FG17">
+        <v>0</v>
+      </c>
+      <c r="FH17">
+        <v>0</v>
+      </c>
+      <c r="FI17">
+        <v>0</v>
+      </c>
+      <c r="FJ17">
+        <v>0</v>
+      </c>
+      <c r="FK17">
+        <v>0</v>
+      </c>
+      <c r="FL17">
+        <v>0</v>
+      </c>
+      <c r="FM17">
+        <v>0</v>
+      </c>
+      <c r="FN17">
+        <v>0</v>
+      </c>
+      <c r="FO17">
+        <v>0</v>
+      </c>
+      <c r="FP17">
+        <v>0</v>
+      </c>
+      <c r="FQ17">
+        <v>0</v>
+      </c>
+      <c r="FR17">
+        <v>0</v>
+      </c>
+      <c r="FS17">
+        <v>0</v>
+      </c>
+      <c r="FT17">
+        <v>0</v>
+      </c>
+      <c r="FU17">
+        <v>0</v>
+      </c>
+      <c r="FV17">
         <v>0</v>
       </c>
     </row>

--- a/public/analytics-data.xlsx
+++ b/public/analytics-data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mona\Downloads\PhysicsWallahDashboard-Axio\axioP-x-PW-main\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D06B6241-E95C-4697-8141-FC010AEF3FF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DAC805-09E0-4646-8539-3AACA6E46C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -911,7 +911,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -935,9 +935,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7708,13 +7705,13 @@
         <v>3</v>
       </c>
       <c r="FT12" s="1">
+        <v>14</v>
+      </c>
+      <c r="FU12" s="1">
+        <v>9</v>
+      </c>
+      <c r="FV12" s="1">
         <v>4</v>
-      </c>
-      <c r="FU12" s="1">
-        <v>7</v>
-      </c>
-      <c r="FV12" s="10">
-        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:178" x14ac:dyDescent="0.3">
@@ -8244,13 +8241,13 @@
         <v>100</v>
       </c>
       <c r="FT13" s="1">
-        <v>25</v>
+        <v>85.5</v>
       </c>
       <c r="FU13" s="1">
-        <v>58.33</v>
+        <v>75</v>
       </c>
       <c r="FV13" s="1">
-        <v>0</v>
+        <v>44.44</v>
       </c>
     </row>
     <row r="14" spans="1:178" x14ac:dyDescent="0.3">
@@ -9314,13 +9311,13 @@
         <v>0</v>
       </c>
       <c r="FT15" s="7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="FU15" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="FV15" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:178" x14ac:dyDescent="0.3">
@@ -11467,7 +11464,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="20" spans="1:178" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:178" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>97</v>
       </c>
@@ -11966,41 +11963,41 @@
       <c r="FJ20" s="9">
         <v>130</v>
       </c>
-      <c r="FK20" s="9">
+      <c r="FK20" s="8">
         <v>111</v>
       </c>
-      <c r="FL20" s="9">
-        <v>99</v>
-      </c>
-      <c r="FM20" s="9">
+      <c r="FL20" s="8">
+        <v>107</v>
+      </c>
+      <c r="FM20" s="8">
         <v>106</v>
       </c>
-      <c r="FN20" s="9">
+      <c r="FN20" s="8">
         <v>122</v>
       </c>
-      <c r="FO20" s="9">
+      <c r="FO20" s="8">
         <v>110</v>
       </c>
-      <c r="FP20" s="9">
+      <c r="FP20" s="8">
         <v>87</v>
       </c>
-      <c r="FQ20" s="9">
+      <c r="FQ20" s="8">
         <v>120</v>
       </c>
-      <c r="FR20" s="9">
-        <v>19</v>
-      </c>
-      <c r="FS20" s="9">
-        <v>30</v>
-      </c>
-      <c r="FT20" s="9">
+      <c r="FR20" s="8">
+        <v>98</v>
+      </c>
+      <c r="FS20" s="8">
+        <v>117</v>
+      </c>
+      <c r="FT20" s="8">
         <v>120</v>
       </c>
-      <c r="FU20" s="9">
+      <c r="FU20" s="8">
         <v>88</v>
       </c>
-      <c r="FV20" s="9">
-        <v>14</v>
+      <c r="FV20" s="8">
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:178" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -12506,7 +12503,7 @@
         <v>100</v>
       </c>
       <c r="FL21">
-        <v>92.52</v>
+        <v>100</v>
       </c>
       <c r="FM21">
         <v>100</v>
@@ -12523,20 +12520,20 @@
       <c r="FQ21">
         <v>100</v>
       </c>
-      <c r="FR21" s="1">
-        <v>19.39</v>
-      </c>
-      <c r="FS21" s="1">
-        <v>25.64</v>
-      </c>
-      <c r="FT21" s="1">
-        <v>100</v>
-      </c>
-      <c r="FU21" s="1">
-        <v>100</v>
-      </c>
-      <c r="FV21" s="1">
-        <v>13.21</v>
+      <c r="FR21">
+        <v>100</v>
+      </c>
+      <c r="FS21">
+        <v>100</v>
+      </c>
+      <c r="FT21">
+        <v>100</v>
+      </c>
+      <c r="FU21">
+        <v>100</v>
+      </c>
+      <c r="FV21">
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:178" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -13503,7 +13500,7 @@
       <c r="FJ23" s="7"/>
       <c r="FK23" s="7"/>
       <c r="FL23" s="1">
-        <v>10</v>
+        <v>118</v>
       </c>
       <c r="FM23" s="7"/>
       <c r="FN23" s="1">
@@ -13512,13 +13509,19 @@
       <c r="FO23" s="7"/>
       <c r="FP23" s="7"/>
       <c r="FQ23" s="7"/>
-      <c r="FR23" s="7"/>
-      <c r="FS23" s="7"/>
+      <c r="FR23" s="7">
+        <v>79</v>
+      </c>
+      <c r="FS23" s="7">
+        <v>87</v>
+      </c>
       <c r="FT23" s="1">
         <v>120</v>
       </c>
       <c r="FU23" s="7"/>
-      <c r="FV23" s="7"/>
+      <c r="FV23" s="7">
+        <v>92</v>
+      </c>
     </row>
     <row r="24" spans="1:178" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
